--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127723518</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723479</v>
+        <v>127723434</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445309</v>
+        <v>445345</v>
       </c>
       <c r="R3" t="n">
-        <v>6768491</v>
+        <v>6768366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723434</v>
+        <v>127723480</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445345</v>
+        <v>445314</v>
       </c>
       <c r="R4" t="n">
-        <v>6768366</v>
+        <v>6768485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723480</v>
+        <v>127723421</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445314</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>6768485</v>
+        <v>6768495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723421</v>
+        <v>127723416</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445361</v>
+        <v>445426</v>
       </c>
       <c r="R6" t="n">
-        <v>6768495</v>
+        <v>6768417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723416</v>
+        <v>127723493</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445426</v>
+        <v>445363</v>
       </c>
       <c r="R7" t="n">
-        <v>6768417</v>
+        <v>6768410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723493</v>
+        <v>127723531</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445363</v>
+        <v>445524</v>
       </c>
       <c r="R8" t="n">
-        <v>6768410</v>
+        <v>6768371</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127722873</v>
+        <v>127723424</v>
       </c>
       <c r="B9" t="n">
-        <v>57821</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,39 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445364</v>
+        <v>445311</v>
       </c>
       <c r="R9" t="n">
-        <v>6768295</v>
+        <v>6768500</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723531</v>
+        <v>127722873</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,34 +1462,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445524</v>
+        <v>445364</v>
       </c>
       <c r="R10" t="n">
-        <v>6768371</v>
+        <v>6768295</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723424</v>
+        <v>127723479</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445311</v>
+        <v>445309</v>
       </c>
       <c r="R11" t="n">
-        <v>6768500</v>
+        <v>6768491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1653,7 +1653,7 @@
         <v>127723602</v>
       </c>
       <c r="B12" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127723606</v>
       </c>
       <c r="B13" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>127723445</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>127723512</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723517</v>
+        <v>127723561</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445463</v>
+        <v>445519</v>
       </c>
       <c r="R16" t="n">
-        <v>6768439</v>
+        <v>6768373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723435</v>
+        <v>127723520</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R17" t="n">
-        <v>6768348</v>
+        <v>6768423</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723442</v>
+        <v>127723517</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445407</v>
+        <v>445463</v>
       </c>
       <c r="R18" t="n">
-        <v>6768295</v>
+        <v>6768439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723561</v>
+        <v>127723435</v>
       </c>
       <c r="B19" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445519</v>
+        <v>445375</v>
       </c>
       <c r="R19" t="n">
-        <v>6768373</v>
+        <v>6768348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723520</v>
+        <v>127723442</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445439</v>
+        <v>445407</v>
       </c>
       <c r="R20" t="n">
-        <v>6768423</v>
+        <v>6768295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2526,7 +2526,7 @@
         <v>127723500</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723527</v>
+        <v>127723412</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445476</v>
+        <v>445423</v>
       </c>
       <c r="R22" t="n">
-        <v>6768382</v>
+        <v>6768342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723412</v>
+        <v>127723417</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445423</v>
+        <v>445413</v>
       </c>
       <c r="R23" t="n">
-        <v>6768342</v>
+        <v>6768451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723417</v>
+        <v>127723525</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445413</v>
+        <v>445465</v>
       </c>
       <c r="R24" t="n">
-        <v>6768451</v>
+        <v>6768379</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723433</v>
+        <v>127723527</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445354</v>
+        <v>445476</v>
       </c>
       <c r="R25" t="n">
-        <v>6768399</v>
+        <v>6768382</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723525</v>
+        <v>127723433</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445465</v>
+        <v>445354</v>
       </c>
       <c r="R26" t="n">
-        <v>6768379</v>
+        <v>6768399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723523</v>
+        <v>127723487</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445451</v>
+        <v>445328</v>
       </c>
       <c r="R27" t="n">
-        <v>6768402</v>
+        <v>6768445</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723529</v>
+        <v>127723523</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445507</v>
+        <v>445451</v>
       </c>
       <c r="R28" t="n">
-        <v>6768383</v>
+        <v>6768402</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127722895</v>
+        <v>127723529</v>
       </c>
       <c r="B29" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3310,39 +3310,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445370</v>
+        <v>445507</v>
       </c>
       <c r="R29" t="n">
-        <v>6768276</v>
+        <v>6768383</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3401,50 +3396,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723028</v>
+        <v>127723538</v>
       </c>
       <c r="B30" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445345</v>
+        <v>445485</v>
       </c>
       <c r="R30" t="n">
-        <v>6768382</v>
+        <v>6768313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3471,12 +3461,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3503,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723538</v>
+        <v>127723428</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3538,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445485</v>
+        <v>445329</v>
       </c>
       <c r="R31" t="n">
-        <v>6768313</v>
+        <v>6768465</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3600,45 +3590,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723487</v>
+        <v>127723028</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445328</v>
+        <v>445345</v>
       </c>
       <c r="R32" t="n">
-        <v>6768445</v>
+        <v>6768382</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3665,12 +3660,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3697,10 +3692,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723428</v>
+        <v>127722895</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3708,34 +3703,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445329</v>
+        <v>445370</v>
       </c>
       <c r="R33" t="n">
-        <v>6768465</v>
+        <v>6768276</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723431</v>
+        <v>127723482</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445369</v>
+        <v>445318</v>
       </c>
       <c r="R35" t="n">
-        <v>6768408</v>
+        <v>6768474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723536</v>
+        <v>127723515</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445500</v>
+        <v>445465</v>
       </c>
       <c r="R36" t="n">
-        <v>6768348</v>
+        <v>6768438</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723482</v>
+        <v>127723431</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445318</v>
+        <v>445369</v>
       </c>
       <c r="R37" t="n">
-        <v>6768474</v>
+        <v>6768408</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723446</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445453</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723515</v>
+        <v>127723446</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445465</v>
+        <v>445453</v>
       </c>
       <c r="R39" t="n">
-        <v>6768438</v>
+        <v>6768321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4379,7 +4379,7 @@
         <v>127723422</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>127723565</v>
       </c>
       <c r="B41" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>127723427</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127723418</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,50 +4769,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723025</v>
+        <v>127723534</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445397</v>
+        <v>445528</v>
       </c>
       <c r="R44" t="n">
-        <v>6768481</v>
+        <v>6768349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4839,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4871,50 +4866,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723026</v>
+        <v>127723521</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445387</v>
+        <v>445445</v>
       </c>
       <c r="R45" t="n">
-        <v>6768492</v>
+        <v>6768409</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4941,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4973,45 +4963,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723604</v>
+        <v>127723025</v>
       </c>
       <c r="B46" t="n">
-        <v>78685</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R46" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5038,12 +5033,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5070,45 +5065,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723592</v>
+        <v>127723026</v>
       </c>
       <c r="B47" t="n">
-        <v>78685</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445370</v>
+        <v>445387</v>
       </c>
       <c r="R47" t="n">
-        <v>6768478</v>
+        <v>6768492</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,10 +5167,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723534</v>
+        <v>127723604</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5178,21 +5178,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445528</v>
+        <v>445370</v>
       </c>
       <c r="R48" t="n">
-        <v>6768349</v>
+        <v>6768425</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723521</v>
+        <v>127723592</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5275,21 +5275,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445445</v>
+        <v>445370</v>
       </c>
       <c r="R49" t="n">
-        <v>6768409</v>
+        <v>6768478</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5364,7 +5364,7 @@
         <v>127723501</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127723478</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723444</v>
+        <v>127722889</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,34 +5566,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445432</v>
+        <v>445372</v>
       </c>
       <c r="R52" t="n">
-        <v>6768299</v>
+        <v>6768323</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,10 +5657,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127723444</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445432</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768299</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,10 +5754,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723425</v>
+        <v>127723430</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5784,10 +5789,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445321</v>
+        <v>445357</v>
       </c>
       <c r="R54" t="n">
-        <v>6768501</v>
+        <v>6768451</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5851,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722889</v>
+        <v>127723425</v>
       </c>
       <c r="B55" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,39 +5862,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445372</v>
+        <v>445321</v>
       </c>
       <c r="R55" t="n">
-        <v>6768323</v>
+        <v>6768501</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5948,10 +5948,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722829</v>
+        <v>127723524</v>
       </c>
       <c r="B56" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5959,21 +5959,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445339</v>
+        <v>445455</v>
       </c>
       <c r="R56" t="n">
-        <v>6768436</v>
+        <v>6768391</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6045,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723524</v>
+        <v>127722829</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,21 +6056,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445455</v>
+        <v>445339</v>
       </c>
       <c r="R57" t="n">
-        <v>6768391</v>
+        <v>6768436</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723499</v>
+        <v>127723526</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445418</v>
+        <v>445468</v>
       </c>
       <c r="R58" t="n">
-        <v>6768394</v>
+        <v>6768377</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723526</v>
+        <v>127723499</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445468</v>
+        <v>445418</v>
       </c>
       <c r="R59" t="n">
-        <v>6768377</v>
+        <v>6768394</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6339,7 +6339,7 @@
         <v>127723492</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
         <v>127723488</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B62" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,39 +6541,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R62" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,11 +6601,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6637,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723413</v>
+        <v>127722914</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6648,34 +6638,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445444</v>
+        <v>445325</v>
       </c>
       <c r="R63" t="n">
-        <v>6768341</v>
+        <v>6768463</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6708,6 +6703,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6737,7 +6737,7 @@
         <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723514</v>
+        <v>127723506</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445468</v>
+        <v>445509</v>
       </c>
       <c r="R65" t="n">
-        <v>6768439</v>
+        <v>6768424</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723439</v>
+        <v>127723511</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445382</v>
+        <v>445497</v>
       </c>
       <c r="R66" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7030,10 +7030,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723506</v>
+        <v>127723514</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445509</v>
+        <v>445468</v>
       </c>
       <c r="R67" t="n">
-        <v>6768424</v>
+        <v>6768439</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723489</v>
+        <v>127723439</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445349</v>
+        <v>445382</v>
       </c>
       <c r="R68" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7192,12 +7192,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7224,10 +7224,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723455</v>
+        <v>127723489</v>
       </c>
       <c r="B69" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445417</v>
+        <v>445349</v>
       </c>
       <c r="R69" t="n">
-        <v>6768483</v>
+        <v>6768438</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127722917</v>
+        <v>127723455</v>
       </c>
       <c r="B70" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7332,39 +7332,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445329</v>
+        <v>445417</v>
       </c>
       <c r="R70" t="n">
-        <v>6768466</v>
+        <v>6768483</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7391,17 +7386,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7431,7 +7421,7 @@
         <v>127723522</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7528,7 +7518,7 @@
         <v>127723519</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7622,10 +7612,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127722908</v>
+        <v>127723496</v>
       </c>
       <c r="B73" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7633,39 +7623,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445329</v>
+        <v>445376</v>
       </c>
       <c r="R73" t="n">
-        <v>6768474</v>
+        <v>6768426</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7692,17 +7677,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7729,10 +7709,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723496</v>
+        <v>127723528</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7764,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445376</v>
+        <v>445493</v>
       </c>
       <c r="R74" t="n">
-        <v>6768426</v>
+        <v>6768388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7826,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723511</v>
+        <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7837,34 +7817,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445497</v>
+        <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768438</v>
+        <v>6768466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7891,12 +7876,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7923,10 +7913,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723528</v>
+        <v>127722908</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7934,34 +7924,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445493</v>
+        <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768388</v>
+        <v>6768474</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7988,12 +7983,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8122,32 +8122,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723415</v>
+        <v>127723560</v>
       </c>
       <c r="B78" t="n">
-        <v>79018</v>
+        <v>92622</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445433</v>
       </c>
       <c r="R78" t="n">
-        <v>6768387</v>
+        <v>6768412</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723411</v>
+        <v>127723415</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445410</v>
+        <v>445422</v>
       </c>
       <c r="R79" t="n">
-        <v>6768338</v>
+        <v>6768387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,50 +8316,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127722931</v>
+        <v>127723411</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445518</v>
+        <v>445410</v>
       </c>
       <c r="R80" t="n">
-        <v>6768355</v>
+        <v>6768338</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8421,7 +8416,7 @@
         <v>127723494</v>
       </c>
       <c r="B81" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8515,50 +8510,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127722930</v>
+        <v>127723537</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445390</v>
+        <v>445488</v>
       </c>
       <c r="R82" t="n">
-        <v>6768381</v>
+        <v>6768315</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8617,32 +8607,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723560</v>
+        <v>127723533</v>
       </c>
       <c r="B83" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8652,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445433</v>
+        <v>445523</v>
       </c>
       <c r="R83" t="n">
-        <v>6768412</v>
+        <v>6768356</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8714,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723537</v>
+        <v>127723432</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8749,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445488</v>
+        <v>445360</v>
       </c>
       <c r="R84" t="n">
-        <v>6768315</v>
+        <v>6768399</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8779,12 +8769,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8811,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723533</v>
+        <v>127723423</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8846,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445523</v>
+        <v>445325</v>
       </c>
       <c r="R85" t="n">
-        <v>6768356</v>
+        <v>6768515</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8876,12 +8866,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8908,10 +8898,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127722825</v>
+        <v>127723420</v>
       </c>
       <c r="B86" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8919,21 +8909,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8943,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445386</v>
+        <v>445395</v>
       </c>
       <c r="R86" t="n">
-        <v>6768493</v>
+        <v>6768485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9005,10 +8995,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723432</v>
+        <v>127722825</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9016,21 +9006,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9040,10 +9030,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445360</v>
+        <v>445386</v>
       </c>
       <c r="R87" t="n">
-        <v>6768399</v>
+        <v>6768493</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,45 +9092,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723423</v>
+        <v>127722931</v>
       </c>
       <c r="B88" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445325</v>
+        <v>445518</v>
       </c>
       <c r="R88" t="n">
-        <v>6768515</v>
+        <v>6768355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9199,7 +9194,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723030</v>
+        <v>127722930</v>
       </c>
       <c r="B89" t="n">
         <v>8450</v>
@@ -9230,7 +9225,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9239,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445376</v>
+        <v>445390</v>
       </c>
       <c r="R89" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9269,12 +9264,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9301,45 +9296,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723420</v>
+        <v>127723030</v>
       </c>
       <c r="B90" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445395</v>
+        <v>445376</v>
       </c>
       <c r="R90" t="n">
-        <v>6768485</v>
+        <v>6768336</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9500,10 +9500,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723436</v>
+        <v>127723414</v>
       </c>
       <c r="B92" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9535,10 +9535,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445366</v>
+        <v>445429</v>
       </c>
       <c r="R92" t="n">
-        <v>6768321</v>
+        <v>6768360</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9597,10 +9597,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723426</v>
+        <v>127723436</v>
       </c>
       <c r="B93" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9632,10 +9632,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445366</v>
       </c>
       <c r="R93" t="n">
-        <v>6768470</v>
+        <v>6768321</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9694,10 +9694,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723452</v>
+        <v>127723426</v>
       </c>
       <c r="B94" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9729,10 +9729,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445473</v>
+        <v>445324</v>
       </c>
       <c r="R94" t="n">
-        <v>6768325</v>
+        <v>6768470</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9759,12 +9759,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9791,10 +9791,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723497</v>
+        <v>127723452</v>
       </c>
       <c r="B95" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9826,10 +9826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445376</v>
+        <v>445473</v>
       </c>
       <c r="R95" t="n">
-        <v>6768407</v>
+        <v>6768325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9888,10 +9888,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723504</v>
+        <v>127723497</v>
       </c>
       <c r="B96" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9923,10 +9923,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445449</v>
+        <v>445376</v>
       </c>
       <c r="R96" t="n">
-        <v>6768387</v>
+        <v>6768407</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9985,10 +9985,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723414</v>
+        <v>127723504</v>
       </c>
       <c r="B97" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10020,10 +10020,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445429</v>
+        <v>445449</v>
       </c>
       <c r="R97" t="n">
-        <v>6768360</v>
+        <v>6768387</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723440</v>
+        <v>127722864</v>
       </c>
       <c r="B98" t="n">
-        <v>79018</v>
+        <v>91332</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445394</v>
+        <v>445327</v>
       </c>
       <c r="R98" t="n">
-        <v>6768290</v>
+        <v>6768444</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,12 +10147,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10179,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127722864</v>
+        <v>127723605</v>
       </c>
       <c r="B99" t="n">
-        <v>91330</v>
+        <v>78687</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10190,21 +10190,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445327</v>
+        <v>445403</v>
       </c>
       <c r="R99" t="n">
-        <v>6768444</v>
+        <v>6768385</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723490</v>
+        <v>127723440</v>
       </c>
       <c r="B100" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445353</v>
+        <v>445394</v>
       </c>
       <c r="R100" t="n">
-        <v>6768438</v>
+        <v>6768290</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,10 +10373,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127722918</v>
+        <v>127723490</v>
       </c>
       <c r="B101" t="n">
-        <v>57661</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10384,39 +10384,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445382</v>
+        <v>445353</v>
       </c>
       <c r="R101" t="n">
-        <v>6768422</v>
+        <v>6768438</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10449,11 +10444,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10483,7 +10473,7 @@
         <v>127723447</v>
       </c>
       <c r="B102" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10577,50 +10567,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723027</v>
+        <v>127723535</v>
       </c>
       <c r="B103" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445343</v>
+        <v>445518</v>
       </c>
       <c r="R103" t="n">
-        <v>6768460</v>
+        <v>6768343</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10647,12 +10632,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10679,10 +10664,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723605</v>
+        <v>127723483</v>
       </c>
       <c r="B104" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10690,21 +10675,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10714,10 +10699,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445403</v>
+        <v>445310</v>
       </c>
       <c r="R104" t="n">
-        <v>6768385</v>
+        <v>6768467</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10776,10 +10761,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723535</v>
+        <v>127723454</v>
       </c>
       <c r="B105" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10811,10 +10796,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445518</v>
+        <v>445421</v>
       </c>
       <c r="R105" t="n">
-        <v>6768343</v>
+        <v>6768465</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10873,10 +10858,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723483</v>
+        <v>127722918</v>
       </c>
       <c r="B106" t="n">
-        <v>79018</v>
+        <v>57663</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10884,34 +10869,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445310</v>
+        <v>445382</v>
       </c>
       <c r="R106" t="n">
-        <v>6768467</v>
+        <v>6768422</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10944,6 +10934,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10970,45 +10965,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723454</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445421</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768465</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723495</v>
+        <v>127723593</v>
       </c>
       <c r="B108" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,21 +11078,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445361</v>
+        <v>445417</v>
       </c>
       <c r="R108" t="n">
-        <v>6768425</v>
+        <v>6768470</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723593</v>
+        <v>127722832</v>
       </c>
       <c r="B109" t="n">
-        <v>78685</v>
+        <v>79638</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11175,21 +11175,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445417</v>
+        <v>445457</v>
       </c>
       <c r="R109" t="n">
-        <v>6768470</v>
+        <v>6768397</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723481</v>
+        <v>127723495</v>
       </c>
       <c r="B110" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445320</v>
+        <v>445361</v>
       </c>
       <c r="R110" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127722832</v>
+        <v>127723481</v>
       </c>
       <c r="B111" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445457</v>
+        <v>445320</v>
       </c>
       <c r="R111" t="n">
-        <v>6768397</v>
+        <v>6768481</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11458,7 +11458,7 @@
         <v>127723429</v>
       </c>
       <c r="B112" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723498</v>
+        <v>127723607</v>
       </c>
       <c r="B113" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445386</v>
+        <v>445529</v>
       </c>
       <c r="R113" t="n">
-        <v>6768393</v>
+        <v>6768354</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723530</v>
+        <v>127723498</v>
       </c>
       <c r="B114" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445515</v>
+        <v>445386</v>
       </c>
       <c r="R114" t="n">
-        <v>6768378</v>
+        <v>6768393</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11749,7 +11749,7 @@
         <v>127723441</v>
       </c>
       <c r="B115" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11843,10 +11843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723607</v>
+        <v>127723532</v>
       </c>
       <c r="B116" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11854,21 +11854,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445529</v>
+        <v>445523</v>
       </c>
       <c r="R116" t="n">
-        <v>6768354</v>
+        <v>6768362</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,10 +11940,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723532</v>
+        <v>127723453</v>
       </c>
       <c r="B117" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445523</v>
+        <v>445418</v>
       </c>
       <c r="R117" t="n">
-        <v>6768362</v>
+        <v>6768439</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723453</v>
+        <v>127723530</v>
       </c>
       <c r="B118" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445418</v>
+        <v>445515</v>
       </c>
       <c r="R118" t="n">
-        <v>6768439</v>
+        <v>6768378</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723410</v>
+        <v>127722831</v>
       </c>
       <c r="B119" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445434</v>
+        <v>445370</v>
       </c>
       <c r="R119" t="n">
-        <v>6768336</v>
+        <v>6768425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,10 +12231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723503</v>
+        <v>127723410</v>
       </c>
       <c r="B120" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445439</v>
+        <v>445434</v>
       </c>
       <c r="R120" t="n">
-        <v>6768381</v>
+        <v>6768336</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722831</v>
+        <v>127723503</v>
       </c>
       <c r="B121" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12339,21 +12339,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445370</v>
+        <v>445439</v>
       </c>
       <c r="R121" t="n">
-        <v>6768425</v>
+        <v>6768381</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12428,7 +12428,7 @@
         <v>127723443</v>
       </c>
       <c r="B122" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>127723505</v>
       </c>
       <c r="B123" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>127723438</v>
       </c>
       <c r="B124" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723518</v>
+        <v>127723479</v>
       </c>
       <c r="B2" t="n">
         <v>79020</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445431</v>
+        <v>445309</v>
       </c>
       <c r="R2" t="n">
-        <v>6768443</v>
+        <v>6768491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723434</v>
+        <v>127723421</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445345</v>
+        <v>445361</v>
       </c>
       <c r="R3" t="n">
-        <v>6768366</v>
+        <v>6768495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723480</v>
+        <v>127723531</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445314</v>
+        <v>445524</v>
       </c>
       <c r="R4" t="n">
-        <v>6768485</v>
+        <v>6768371</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723421</v>
+        <v>127723480</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445314</v>
       </c>
       <c r="R5" t="n">
-        <v>6768495</v>
+        <v>6768485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723416</v>
+        <v>127723434</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445426</v>
+        <v>445345</v>
       </c>
       <c r="R6" t="n">
-        <v>6768417</v>
+        <v>6768366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723493</v>
+        <v>127723518</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445363</v>
+        <v>445431</v>
       </c>
       <c r="R7" t="n">
-        <v>6768410</v>
+        <v>6768443</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723531</v>
+        <v>127723416</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445524</v>
+        <v>445426</v>
       </c>
       <c r="R8" t="n">
-        <v>6768371</v>
+        <v>6768417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723424</v>
+        <v>127723493</v>
       </c>
       <c r="B9" t="n">
         <v>79020</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445311</v>
+        <v>445363</v>
       </c>
       <c r="R9" t="n">
-        <v>6768500</v>
+        <v>6768410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127722873</v>
+        <v>127723424</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,39 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445364</v>
+        <v>445311</v>
       </c>
       <c r="R10" t="n">
-        <v>6768295</v>
+        <v>6768500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723479</v>
+        <v>127722873</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1559,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445309</v>
+        <v>445364</v>
       </c>
       <c r="R11" t="n">
-        <v>6768491</v>
+        <v>6768295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R14" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R15" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723520</v>
+        <v>127723442</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445439</v>
+        <v>445407</v>
       </c>
       <c r="R17" t="n">
-        <v>6768423</v>
+        <v>6768295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723517</v>
+        <v>127723435</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445463</v>
+        <v>445375</v>
       </c>
       <c r="R18" t="n">
-        <v>6768439</v>
+        <v>6768348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R19" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723442</v>
+        <v>127723520</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445407</v>
+        <v>445439</v>
       </c>
       <c r="R20" t="n">
-        <v>6768295</v>
+        <v>6768423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R22" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723417</v>
+        <v>127723527</v>
       </c>
       <c r="B23" t="n">
         <v>79020</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445413</v>
+        <v>445476</v>
       </c>
       <c r="R23" t="n">
-        <v>6768451</v>
+        <v>6768382</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723525</v>
+        <v>127723417</v>
       </c>
       <c r="B24" t="n">
         <v>79020</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445465</v>
+        <v>445413</v>
       </c>
       <c r="R24" t="n">
-        <v>6768379</v>
+        <v>6768451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723527</v>
+        <v>127723412</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445476</v>
+        <v>445423</v>
       </c>
       <c r="R25" t="n">
-        <v>6768382</v>
+        <v>6768342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,7 +3105,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723487</v>
+        <v>127723538</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445328</v>
+        <v>445485</v>
       </c>
       <c r="R27" t="n">
-        <v>6768445</v>
+        <v>6768313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723529</v>
+        <v>127723428</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445507</v>
+        <v>445329</v>
       </c>
       <c r="R29" t="n">
-        <v>6768383</v>
+        <v>6768465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3396,7 +3396,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723538</v>
+        <v>127723487</v>
       </c>
       <c r="B30" t="n">
         <v>79020</v>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445485</v>
+        <v>445328</v>
       </c>
       <c r="R30" t="n">
-        <v>6768313</v>
+        <v>6768445</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,7 +3493,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723428</v>
+        <v>127723529</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445329</v>
+        <v>445507</v>
       </c>
       <c r="R31" t="n">
-        <v>6768465</v>
+        <v>6768383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3590,38 +3590,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723028</v>
+        <v>127722895</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445345</v>
+        <v>445370</v>
       </c>
       <c r="R32" t="n">
-        <v>6768382</v>
+        <v>6768276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3692,38 +3692,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722895</v>
+        <v>127723028</v>
       </c>
       <c r="B33" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445370</v>
+        <v>445345</v>
       </c>
       <c r="R33" t="n">
-        <v>6768276</v>
+        <v>6768382</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723482</v>
+        <v>127723515</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445318</v>
+        <v>445465</v>
       </c>
       <c r="R35" t="n">
-        <v>6768474</v>
+        <v>6768438</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723515</v>
+        <v>127723482</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445465</v>
+        <v>445318</v>
       </c>
       <c r="R36" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723431</v>
+        <v>127723446</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445369</v>
+        <v>445453</v>
       </c>
       <c r="R37" t="n">
-        <v>6768408</v>
+        <v>6768321</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723431</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445369</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768408</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723446</v>
+        <v>127723536</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445453</v>
+        <v>445500</v>
       </c>
       <c r="R39" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4376,7 +4376,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723422</v>
+        <v>127723418</v>
       </c>
       <c r="B40" t="n">
         <v>79020</v>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445332</v>
+        <v>445411</v>
       </c>
       <c r="R40" t="n">
-        <v>6768518</v>
+        <v>6768470</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723565</v>
+        <v>127723427</v>
       </c>
       <c r="B41" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445406</v>
+        <v>445322</v>
       </c>
       <c r="R41" t="n">
-        <v>6768484</v>
+        <v>6768457</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4544,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723427</v>
+        <v>127723565</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445322</v>
+        <v>445406</v>
       </c>
       <c r="R42" t="n">
-        <v>6768457</v>
+        <v>6768484</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723418</v>
+        <v>127723422</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445411</v>
+        <v>445332</v>
       </c>
       <c r="R43" t="n">
-        <v>6768470</v>
+        <v>6768518</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723534</v>
+        <v>127723604</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445528</v>
+        <v>445370</v>
       </c>
       <c r="R44" t="n">
-        <v>6768349</v>
+        <v>6768425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723521</v>
+        <v>127723592</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445445</v>
+        <v>445370</v>
       </c>
       <c r="R45" t="n">
-        <v>6768409</v>
+        <v>6768478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4963,50 +4963,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723025</v>
+        <v>127723521</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445397</v>
+        <v>445445</v>
       </c>
       <c r="R46" t="n">
-        <v>6768481</v>
+        <v>6768409</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,12 +5028,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5065,50 +5060,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723026</v>
+        <v>127723534</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445387</v>
+        <v>445528</v>
       </c>
       <c r="R47" t="n">
-        <v>6768492</v>
+        <v>6768349</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5135,12 +5125,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5167,45 +5157,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723604</v>
+        <v>127723025</v>
       </c>
       <c r="B48" t="n">
-        <v>78687</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R48" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5232,12 +5227,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5264,45 +5259,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723592</v>
+        <v>127723026</v>
       </c>
       <c r="B49" t="n">
-        <v>78687</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445370</v>
+        <v>445387</v>
       </c>
       <c r="R49" t="n">
-        <v>6768478</v>
+        <v>6768492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722889</v>
+        <v>127723425</v>
       </c>
       <c r="B52" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,39 +5566,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445372</v>
+        <v>445321</v>
       </c>
       <c r="R52" t="n">
-        <v>6768323</v>
+        <v>6768501</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5657,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723444</v>
+        <v>127723430</v>
       </c>
       <c r="B53" t="n">
         <v>79020</v>
@@ -5692,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445432</v>
+        <v>445357</v>
       </c>
       <c r="R53" t="n">
-        <v>6768299</v>
+        <v>6768451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5754,7 +5749,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723430</v>
+        <v>127723444</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -5789,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445357</v>
+        <v>445432</v>
       </c>
       <c r="R54" t="n">
-        <v>6768451</v>
+        <v>6768299</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5851,7 +5846,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723425</v>
+        <v>127723524</v>
       </c>
       <c r="B55" t="n">
         <v>79020</v>
@@ -5886,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445321</v>
+        <v>445455</v>
       </c>
       <c r="R55" t="n">
-        <v>6768501</v>
+        <v>6768391</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5916,12 +5911,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5948,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723524</v>
+        <v>127722889</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5959,34 +5954,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445455</v>
+        <v>445372</v>
       </c>
       <c r="R56" t="n">
-        <v>6768391</v>
+        <v>6768323</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6013,12 +6013,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6142,7 +6142,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723526</v>
+        <v>127723492</v>
       </c>
       <c r="B58" t="n">
         <v>79020</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445468</v>
+        <v>445366</v>
       </c>
       <c r="R58" t="n">
-        <v>6768377</v>
+        <v>6768409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723499</v>
+        <v>127723526</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445418</v>
+        <v>445468</v>
       </c>
       <c r="R59" t="n">
-        <v>6768394</v>
+        <v>6768377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723492</v>
+        <v>127723499</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445366</v>
+        <v>445418</v>
       </c>
       <c r="R60" t="n">
-        <v>6768409</v>
+        <v>6768394</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723413</v>
+        <v>127722872</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,34 +6541,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445444</v>
+        <v>445414</v>
       </c>
       <c r="R62" t="n">
-        <v>6768341</v>
+        <v>6768450</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6627,10 +6632,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B63" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,39 +6643,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R63" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6703,11 +6703,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6734,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722872</v>
+        <v>127722914</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6745,27 +6740,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445325</v>
       </c>
       <c r="R64" t="n">
-        <v>6768450</v>
+        <v>6768463</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6810,6 +6805,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6836,7 +6836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723506</v>
+        <v>127723519</v>
       </c>
       <c r="B65" t="n">
         <v>79020</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445509</v>
+        <v>445434</v>
       </c>
       <c r="R65" t="n">
-        <v>6768424</v>
+        <v>6768437</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723511</v>
+        <v>127723496</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445497</v>
+        <v>445376</v>
       </c>
       <c r="R66" t="n">
-        <v>6768438</v>
+        <v>6768426</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723514</v>
+        <v>127723506</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445468</v>
+        <v>445509</v>
       </c>
       <c r="R67" t="n">
-        <v>6768439</v>
+        <v>6768424</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B68" t="n">
         <v>79020</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R68" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7192,12 +7192,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7224,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723489</v>
+        <v>127723439</v>
       </c>
       <c r="B69" t="n">
         <v>79020</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445349</v>
+        <v>445382</v>
       </c>
       <c r="R69" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7418,7 +7418,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723522</v>
+        <v>127723528</v>
       </c>
       <c r="B71" t="n">
         <v>79020</v>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445457</v>
+        <v>445493</v>
       </c>
       <c r="R71" t="n">
-        <v>6768411</v>
+        <v>6768388</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723519</v>
+        <v>127723522</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445434</v>
+        <v>445457</v>
       </c>
       <c r="R72" t="n">
-        <v>6768437</v>
+        <v>6768411</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723496</v>
+        <v>127723511</v>
       </c>
       <c r="B73" t="n">
         <v>79020</v>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445376</v>
+        <v>445497</v>
       </c>
       <c r="R73" t="n">
-        <v>6768426</v>
+        <v>6768438</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,45 +7709,50 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723528</v>
+        <v>127723034</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445493</v>
+        <v>445377</v>
       </c>
       <c r="R74" t="n">
-        <v>6768388</v>
+        <v>6768394</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7806,10 +7811,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722917</v>
+        <v>127723514</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,39 +7822,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445329</v>
+        <v>445468</v>
       </c>
       <c r="R75" t="n">
-        <v>6768466</v>
+        <v>6768439</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,17 +7876,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7913,7 +7908,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722908</v>
+        <v>127722917</v>
       </c>
       <c r="B76" t="n">
         <v>57663</v>
@@ -7956,7 +7951,7 @@
         <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768474</v>
+        <v>6768466</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7993,7 +7988,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack (tall)</t>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8020,38 +8015,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723034</v>
+        <v>127722908</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8060,10 +8055,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445377</v>
+        <v>445329</v>
       </c>
       <c r="R77" t="n">
-        <v>6768394</v>
+        <v>6768474</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8090,12 +8085,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8316,7 +8316,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723411</v>
+        <v>127723420</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445410</v>
+        <v>445395</v>
       </c>
       <c r="R80" t="n">
-        <v>6768338</v>
+        <v>6768485</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723537</v>
+        <v>127723423</v>
       </c>
       <c r="B82" t="n">
         <v>79020</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445488</v>
+        <v>445325</v>
       </c>
       <c r="R82" t="n">
-        <v>6768315</v>
+        <v>6768515</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8704,7 +8704,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723432</v>
+        <v>127723537</v>
       </c>
       <c r="B84" t="n">
         <v>79020</v>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445360</v>
+        <v>445488</v>
       </c>
       <c r="R84" t="n">
-        <v>6768399</v>
+        <v>6768315</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723423</v>
+        <v>127723432</v>
       </c>
       <c r="B85" t="n">
         <v>79020</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445325</v>
+        <v>445360</v>
       </c>
       <c r="R85" t="n">
-        <v>6768515</v>
+        <v>6768399</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8898,7 +8898,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723420</v>
+        <v>127723411</v>
       </c>
       <c r="B86" t="n">
         <v>79020</v>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445395</v>
+        <v>445410</v>
       </c>
       <c r="R86" t="n">
-        <v>6768485</v>
+        <v>6768338</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9398,50 +9398,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723029</v>
+        <v>127723504</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445351</v>
+        <v>445449</v>
       </c>
       <c r="R91" t="n">
-        <v>6768348</v>
+        <v>6768387</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9468,12 +9463,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9597,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723436</v>
+        <v>127723426</v>
       </c>
       <c r="B93" t="n">
         <v>79020</v>
@@ -9632,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445366</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6768321</v>
+        <v>6768470</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9694,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723426</v>
+        <v>127723436</v>
       </c>
       <c r="B94" t="n">
         <v>79020</v>
@@ -9729,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445324</v>
+        <v>445366</v>
       </c>
       <c r="R94" t="n">
-        <v>6768470</v>
+        <v>6768321</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9985,45 +9980,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723504</v>
+        <v>127723029</v>
       </c>
       <c r="B97" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445449</v>
+        <v>445351</v>
       </c>
       <c r="R97" t="n">
-        <v>6768387</v>
+        <v>6768348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10179,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723605</v>
+        <v>127722918</v>
       </c>
       <c r="B99" t="n">
-        <v>78687</v>
+        <v>57663</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10190,34 +10190,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445403</v>
+        <v>445382</v>
       </c>
       <c r="R99" t="n">
-        <v>6768385</v>
+        <v>6768422</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10250,6 +10255,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,45 +10286,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723440</v>
+        <v>127723027</v>
       </c>
       <c r="B100" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445394</v>
+        <v>445343</v>
       </c>
       <c r="R100" t="n">
-        <v>6768290</v>
+        <v>6768460</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10373,10 +10388,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723490</v>
+        <v>127723605</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10384,21 +10399,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10408,10 +10423,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445353</v>
+        <v>445403</v>
       </c>
       <c r="R101" t="n">
-        <v>6768438</v>
+        <v>6768385</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10485,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723447</v>
+        <v>127723454</v>
       </c>
       <c r="B102" t="n">
         <v>79020</v>
@@ -10505,10 +10520,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445458</v>
+        <v>445421</v>
       </c>
       <c r="R102" t="n">
-        <v>6768338</v>
+        <v>6768465</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10550,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,7 +10582,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723535</v>
+        <v>127723447</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10602,10 +10617,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445518</v>
+        <v>445458</v>
       </c>
       <c r="R103" t="n">
-        <v>6768343</v>
+        <v>6768338</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10632,12 +10647,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10664,7 +10679,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723483</v>
+        <v>127723535</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10699,10 +10714,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445310</v>
+        <v>445518</v>
       </c>
       <c r="R104" t="n">
-        <v>6768467</v>
+        <v>6768343</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10761,7 +10776,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723454</v>
+        <v>127723490</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10796,10 +10811,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445421</v>
+        <v>445353</v>
       </c>
       <c r="R105" t="n">
-        <v>6768465</v>
+        <v>6768438</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10858,10 +10873,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127722918</v>
+        <v>127723483</v>
       </c>
       <c r="B106" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10869,39 +10884,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445382</v>
+        <v>445310</v>
       </c>
       <c r="R106" t="n">
-        <v>6768422</v>
+        <v>6768467</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10934,11 +10944,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10965,50 +10970,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127723440</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445394</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768290</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723593</v>
+        <v>127723481</v>
       </c>
       <c r="B108" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,21 +11078,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445417</v>
+        <v>445320</v>
       </c>
       <c r="R108" t="n">
-        <v>6768470</v>
+        <v>6768481</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B109" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11175,21 +11175,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R109" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11229,12 +11229,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723481</v>
+        <v>127723593</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445320</v>
+        <v>445417</v>
       </c>
       <c r="R111" t="n">
-        <v>6768481</v>
+        <v>6768470</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723429</v>
+        <v>127722832</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445339</v>
+        <v>445457</v>
       </c>
       <c r="R112" t="n">
-        <v>6768457</v>
+        <v>6768397</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11649,7 +11649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723498</v>
+        <v>127723453</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445386</v>
+        <v>445418</v>
       </c>
       <c r="R114" t="n">
-        <v>6768393</v>
+        <v>6768439</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11843,7 +11843,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723532</v>
+        <v>127723498</v>
       </c>
       <c r="B116" t="n">
         <v>79020</v>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445523</v>
+        <v>445386</v>
       </c>
       <c r="R116" t="n">
-        <v>6768362</v>
+        <v>6768393</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723453</v>
+        <v>127723530</v>
       </c>
       <c r="B117" t="n">
         <v>79020</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445418</v>
+        <v>445515</v>
       </c>
       <c r="R117" t="n">
-        <v>6768439</v>
+        <v>6768378</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B118" t="n">
         <v>79020</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R118" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127722831</v>
+        <v>127723443</v>
       </c>
       <c r="B119" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445370</v>
+        <v>445422</v>
       </c>
       <c r="R119" t="n">
-        <v>6768425</v>
+        <v>6768295</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723410</v>
+        <v>127723503</v>
       </c>
       <c r="B120" t="n">
         <v>79020</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445434</v>
+        <v>445439</v>
       </c>
       <c r="R120" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,7 +12328,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723503</v>
+        <v>127723410</v>
       </c>
       <c r="B121" t="n">
         <v>79020</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445439</v>
+        <v>445434</v>
       </c>
       <c r="R121" t="n">
-        <v>6768381</v>
+        <v>6768336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723443</v>
+        <v>127723505</v>
       </c>
       <c r="B122" t="n">
         <v>79020</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445422</v>
+        <v>445493</v>
       </c>
       <c r="R122" t="n">
-        <v>6768295</v>
+        <v>6768418</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723505</v>
+        <v>127723438</v>
       </c>
       <c r="B123" t="n">
         <v>79020</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445493</v>
+        <v>445375</v>
       </c>
       <c r="R123" t="n">
-        <v>6768418</v>
+        <v>6768277</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723438</v>
+        <v>127722831</v>
       </c>
       <c r="B124" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445375</v>
+        <v>445370</v>
       </c>
       <c r="R124" t="n">
-        <v>6768277</v>
+        <v>6768425</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723480</v>
+        <v>127723424</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445314</v>
+        <v>445311</v>
       </c>
       <c r="R5" t="n">
-        <v>6768485</v>
+        <v>6768500</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723424</v>
+        <v>127723480</v>
       </c>
       <c r="B10" t="n">
         <v>79020</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445311</v>
+        <v>445314</v>
       </c>
       <c r="R10" t="n">
-        <v>6768500</v>
+        <v>6768485</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723529</v>
+        <v>127722895</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,34 +3504,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445507</v>
+        <v>445370</v>
       </c>
       <c r="R31" t="n">
-        <v>6768383</v>
+        <v>6768276</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3558,12 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3590,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722895</v>
+        <v>127723529</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,39 +3606,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445370</v>
+        <v>445507</v>
       </c>
       <c r="R32" t="n">
-        <v>6768276</v>
+        <v>6768383</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5060,45 +5060,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723534</v>
+        <v>127723025</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445528</v>
+        <v>445397</v>
       </c>
       <c r="R47" t="n">
-        <v>6768349</v>
+        <v>6768481</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5125,12 +5130,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5157,7 +5162,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723025</v>
+        <v>127723026</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5197,10 +5202,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445397</v>
+        <v>445387</v>
       </c>
       <c r="R48" t="n">
-        <v>6768481</v>
+        <v>6768492</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5259,50 +5264,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723026</v>
+        <v>127723534</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445387</v>
+        <v>445528</v>
       </c>
       <c r="R49" t="n">
-        <v>6768492</v>
+        <v>6768349</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6836,45 +6836,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723519</v>
+        <v>127723034</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445434</v>
+        <v>445377</v>
       </c>
       <c r="R65" t="n">
-        <v>6768437</v>
+        <v>6768394</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6933,7 +6938,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723496</v>
+        <v>127723519</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -6968,10 +6973,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445376</v>
+        <v>445434</v>
       </c>
       <c r="R66" t="n">
-        <v>6768426</v>
+        <v>6768437</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7035,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723506</v>
+        <v>127723496</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7065,10 +7070,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445509</v>
+        <v>445376</v>
       </c>
       <c r="R67" t="n">
-        <v>6768424</v>
+        <v>6768426</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7132,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723489</v>
+        <v>127723506</v>
       </c>
       <c r="B68" t="n">
         <v>79020</v>
@@ -7162,10 +7167,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445349</v>
+        <v>445509</v>
       </c>
       <c r="R68" t="n">
-        <v>6768438</v>
+        <v>6768424</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7229,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B69" t="n">
         <v>79020</v>
@@ -7259,10 +7264,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R69" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7294,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7321,7 +7326,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723455</v>
+        <v>127723439</v>
       </c>
       <c r="B70" t="n">
         <v>79020</v>
@@ -7356,10 +7361,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445417</v>
+        <v>445382</v>
       </c>
       <c r="R70" t="n">
-        <v>6768483</v>
+        <v>6768296</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7386,12 +7391,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7418,7 +7423,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723528</v>
+        <v>127723455</v>
       </c>
       <c r="B71" t="n">
         <v>79020</v>
@@ -7453,10 +7458,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445493</v>
+        <v>445417</v>
       </c>
       <c r="R71" t="n">
-        <v>6768388</v>
+        <v>6768483</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7515,7 +7520,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723522</v>
+        <v>127723528</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -7550,10 +7555,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445457</v>
+        <v>445493</v>
       </c>
       <c r="R72" t="n">
-        <v>6768411</v>
+        <v>6768388</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,10 +7617,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723511</v>
+        <v>127722917</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7623,34 +7628,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445497</v>
+        <v>445329</v>
       </c>
       <c r="R73" t="n">
-        <v>6768438</v>
+        <v>6768466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7677,12 +7687,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7709,38 +7724,38 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723034</v>
+        <v>127722908</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -7749,10 +7764,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445377</v>
+        <v>445329</v>
       </c>
       <c r="R74" t="n">
-        <v>6768394</v>
+        <v>6768474</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7779,12 +7794,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7811,7 +7831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723514</v>
+        <v>127723522</v>
       </c>
       <c r="B75" t="n">
         <v>79020</v>
@@ -7846,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445468</v>
+        <v>445457</v>
       </c>
       <c r="R75" t="n">
-        <v>6768439</v>
+        <v>6768411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7908,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722917</v>
+        <v>127723511</v>
       </c>
       <c r="B76" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7919,39 +7939,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445329</v>
+        <v>445497</v>
       </c>
       <c r="R76" t="n">
-        <v>6768466</v>
+        <v>6768438</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7978,17 +7993,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8015,10 +8025,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127722908</v>
+        <v>127723514</v>
       </c>
       <c r="B77" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8026,39 +8036,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445329</v>
+        <v>445468</v>
       </c>
       <c r="R77" t="n">
-        <v>6768474</v>
+        <v>6768439</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8085,17 +8090,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127722864</v>
+        <v>127723605</v>
       </c>
       <c r="B98" t="n">
-        <v>91332</v>
+        <v>78687</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445327</v>
+        <v>445403</v>
       </c>
       <c r="R98" t="n">
-        <v>6768444</v>
+        <v>6768385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10286,50 +10286,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723027</v>
+        <v>127722864</v>
       </c>
       <c r="B100" t="n">
-        <v>8450</v>
+        <v>91332</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445343</v>
+        <v>445327</v>
       </c>
       <c r="R100" t="n">
-        <v>6768460</v>
+        <v>6768444</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10356,12 +10351,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10388,10 +10383,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723605</v>
+        <v>127723454</v>
       </c>
       <c r="B101" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10399,21 +10394,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10423,10 +10418,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445403</v>
+        <v>445421</v>
       </c>
       <c r="R101" t="n">
-        <v>6768385</v>
+        <v>6768465</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10485,7 +10480,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723454</v>
+        <v>127723447</v>
       </c>
       <c r="B102" t="n">
         <v>79020</v>
@@ -10520,10 +10515,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445421</v>
+        <v>445458</v>
       </c>
       <c r="R102" t="n">
-        <v>6768465</v>
+        <v>6768338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10550,12 +10545,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10582,7 +10577,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723447</v>
+        <v>127723535</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10617,10 +10612,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445458</v>
+        <v>445518</v>
       </c>
       <c r="R103" t="n">
-        <v>6768338</v>
+        <v>6768343</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10647,12 +10642,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10679,7 +10674,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723535</v>
+        <v>127723490</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10714,10 +10709,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445518</v>
+        <v>445353</v>
       </c>
       <c r="R104" t="n">
-        <v>6768343</v>
+        <v>6768438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10776,7 +10771,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723490</v>
+        <v>127723483</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10811,10 +10806,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445353</v>
+        <v>445310</v>
       </c>
       <c r="R105" t="n">
-        <v>6768438</v>
+        <v>6768467</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10873,7 +10868,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723483</v>
+        <v>127723440</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -10908,10 +10903,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445310</v>
+        <v>445394</v>
       </c>
       <c r="R106" t="n">
-        <v>6768467</v>
+        <v>6768290</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10938,12 +10933,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10970,45 +10965,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723440</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445394</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768290</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723481</v>
+        <v>127723593</v>
       </c>
       <c r="B108" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,21 +11078,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445320</v>
+        <v>445417</v>
       </c>
       <c r="R108" t="n">
-        <v>6768481</v>
+        <v>6768470</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,7 +11164,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723429</v>
+        <v>127723481</v>
       </c>
       <c r="B109" t="n">
         <v>79020</v>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445339</v>
+        <v>445320</v>
       </c>
       <c r="R109" t="n">
-        <v>6768457</v>
+        <v>6768481</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11229,12 +11229,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11261,7 +11261,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723495</v>
+        <v>127723429</v>
       </c>
       <c r="B110" t="n">
         <v>79020</v>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445361</v>
+        <v>445339</v>
       </c>
       <c r="R110" t="n">
-        <v>6768425</v>
+        <v>6768457</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723593</v>
+        <v>127723495</v>
       </c>
       <c r="B111" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445417</v>
+        <v>445361</v>
       </c>
       <c r="R111" t="n">
-        <v>6768470</v>
+        <v>6768425</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723479</v>
+        <v>127723421</v>
       </c>
       <c r="B2" t="n">
         <v>79020</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445309</v>
+        <v>445361</v>
       </c>
       <c r="R2" t="n">
-        <v>6768491</v>
+        <v>6768495</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723421</v>
+        <v>127723531</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445361</v>
+        <v>445524</v>
       </c>
       <c r="R3" t="n">
-        <v>6768495</v>
+        <v>6768371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723531</v>
+        <v>127723434</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445524</v>
+        <v>445345</v>
       </c>
       <c r="R4" t="n">
-        <v>6768371</v>
+        <v>6768366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723424</v>
+        <v>127723416</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445311</v>
+        <v>445426</v>
       </c>
       <c r="R5" t="n">
-        <v>6768500</v>
+        <v>6768417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723434</v>
+        <v>127723479</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445345</v>
+        <v>445309</v>
       </c>
       <c r="R6" t="n">
-        <v>6768366</v>
+        <v>6768491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723518</v>
+        <v>127723424</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445431</v>
+        <v>445311</v>
       </c>
       <c r="R7" t="n">
-        <v>6768443</v>
+        <v>6768500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723416</v>
+        <v>127722873</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445426</v>
+        <v>445364</v>
       </c>
       <c r="R8" t="n">
-        <v>6768417</v>
+        <v>6768295</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723493</v>
+        <v>127723518</v>
       </c>
       <c r="B9" t="n">
         <v>79020</v>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445363</v>
+        <v>445431</v>
       </c>
       <c r="R9" t="n">
-        <v>6768410</v>
+        <v>6768443</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127722873</v>
+        <v>127723493</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445364</v>
+        <v>445363</v>
       </c>
       <c r="R11" t="n">
-        <v>6768295</v>
+        <v>6768410</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723602</v>
+        <v>127723606</v>
       </c>
       <c r="B12" t="n">
         <v>78687</v>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445339</v>
+        <v>445475</v>
       </c>
       <c r="R12" t="n">
-        <v>6768436</v>
+        <v>6768378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,7 +1747,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723606</v>
+        <v>127723602</v>
       </c>
       <c r="B13" t="n">
         <v>78687</v>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445475</v>
+        <v>445339</v>
       </c>
       <c r="R13" t="n">
-        <v>6768378</v>
+        <v>6768436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R14" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B15" t="n">
         <v>79020</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R15" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723442</v>
+        <v>127723435</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445407</v>
+        <v>445375</v>
       </c>
       <c r="R17" t="n">
-        <v>6768295</v>
+        <v>6768348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723435</v>
+        <v>127723520</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R18" t="n">
-        <v>6768348</v>
+        <v>6768423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723520</v>
+        <v>127723442</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445439</v>
+        <v>445407</v>
       </c>
       <c r="R20" t="n">
-        <v>6768423</v>
+        <v>6768295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723525</v>
+        <v>127723527</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445465</v>
+        <v>445476</v>
       </c>
       <c r="R22" t="n">
-        <v>6768379</v>
+        <v>6768382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723527</v>
+        <v>127723433</v>
       </c>
       <c r="B23" t="n">
         <v>79020</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445476</v>
+        <v>445354</v>
       </c>
       <c r="R23" t="n">
-        <v>6768382</v>
+        <v>6768399</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R25" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723433</v>
+        <v>127723412</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445354</v>
+        <v>445423</v>
       </c>
       <c r="R26" t="n">
-        <v>6768399</v>
+        <v>6768342</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723538</v>
+        <v>127723428</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445485</v>
+        <v>445329</v>
       </c>
       <c r="R27" t="n">
-        <v>6768313</v>
+        <v>6768465</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3202,45 +3202,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723523</v>
+        <v>127723028</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445451</v>
+        <v>445345</v>
       </c>
       <c r="R28" t="n">
-        <v>6768402</v>
+        <v>6768382</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3267,12 +3272,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3299,7 +3304,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723428</v>
+        <v>127723538</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3334,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445329</v>
+        <v>445485</v>
       </c>
       <c r="R29" t="n">
-        <v>6768465</v>
+        <v>6768313</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3364,12 +3369,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3493,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127722895</v>
+        <v>127723523</v>
       </c>
       <c r="B31" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3504,39 +3509,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445370</v>
+        <v>445451</v>
       </c>
       <c r="R31" t="n">
-        <v>6768276</v>
+        <v>6768402</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3692,38 +3692,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723028</v>
+        <v>127722895</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445345</v>
+        <v>445370</v>
       </c>
       <c r="R33" t="n">
-        <v>6768382</v>
+        <v>6768276</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723482</v>
+        <v>127723431</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445318</v>
+        <v>445369</v>
       </c>
       <c r="R36" t="n">
-        <v>6768474</v>
+        <v>6768408</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723446</v>
+        <v>127723482</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445453</v>
+        <v>445318</v>
       </c>
       <c r="R37" t="n">
-        <v>6768321</v>
+        <v>6768474</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723431</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445369</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768408</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723536</v>
+        <v>127723446</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445500</v>
+        <v>445453</v>
       </c>
       <c r="R39" t="n">
-        <v>6768348</v>
+        <v>6768321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723427</v>
+        <v>127723565</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445322</v>
+        <v>445406</v>
       </c>
       <c r="R41" t="n">
-        <v>6768457</v>
+        <v>6768484</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4570,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723565</v>
+        <v>127723422</v>
       </c>
       <c r="B42" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445406</v>
+        <v>445332</v>
       </c>
       <c r="R42" t="n">
-        <v>6768484</v>
+        <v>6768518</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723422</v>
+        <v>127723427</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445332</v>
+        <v>445322</v>
       </c>
       <c r="R43" t="n">
-        <v>6768518</v>
+        <v>6768457</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723604</v>
+        <v>127723592</v>
       </c>
       <c r="B44" t="n">
         <v>78687</v>
@@ -4807,7 +4807,7 @@
         <v>445370</v>
       </c>
       <c r="R44" t="n">
-        <v>6768425</v>
+        <v>6768478</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4834,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,7 +4866,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723592</v>
+        <v>127723604</v>
       </c>
       <c r="B45" t="n">
         <v>78687</v>
@@ -4904,7 +4904,7 @@
         <v>445370</v>
       </c>
       <c r="R45" t="n">
-        <v>6768478</v>
+        <v>6768425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4963,7 +4963,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723521</v>
+        <v>127723534</v>
       </c>
       <c r="B46" t="n">
         <v>79020</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445445</v>
+        <v>445528</v>
       </c>
       <c r="R46" t="n">
-        <v>6768409</v>
+        <v>6768349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,50 +5060,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723025</v>
+        <v>127723521</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445397</v>
+        <v>445445</v>
       </c>
       <c r="R47" t="n">
-        <v>6768481</v>
+        <v>6768409</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5130,12 +5125,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5162,7 +5157,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723026</v>
+        <v>127723025</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5202,10 +5197,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445387</v>
+        <v>445397</v>
       </c>
       <c r="R48" t="n">
-        <v>6768492</v>
+        <v>6768481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,45 +5259,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723534</v>
+        <v>127723026</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445528</v>
+        <v>445387</v>
       </c>
       <c r="R49" t="n">
-        <v>6768349</v>
+        <v>6768492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5555,7 +5555,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723425</v>
+        <v>127723430</v>
       </c>
       <c r="B52" t="n">
         <v>79020</v>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445321</v>
+        <v>445357</v>
       </c>
       <c r="R52" t="n">
-        <v>6768501</v>
+        <v>6768451</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127723444</v>
       </c>
       <c r="B53" t="n">
         <v>79020</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445432</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768299</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,7 +5749,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723444</v>
+        <v>127723425</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445432</v>
+        <v>445321</v>
       </c>
       <c r="R54" t="n">
-        <v>6768299</v>
+        <v>6768501</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5943,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722889</v>
+        <v>127722829</v>
       </c>
       <c r="B56" t="n">
-        <v>57660</v>
+        <v>79638</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5954,39 +5954,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445372</v>
+        <v>445339</v>
       </c>
       <c r="R56" t="n">
-        <v>6768323</v>
+        <v>6768436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6013,12 +6008,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6045,10 +6040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722829</v>
+        <v>127722889</v>
       </c>
       <c r="B57" t="n">
-        <v>79638</v>
+        <v>57660</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,34 +6051,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445339</v>
+        <v>445372</v>
       </c>
       <c r="R57" t="n">
-        <v>6768436</v>
+        <v>6768323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723526</v>
+        <v>127723488</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445468</v>
+        <v>445340</v>
       </c>
       <c r="R59" t="n">
-        <v>6768377</v>
+        <v>6768445</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723499</v>
+        <v>127723526</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445418</v>
+        <v>445468</v>
       </c>
       <c r="R60" t="n">
-        <v>6768394</v>
+        <v>6768377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723488</v>
+        <v>127723499</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445340</v>
+        <v>445418</v>
       </c>
       <c r="R61" t="n">
-        <v>6768445</v>
+        <v>6768394</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722872</v>
+        <v>127722914</v>
       </c>
       <c r="B62" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,27 +6541,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445414</v>
+        <v>445325</v>
       </c>
       <c r="R62" t="n">
-        <v>6768450</v>
+        <v>6768463</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,6 +6606,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6729,10 +6734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722914</v>
+        <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,27 +6745,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6769,10 +6774,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445325</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6768463</v>
+        <v>6768450</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6805,11 +6810,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6836,50 +6836,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723034</v>
+        <v>127723514</v>
       </c>
       <c r="B65" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445377</v>
+        <v>445468</v>
       </c>
       <c r="R65" t="n">
-        <v>6768394</v>
+        <v>6768439</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6938,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723519</v>
+        <v>127723455</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -6973,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445434</v>
+        <v>445417</v>
       </c>
       <c r="R66" t="n">
-        <v>6768437</v>
+        <v>6768483</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7035,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723496</v>
+        <v>127723511</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7070,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445376</v>
+        <v>445497</v>
       </c>
       <c r="R67" t="n">
-        <v>6768426</v>
+        <v>6768438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7132,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723506</v>
+        <v>127723528</v>
       </c>
       <c r="B68" t="n">
         <v>79020</v>
@@ -7167,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445509</v>
+        <v>445493</v>
       </c>
       <c r="R68" t="n">
-        <v>6768424</v>
+        <v>6768388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7229,10 +7224,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723489</v>
+        <v>127722917</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7240,34 +7235,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445349</v>
+        <v>445329</v>
       </c>
       <c r="R69" t="n">
-        <v>6768438</v>
+        <v>6768466</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7294,12 +7294,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7326,10 +7331,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723439</v>
+        <v>127722908</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7337,34 +7342,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445382</v>
+        <v>445329</v>
       </c>
       <c r="R70" t="n">
-        <v>6768296</v>
+        <v>6768474</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7397,6 +7407,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7423,45 +7438,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723455</v>
+        <v>127723034</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445417</v>
+        <v>445377</v>
       </c>
       <c r="R71" t="n">
-        <v>6768483</v>
+        <v>6768394</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7520,7 +7540,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723528</v>
+        <v>127723496</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -7555,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445493</v>
+        <v>445376</v>
       </c>
       <c r="R72" t="n">
-        <v>6768388</v>
+        <v>6768426</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7617,10 +7637,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127722917</v>
+        <v>127723489</v>
       </c>
       <c r="B73" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7628,39 +7648,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445329</v>
+        <v>445349</v>
       </c>
       <c r="R73" t="n">
-        <v>6768466</v>
+        <v>6768438</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7687,17 +7702,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7724,10 +7734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127722908</v>
+        <v>127723522</v>
       </c>
       <c r="B74" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7735,39 +7745,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445329</v>
+        <v>445457</v>
       </c>
       <c r="R74" t="n">
-        <v>6768474</v>
+        <v>6768411</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7794,17 +7799,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7831,7 +7831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723522</v>
+        <v>127723439</v>
       </c>
       <c r="B75" t="n">
         <v>79020</v>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445457</v>
+        <v>445382</v>
       </c>
       <c r="R75" t="n">
-        <v>6768411</v>
+        <v>6768296</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7896,12 +7896,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7928,7 +7928,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723511</v>
+        <v>127723506</v>
       </c>
       <c r="B76" t="n">
         <v>79020</v>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445497</v>
+        <v>445509</v>
       </c>
       <c r="R76" t="n">
-        <v>6768438</v>
+        <v>6768424</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723514</v>
+        <v>127723519</v>
       </c>
       <c r="B77" t="n">
         <v>79020</v>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445468</v>
+        <v>445434</v>
       </c>
       <c r="R77" t="n">
-        <v>6768439</v>
+        <v>6768437</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,32 +8122,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723560</v>
+        <v>127723423</v>
       </c>
       <c r="B78" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445433</v>
+        <v>445325</v>
       </c>
       <c r="R78" t="n">
-        <v>6768412</v>
+        <v>6768515</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8316,7 +8316,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723420</v>
+        <v>127723494</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445395</v>
+        <v>445355</v>
       </c>
       <c r="R80" t="n">
-        <v>6768485</v>
+        <v>6768420</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8381,12 +8381,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8413,7 +8413,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723494</v>
+        <v>127723420</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445355</v>
+        <v>445395</v>
       </c>
       <c r="R81" t="n">
-        <v>6768420</v>
+        <v>6768485</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8510,10 +8510,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723423</v>
+        <v>127722825</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8521,21 +8521,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445325</v>
+        <v>445386</v>
       </c>
       <c r="R82" t="n">
-        <v>6768515</v>
+        <v>6768493</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8607,45 +8607,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723533</v>
+        <v>127722931</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445523</v>
+        <v>445518</v>
       </c>
       <c r="R83" t="n">
-        <v>6768356</v>
+        <v>6768355</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8672,12 +8677,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,45 +8709,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723537</v>
+        <v>127722930</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445488</v>
+        <v>445390</v>
       </c>
       <c r="R84" t="n">
-        <v>6768315</v>
+        <v>6768381</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,45 +8811,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723432</v>
+        <v>127723030</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445360</v>
+        <v>445376</v>
       </c>
       <c r="R85" t="n">
-        <v>6768399</v>
+        <v>6768336</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8898,32 +8913,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723411</v>
+        <v>127723560</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8933,10 +8948,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445410</v>
+        <v>445433</v>
       </c>
       <c r="R86" t="n">
-        <v>6768338</v>
+        <v>6768412</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8963,12 +8978,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8995,10 +9010,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722825</v>
+        <v>127723432</v>
       </c>
       <c r="B87" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9006,21 +9021,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9030,10 +9045,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445386</v>
+        <v>445360</v>
       </c>
       <c r="R87" t="n">
-        <v>6768493</v>
+        <v>6768399</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9092,50 +9107,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722931</v>
+        <v>127723411</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445518</v>
+        <v>445410</v>
       </c>
       <c r="R88" t="n">
-        <v>6768355</v>
+        <v>6768338</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9194,50 +9204,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722930</v>
+        <v>127723533</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445390</v>
+        <v>445523</v>
       </c>
       <c r="R89" t="n">
-        <v>6768381</v>
+        <v>6768356</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9296,50 +9301,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723030</v>
+        <v>127723537</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445376</v>
+        <v>445488</v>
       </c>
       <c r="R90" t="n">
-        <v>6768336</v>
+        <v>6768315</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723504</v>
+        <v>127723436</v>
       </c>
       <c r="B91" t="n">
         <v>79020</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445449</v>
+        <v>445366</v>
       </c>
       <c r="R91" t="n">
-        <v>6768387</v>
+        <v>6768321</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723426</v>
+        <v>127723497</v>
       </c>
       <c r="B93" t="n">
         <v>79020</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445376</v>
       </c>
       <c r="R93" t="n">
-        <v>6768470</v>
+        <v>6768407</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723436</v>
+        <v>127723426</v>
       </c>
       <c r="B94" t="n">
         <v>79020</v>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445366</v>
+        <v>445324</v>
       </c>
       <c r="R94" t="n">
-        <v>6768321</v>
+        <v>6768470</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723497</v>
+        <v>127723504</v>
       </c>
       <c r="B96" t="n">
         <v>79020</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445376</v>
+        <v>445449</v>
       </c>
       <c r="R96" t="n">
-        <v>6768407</v>
+        <v>6768387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10082,45 +10082,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723605</v>
+        <v>127723027</v>
       </c>
       <c r="B98" t="n">
-        <v>78687</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445403</v>
+        <v>445343</v>
       </c>
       <c r="R98" t="n">
-        <v>6768385</v>
+        <v>6768460</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,12 +10152,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10179,10 +10184,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127722918</v>
+        <v>127723605</v>
       </c>
       <c r="B99" t="n">
-        <v>57663</v>
+        <v>78687</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10190,39 +10195,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445382</v>
+        <v>445403</v>
       </c>
       <c r="R99" t="n">
-        <v>6768422</v>
+        <v>6768385</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10255,11 +10255,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10577,7 +10572,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723535</v>
+        <v>127723490</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10612,10 +10607,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445518</v>
+        <v>445353</v>
       </c>
       <c r="R103" t="n">
-        <v>6768343</v>
+        <v>6768438</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10674,7 +10669,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723490</v>
+        <v>127723483</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10709,10 +10704,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445353</v>
+        <v>445310</v>
       </c>
       <c r="R104" t="n">
-        <v>6768438</v>
+        <v>6768467</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10771,7 +10766,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723483</v>
+        <v>127723440</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10806,10 +10801,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445310</v>
+        <v>445394</v>
       </c>
       <c r="R105" t="n">
-        <v>6768467</v>
+        <v>6768290</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10836,12 +10831,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10868,7 +10863,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723440</v>
+        <v>127723535</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -10903,10 +10898,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445394</v>
+        <v>445518</v>
       </c>
       <c r="R106" t="n">
-        <v>6768290</v>
+        <v>6768343</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10933,12 +10928,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10965,38 +10960,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127722918</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11005,10 +11000,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445382</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768422</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11030,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11649,7 +11649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723453</v>
+        <v>127723441</v>
       </c>
       <c r="B114" t="n">
         <v>79020</v>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445418</v>
+        <v>445408</v>
       </c>
       <c r="R114" t="n">
-        <v>6768439</v>
+        <v>6768287</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11746,7 +11746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723441</v>
+        <v>127723498</v>
       </c>
       <c r="B115" t="n">
         <v>79020</v>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445408</v>
+        <v>445386</v>
       </c>
       <c r="R115" t="n">
-        <v>6768287</v>
+        <v>6768393</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11811,12 +11811,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11843,7 +11843,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723498</v>
+        <v>127723530</v>
       </c>
       <c r="B116" t="n">
         <v>79020</v>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445386</v>
+        <v>445515</v>
       </c>
       <c r="R116" t="n">
-        <v>6768393</v>
+        <v>6768378</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B117" t="n">
         <v>79020</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R117" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723532</v>
+        <v>127723453</v>
       </c>
       <c r="B118" t="n">
         <v>79020</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445523</v>
+        <v>445418</v>
       </c>
       <c r="R118" t="n">
-        <v>6768362</v>
+        <v>6768439</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723443</v>
+        <v>127723505</v>
       </c>
       <c r="B119" t="n">
         <v>79020</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445422</v>
+        <v>445493</v>
       </c>
       <c r="R119" t="n">
-        <v>6768295</v>
+        <v>6768418</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723503</v>
+        <v>127723438</v>
       </c>
       <c r="B120" t="n">
         <v>79020</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445439</v>
+        <v>445375</v>
       </c>
       <c r="R120" t="n">
-        <v>6768381</v>
+        <v>6768277</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723410</v>
+        <v>127722831</v>
       </c>
       <c r="B121" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12339,21 +12339,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445434</v>
+        <v>445370</v>
       </c>
       <c r="R121" t="n">
-        <v>6768336</v>
+        <v>6768425</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723505</v>
+        <v>127723410</v>
       </c>
       <c r="B122" t="n">
         <v>79020</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445493</v>
+        <v>445434</v>
       </c>
       <c r="R122" t="n">
-        <v>6768418</v>
+        <v>6768336</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723438</v>
+        <v>127723503</v>
       </c>
       <c r="B123" t="n">
         <v>79020</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R123" t="n">
-        <v>6768277</v>
+        <v>6768381</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722831</v>
+        <v>127723443</v>
       </c>
       <c r="B124" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445370</v>
+        <v>445422</v>
       </c>
       <c r="R124" t="n">
-        <v>6768425</v>
+        <v>6768295</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723421</v>
+        <v>127723518</v>
       </c>
       <c r="B2" t="n">
         <v>79020</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445361</v>
+        <v>445431</v>
       </c>
       <c r="R2" t="n">
-        <v>6768495</v>
+        <v>6768443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723531</v>
+        <v>127723479</v>
       </c>
       <c r="B3" t="n">
         <v>79020</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445524</v>
+        <v>445309</v>
       </c>
       <c r="R3" t="n">
-        <v>6768371</v>
+        <v>6768491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723434</v>
+        <v>127723416</v>
       </c>
       <c r="B4" t="n">
         <v>79020</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445345</v>
+        <v>445426</v>
       </c>
       <c r="R4" t="n">
-        <v>6768366</v>
+        <v>6768417</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723416</v>
+        <v>127723531</v>
       </c>
       <c r="B5" t="n">
         <v>79020</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445426</v>
+        <v>445524</v>
       </c>
       <c r="R5" t="n">
-        <v>6768417</v>
+        <v>6768371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723479</v>
+        <v>127723424</v>
       </c>
       <c r="B6" t="n">
         <v>79020</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445309</v>
+        <v>445311</v>
       </c>
       <c r="R6" t="n">
-        <v>6768491</v>
+        <v>6768500</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723424</v>
+        <v>127722873</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445311</v>
+        <v>445364</v>
       </c>
       <c r="R7" t="n">
-        <v>6768500</v>
+        <v>6768295</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127722873</v>
+        <v>127723434</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,39 +1273,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445364</v>
+        <v>445345</v>
       </c>
       <c r="R8" t="n">
-        <v>6768295</v>
+        <v>6768366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723518</v>
+        <v>127723480</v>
       </c>
       <c r="B9" t="n">
         <v>79020</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445431</v>
+        <v>445314</v>
       </c>
       <c r="R9" t="n">
-        <v>6768443</v>
+        <v>6768485</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723480</v>
+        <v>127723421</v>
       </c>
       <c r="B10" t="n">
         <v>79020</v>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445314</v>
+        <v>445361</v>
       </c>
       <c r="R10" t="n">
-        <v>6768485</v>
+        <v>6768495</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2041,7 +2041,7 @@
         <v>127723561</v>
       </c>
       <c r="B16" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B17" t="n">
         <v>79020</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R17" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723520</v>
+        <v>127723435</v>
       </c>
       <c r="B18" t="n">
         <v>79020</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445439</v>
+        <v>445375</v>
       </c>
       <c r="R18" t="n">
-        <v>6768423</v>
+        <v>6768348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723517</v>
+        <v>127723442</v>
       </c>
       <c r="B19" t="n">
         <v>79020</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445463</v>
+        <v>445407</v>
       </c>
       <c r="R19" t="n">
-        <v>6768439</v>
+        <v>6768295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723442</v>
+        <v>127723520</v>
       </c>
       <c r="B20" t="n">
         <v>79020</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445407</v>
+        <v>445439</v>
       </c>
       <c r="R20" t="n">
-        <v>6768295</v>
+        <v>6768423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723433</v>
+        <v>127723412</v>
       </c>
       <c r="B23" t="n">
         <v>79020</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445354</v>
+        <v>445423</v>
       </c>
       <c r="R23" t="n">
-        <v>6768399</v>
+        <v>6768342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723525</v>
+        <v>127723433</v>
       </c>
       <c r="B25" t="n">
         <v>79020</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445465</v>
+        <v>445354</v>
       </c>
       <c r="R25" t="n">
-        <v>6768379</v>
+        <v>6768399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B26" t="n">
         <v>79020</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R26" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,7 +3105,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723428</v>
+        <v>127723523</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445329</v>
+        <v>445451</v>
       </c>
       <c r="R27" t="n">
-        <v>6768465</v>
+        <v>6768402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3202,50 +3202,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723028</v>
+        <v>127723487</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445345</v>
+        <v>445328</v>
       </c>
       <c r="R28" t="n">
-        <v>6768382</v>
+        <v>6768445</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3272,12 +3267,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3304,7 +3299,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723538</v>
+        <v>127723428</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3339,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445485</v>
+        <v>445329</v>
       </c>
       <c r="R29" t="n">
-        <v>6768313</v>
+        <v>6768465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3401,7 +3396,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723487</v>
+        <v>127723529</v>
       </c>
       <c r="B30" t="n">
         <v>79020</v>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445328</v>
+        <v>445507</v>
       </c>
       <c r="R30" t="n">
-        <v>6768445</v>
+        <v>6768383</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,7 +3493,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723523</v>
+        <v>127723538</v>
       </c>
       <c r="B31" t="n">
         <v>79020</v>
@@ -3533,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445451</v>
+        <v>445485</v>
       </c>
       <c r="R31" t="n">
-        <v>6768402</v>
+        <v>6768313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723529</v>
+        <v>127722895</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,34 +3601,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445507</v>
+        <v>445370</v>
       </c>
       <c r="R32" t="n">
-        <v>6768383</v>
+        <v>6768276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3692,38 +3692,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722895</v>
+        <v>127723028</v>
       </c>
       <c r="B33" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445370</v>
+        <v>445345</v>
       </c>
       <c r="R33" t="n">
-        <v>6768276</v>
+        <v>6768382</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723515</v>
+        <v>127723431</v>
       </c>
       <c r="B35" t="n">
         <v>79020</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445465</v>
+        <v>445369</v>
       </c>
       <c r="R35" t="n">
-        <v>6768438</v>
+        <v>6768408</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723431</v>
+        <v>127723536</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445369</v>
+        <v>445500</v>
       </c>
       <c r="R36" t="n">
-        <v>6768408</v>
+        <v>6768348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723446</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445453</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723446</v>
+        <v>127723515</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445453</v>
+        <v>445465</v>
       </c>
       <c r="R39" t="n">
-        <v>6768321</v>
+        <v>6768438</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723418</v>
+        <v>127723565</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445411</v>
+        <v>445406</v>
       </c>
       <c r="R40" t="n">
-        <v>6768470</v>
+        <v>6768484</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4447,6 +4447,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4473,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723565</v>
+        <v>127723427</v>
       </c>
       <c r="B41" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445406</v>
+        <v>445322</v>
       </c>
       <c r="R41" t="n">
-        <v>6768484</v>
+        <v>6768457</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4549,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,7 +4575,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723422</v>
+        <v>127723418</v>
       </c>
       <c r="B42" t="n">
         <v>79020</v>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445332</v>
+        <v>445411</v>
       </c>
       <c r="R42" t="n">
-        <v>6768518</v>
+        <v>6768470</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723427</v>
+        <v>127723422</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445322</v>
+        <v>445332</v>
       </c>
       <c r="R43" t="n">
-        <v>6768457</v>
+        <v>6768518</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4963,45 +4963,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723534</v>
+        <v>127723025</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445528</v>
+        <v>445397</v>
       </c>
       <c r="R46" t="n">
-        <v>6768349</v>
+        <v>6768481</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5028,12 +5033,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5060,45 +5065,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723521</v>
+        <v>127723026</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445445</v>
+        <v>445387</v>
       </c>
       <c r="R47" t="n">
-        <v>6768409</v>
+        <v>6768492</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5125,12 +5135,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5157,50 +5167,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723025</v>
+        <v>127723534</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445397</v>
+        <v>445528</v>
       </c>
       <c r="R48" t="n">
-        <v>6768481</v>
+        <v>6768349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5227,12 +5232,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5259,50 +5264,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723026</v>
+        <v>127723521</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445387</v>
+        <v>445445</v>
       </c>
       <c r="R49" t="n">
-        <v>6768492</v>
+        <v>6768409</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5555,7 +5555,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723430</v>
+        <v>127723444</v>
       </c>
       <c r="B52" t="n">
         <v>79020</v>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445357</v>
+        <v>445432</v>
       </c>
       <c r="R52" t="n">
-        <v>6768451</v>
+        <v>6768299</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723444</v>
+        <v>127723430</v>
       </c>
       <c r="B53" t="n">
         <v>79020</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445432</v>
+        <v>445357</v>
       </c>
       <c r="R53" t="n">
-        <v>6768299</v>
+        <v>6768451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723492</v>
+        <v>127723499</v>
       </c>
       <c r="B58" t="n">
         <v>79020</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445366</v>
+        <v>445418</v>
       </c>
       <c r="R58" t="n">
-        <v>6768409</v>
+        <v>6768394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723488</v>
+        <v>127723526</v>
       </c>
       <c r="B59" t="n">
         <v>79020</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445340</v>
+        <v>445468</v>
       </c>
       <c r="R59" t="n">
-        <v>6768445</v>
+        <v>6768377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723526</v>
+        <v>127723492</v>
       </c>
       <c r="B60" t="n">
         <v>79020</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445468</v>
+        <v>445366</v>
       </c>
       <c r="R60" t="n">
-        <v>6768377</v>
+        <v>6768409</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723499</v>
+        <v>127723488</v>
       </c>
       <c r="B61" t="n">
         <v>79020</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445418</v>
+        <v>445340</v>
       </c>
       <c r="R61" t="n">
-        <v>6768394</v>
+        <v>6768445</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722914</v>
+        <v>127722872</v>
       </c>
       <c r="B62" t="n">
-        <v>57663</v>
+        <v>57823</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,27 +6541,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445325</v>
+        <v>445414</v>
       </c>
       <c r="R62" t="n">
-        <v>6768463</v>
+        <v>6768450</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,11 +6606,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6734,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722872</v>
+        <v>127722914</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>57663</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6745,27 +6740,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445325</v>
       </c>
       <c r="R64" t="n">
-        <v>6768450</v>
+        <v>6768463</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6810,6 +6805,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723455</v>
+        <v>127723439</v>
       </c>
       <c r="B66" t="n">
         <v>79020</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445417</v>
+        <v>445382</v>
       </c>
       <c r="R66" t="n">
-        <v>6768483</v>
+        <v>6768296</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723511</v>
+        <v>127723506</v>
       </c>
       <c r="B67" t="n">
         <v>79020</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445497</v>
+        <v>445509</v>
       </c>
       <c r="R67" t="n">
-        <v>6768438</v>
+        <v>6768424</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723528</v>
+        <v>127723489</v>
       </c>
       <c r="B68" t="n">
         <v>79020</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445493</v>
+        <v>445349</v>
       </c>
       <c r="R68" t="n">
-        <v>6768388</v>
+        <v>6768438</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,10 +7224,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127722917</v>
+        <v>127723455</v>
       </c>
       <c r="B69" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7235,39 +7235,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445329</v>
+        <v>445417</v>
       </c>
       <c r="R69" t="n">
-        <v>6768466</v>
+        <v>6768483</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7294,17 +7289,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7331,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127722908</v>
+        <v>127723522</v>
       </c>
       <c r="B70" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7342,39 +7332,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445329</v>
+        <v>445457</v>
       </c>
       <c r="R70" t="n">
-        <v>6768474</v>
+        <v>6768411</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7401,17 +7386,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7438,50 +7418,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723034</v>
+        <v>127723519</v>
       </c>
       <c r="B71" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445377</v>
+        <v>445434</v>
       </c>
       <c r="R71" t="n">
-        <v>6768394</v>
+        <v>6768437</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7540,7 +7515,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723496</v>
+        <v>127723511</v>
       </c>
       <c r="B72" t="n">
         <v>79020</v>
@@ -7575,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445376</v>
+        <v>445497</v>
       </c>
       <c r="R72" t="n">
-        <v>6768426</v>
+        <v>6768438</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7637,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723489</v>
+        <v>127723496</v>
       </c>
       <c r="B73" t="n">
         <v>79020</v>
@@ -7672,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445349</v>
+        <v>445376</v>
       </c>
       <c r="R73" t="n">
-        <v>6768438</v>
+        <v>6768426</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7734,7 +7709,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723522</v>
+        <v>127723528</v>
       </c>
       <c r="B74" t="n">
         <v>79020</v>
@@ -7769,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445457</v>
+        <v>445493</v>
       </c>
       <c r="R74" t="n">
-        <v>6768411</v>
+        <v>6768388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723439</v>
+        <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,34 +7817,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445382</v>
+        <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768296</v>
+        <v>6768466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7902,6 +7882,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7928,10 +7913,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723506</v>
+        <v>127722908</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7939,34 +7924,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445509</v>
+        <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768424</v>
+        <v>6768474</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7993,12 +7983,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8025,45 +8020,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723519</v>
+        <v>127723034</v>
       </c>
       <c r="B77" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445434</v>
+        <v>445377</v>
       </c>
       <c r="R77" t="n">
-        <v>6768437</v>
+        <v>6768394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,7 +8122,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723423</v>
+        <v>127723415</v>
       </c>
       <c r="B78" t="n">
         <v>79020</v>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445325</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6768515</v>
+        <v>6768387</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723415</v>
+        <v>127723494</v>
       </c>
       <c r="B79" t="n">
         <v>79020</v>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445422</v>
+        <v>445355</v>
       </c>
       <c r="R79" t="n">
-        <v>6768387</v>
+        <v>6768420</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8284,12 +8284,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8316,7 +8316,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723494</v>
+        <v>127723537</v>
       </c>
       <c r="B80" t="n">
         <v>79020</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445355</v>
+        <v>445488</v>
       </c>
       <c r="R80" t="n">
-        <v>6768420</v>
+        <v>6768315</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723420</v>
+        <v>127723533</v>
       </c>
       <c r="B81" t="n">
         <v>79020</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445395</v>
+        <v>445523</v>
       </c>
       <c r="R81" t="n">
-        <v>6768485</v>
+        <v>6768356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8510,10 +8510,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127722825</v>
+        <v>127723432</v>
       </c>
       <c r="B82" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8521,21 +8521,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445386</v>
+        <v>445360</v>
       </c>
       <c r="R82" t="n">
-        <v>6768493</v>
+        <v>6768399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8607,50 +8607,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127722931</v>
+        <v>127723423</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445518</v>
+        <v>445325</v>
       </c>
       <c r="R83" t="n">
-        <v>6768355</v>
+        <v>6768515</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8709,50 +8704,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722930</v>
+        <v>127723420</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445390</v>
+        <v>445395</v>
       </c>
       <c r="R84" t="n">
-        <v>6768381</v>
+        <v>6768485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8779,12 +8769,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8811,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723030</v>
+        <v>127723560</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>92628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8822,39 +8812,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445376</v>
+        <v>445433</v>
       </c>
       <c r="R85" t="n">
-        <v>6768336</v>
+        <v>6768412</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8881,12 +8866,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8913,32 +8898,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723560</v>
+        <v>127723411</v>
       </c>
       <c r="B86" t="n">
-        <v>92622</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8948,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445433</v>
+        <v>445410</v>
       </c>
       <c r="R86" t="n">
-        <v>6768412</v>
+        <v>6768338</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8978,12 +8963,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9010,10 +8995,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723432</v>
+        <v>127722825</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9021,21 +9006,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9045,10 +9030,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445360</v>
+        <v>445386</v>
       </c>
       <c r="R87" t="n">
-        <v>6768399</v>
+        <v>6768493</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9107,45 +9092,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723411</v>
+        <v>127722931</v>
       </c>
       <c r="B88" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445410</v>
+        <v>445518</v>
       </c>
       <c r="R88" t="n">
-        <v>6768338</v>
+        <v>6768355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9204,45 +9194,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723533</v>
+        <v>127722930</v>
       </c>
       <c r="B89" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445523</v>
+        <v>445390</v>
       </c>
       <c r="R89" t="n">
-        <v>6768356</v>
+        <v>6768381</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9301,45 +9296,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723537</v>
+        <v>127723030</v>
       </c>
       <c r="B90" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445488</v>
+        <v>445376</v>
       </c>
       <c r="R90" t="n">
-        <v>6768315</v>
+        <v>6768336</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723414</v>
+        <v>127723426</v>
       </c>
       <c r="B92" t="n">
         <v>79020</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445429</v>
+        <v>445324</v>
       </c>
       <c r="R92" t="n">
-        <v>6768360</v>
+        <v>6768470</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723497</v>
+        <v>127723452</v>
       </c>
       <c r="B93" t="n">
         <v>79020</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445376</v>
+        <v>445473</v>
       </c>
       <c r="R93" t="n">
-        <v>6768407</v>
+        <v>6768325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9689,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723426</v>
+        <v>127723497</v>
       </c>
       <c r="B94" t="n">
         <v>79020</v>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445324</v>
+        <v>445376</v>
       </c>
       <c r="R94" t="n">
-        <v>6768470</v>
+        <v>6768407</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723452</v>
+        <v>127723504</v>
       </c>
       <c r="B95" t="n">
         <v>79020</v>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445473</v>
+        <v>445449</v>
       </c>
       <c r="R95" t="n">
-        <v>6768325</v>
+        <v>6768387</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723504</v>
+        <v>127723414</v>
       </c>
       <c r="B96" t="n">
         <v>79020</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445449</v>
+        <v>445429</v>
       </c>
       <c r="R96" t="n">
-        <v>6768387</v>
+        <v>6768360</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,12 +9948,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10082,38 +10082,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723027</v>
+        <v>127722918</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>57663</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445343</v>
+        <v>445382</v>
       </c>
       <c r="R98" t="n">
-        <v>6768460</v>
+        <v>6768422</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10152,12 +10152,17 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10184,45 +10189,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723605</v>
+        <v>127723027</v>
       </c>
       <c r="B99" t="n">
-        <v>78687</v>
+        <v>8450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445403</v>
+        <v>445343</v>
       </c>
       <c r="R99" t="n">
-        <v>6768385</v>
+        <v>6768460</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10249,12 +10259,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10281,10 +10291,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722864</v>
+        <v>127723605</v>
       </c>
       <c r="B100" t="n">
-        <v>91332</v>
+        <v>78687</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10292,21 +10302,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10316,10 +10326,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445327</v>
+        <v>445403</v>
       </c>
       <c r="R100" t="n">
-        <v>6768444</v>
+        <v>6768385</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10378,10 +10388,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723454</v>
+        <v>127722864</v>
       </c>
       <c r="B101" t="n">
-        <v>79020</v>
+        <v>91338</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10389,21 +10399,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10413,10 +10423,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445421</v>
+        <v>445327</v>
       </c>
       <c r="R101" t="n">
-        <v>6768465</v>
+        <v>6768444</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10475,7 +10485,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723447</v>
+        <v>127723490</v>
       </c>
       <c r="B102" t="n">
         <v>79020</v>
@@ -10510,10 +10520,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445458</v>
+        <v>445353</v>
       </c>
       <c r="R102" t="n">
-        <v>6768338</v>
+        <v>6768438</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10540,12 +10550,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10572,7 +10582,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723490</v>
+        <v>127723447</v>
       </c>
       <c r="B103" t="n">
         <v>79020</v>
@@ -10607,10 +10617,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445353</v>
+        <v>445458</v>
       </c>
       <c r="R103" t="n">
-        <v>6768438</v>
+        <v>6768338</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10637,12 +10647,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10669,7 +10679,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723483</v>
+        <v>127723535</v>
       </c>
       <c r="B104" t="n">
         <v>79020</v>
@@ -10704,10 +10714,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445310</v>
+        <v>445518</v>
       </c>
       <c r="R104" t="n">
-        <v>6768467</v>
+        <v>6768343</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10766,7 +10776,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723440</v>
+        <v>127723483</v>
       </c>
       <c r="B105" t="n">
         <v>79020</v>
@@ -10801,10 +10811,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445394</v>
+        <v>445310</v>
       </c>
       <c r="R105" t="n">
-        <v>6768290</v>
+        <v>6768467</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10831,12 +10841,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10863,7 +10873,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723535</v>
+        <v>127723454</v>
       </c>
       <c r="B106" t="n">
         <v>79020</v>
@@ -10898,10 +10908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445518</v>
+        <v>445421</v>
       </c>
       <c r="R106" t="n">
-        <v>6768343</v>
+        <v>6768465</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10960,10 +10970,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127722918</v>
+        <v>127723440</v>
       </c>
       <c r="B107" t="n">
-        <v>57663</v>
+        <v>79020</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10971,39 +10981,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445382</v>
+        <v>445394</v>
       </c>
       <c r="R107" t="n">
-        <v>6768422</v>
+        <v>6768290</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11030,17 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11261,7 +11261,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723429</v>
+        <v>127723495</v>
       </c>
       <c r="B110" t="n">
         <v>79020</v>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445339</v>
+        <v>445361</v>
       </c>
       <c r="R110" t="n">
-        <v>6768457</v>
+        <v>6768425</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723495</v>
+        <v>127722832</v>
       </c>
       <c r="B111" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445361</v>
+        <v>445457</v>
       </c>
       <c r="R111" t="n">
-        <v>6768425</v>
+        <v>6768397</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B112" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R112" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723607</v>
+        <v>127723441</v>
       </c>
       <c r="B113" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445529</v>
+        <v>445408</v>
       </c>
       <c r="R113" t="n">
-        <v>6768354</v>
+        <v>6768287</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11617,12 +11617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723441</v>
+        <v>127723607</v>
       </c>
       <c r="B114" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445408</v>
+        <v>445529</v>
       </c>
       <c r="R114" t="n">
-        <v>6768287</v>
+        <v>6768354</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11714,12 +11714,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12134,7 +12134,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723505</v>
+        <v>127723410</v>
       </c>
       <c r="B119" t="n">
         <v>79020</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445493</v>
+        <v>445434</v>
       </c>
       <c r="R119" t="n">
-        <v>6768418</v>
+        <v>6768336</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723438</v>
+        <v>127723443</v>
       </c>
       <c r="B120" t="n">
         <v>79020</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445375</v>
+        <v>445422</v>
       </c>
       <c r="R120" t="n">
-        <v>6768277</v>
+        <v>6768295</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722831</v>
+        <v>127723505</v>
       </c>
       <c r="B121" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12339,21 +12339,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445370</v>
+        <v>445493</v>
       </c>
       <c r="R121" t="n">
-        <v>6768425</v>
+        <v>6768418</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723410</v>
+        <v>127723438</v>
       </c>
       <c r="B122" t="n">
         <v>79020</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445434</v>
+        <v>445375</v>
       </c>
       <c r="R122" t="n">
-        <v>6768336</v>
+        <v>6768277</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723443</v>
+        <v>127722831</v>
       </c>
       <c r="B124" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445422</v>
+        <v>445370</v>
       </c>
       <c r="R124" t="n">
-        <v>6768295</v>
+        <v>6768425</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127723518</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723479</v>
+        <v>127723434</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445309</v>
+        <v>445345</v>
       </c>
       <c r="R3" t="n">
-        <v>6768491</v>
+        <v>6768366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723416</v>
+        <v>127723480</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445426</v>
+        <v>445314</v>
       </c>
       <c r="R4" t="n">
-        <v>6768417</v>
+        <v>6768485</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723531</v>
+        <v>127723421</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445524</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>6768371</v>
+        <v>6768495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723424</v>
+        <v>127723416</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445311</v>
+        <v>445426</v>
       </c>
       <c r="R6" t="n">
-        <v>6768500</v>
+        <v>6768417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127722873</v>
+        <v>127723493</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>79023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,39 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445364</v>
+        <v>445363</v>
       </c>
       <c r="R7" t="n">
-        <v>6768295</v>
+        <v>6768410</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1230,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723434</v>
+        <v>127723479</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445345</v>
+        <v>445309</v>
       </c>
       <c r="R8" t="n">
-        <v>6768366</v>
+        <v>6768491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1327,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723480</v>
+        <v>127723531</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445314</v>
+        <v>445524</v>
       </c>
       <c r="R9" t="n">
-        <v>6768485</v>
+        <v>6768371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723421</v>
+        <v>127723424</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445361</v>
+        <v>445311</v>
       </c>
       <c r="R10" t="n">
-        <v>6768495</v>
+        <v>6768500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723493</v>
+        <v>127722873</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>57826</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1559,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445363</v>
+        <v>445364</v>
       </c>
       <c r="R11" t="n">
-        <v>6768410</v>
+        <v>6768295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723606</v>
+        <v>127723445</v>
       </c>
       <c r="B12" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445475</v>
+        <v>445446</v>
       </c>
       <c r="R12" t="n">
-        <v>6768378</v>
+        <v>6768306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1750,7 +1750,7 @@
         <v>127723602</v>
       </c>
       <c r="B13" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723445</v>
+        <v>127723606</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445446</v>
+        <v>445475</v>
       </c>
       <c r="R14" t="n">
-        <v>6768306</v>
+        <v>6768378</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1944,7 +1944,7 @@
         <v>127723512</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723561</v>
+        <v>127723517</v>
       </c>
       <c r="B16" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445519</v>
+        <v>445463</v>
       </c>
       <c r="R16" t="n">
-        <v>6768373</v>
+        <v>6768439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723517</v>
+        <v>127723435</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445463</v>
+        <v>445375</v>
       </c>
       <c r="R17" t="n">
-        <v>6768439</v>
+        <v>6768348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723435</v>
+        <v>127723442</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445375</v>
+        <v>445407</v>
       </c>
       <c r="R18" t="n">
-        <v>6768348</v>
+        <v>6768295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723442</v>
+        <v>127723520</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445407</v>
+        <v>445439</v>
       </c>
       <c r="R19" t="n">
-        <v>6768295</v>
+        <v>6768423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723520</v>
+        <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445439</v>
+        <v>445519</v>
       </c>
       <c r="R20" t="n">
-        <v>6768423</v>
+        <v>6768373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2526,7 +2526,7 @@
         <v>127723500</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723527</v>
+        <v>127723412</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445476</v>
+        <v>445423</v>
       </c>
       <c r="R22" t="n">
-        <v>6768382</v>
+        <v>6768342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723412</v>
+        <v>127723417</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445423</v>
+        <v>445413</v>
       </c>
       <c r="R23" t="n">
-        <v>6768342</v>
+        <v>6768451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723417</v>
+        <v>127723433</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445413</v>
+        <v>445354</v>
       </c>
       <c r="R24" t="n">
-        <v>6768451</v>
+        <v>6768399</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723433</v>
+        <v>127723525</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445354</v>
+        <v>445465</v>
       </c>
       <c r="R25" t="n">
-        <v>6768399</v>
+        <v>6768379</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723525</v>
+        <v>127723527</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445465</v>
+        <v>445476</v>
       </c>
       <c r="R26" t="n">
-        <v>6768379</v>
+        <v>6768382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3108,7 +3108,7 @@
         <v>127723523</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723487</v>
+        <v>127723529</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445328</v>
+        <v>445507</v>
       </c>
       <c r="R28" t="n">
-        <v>6768445</v>
+        <v>6768383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723428</v>
+        <v>127723487</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445329</v>
+        <v>445328</v>
       </c>
       <c r="R29" t="n">
-        <v>6768465</v>
+        <v>6768445</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723529</v>
+        <v>127723428</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445507</v>
+        <v>445329</v>
       </c>
       <c r="R30" t="n">
-        <v>6768383</v>
+        <v>6768465</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3496,7 +3496,7 @@
         <v>127723538</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>127722895</v>
       </c>
       <c r="B32" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>127723431</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723536</v>
+        <v>127723446</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445500</v>
+        <v>445453</v>
       </c>
       <c r="R36" t="n">
-        <v>6768348</v>
+        <v>6768321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723482</v>
+        <v>127723515</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445318</v>
+        <v>445465</v>
       </c>
       <c r="R37" t="n">
-        <v>6768474</v>
+        <v>6768438</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723446</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445453</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723515</v>
+        <v>127723482</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445465</v>
+        <v>445318</v>
       </c>
       <c r="R39" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723565</v>
+        <v>127723427</v>
       </c>
       <c r="B40" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445406</v>
+        <v>445322</v>
       </c>
       <c r="R40" t="n">
-        <v>6768484</v>
+        <v>6768457</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4447,11 +4447,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4478,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723427</v>
+        <v>127723565</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4489,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445322</v>
+        <v>445406</v>
       </c>
       <c r="R41" t="n">
-        <v>6768457</v>
+        <v>6768484</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4549,6 +4544,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723418</v>
+        <v>127723422</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445411</v>
+        <v>445332</v>
       </c>
       <c r="R42" t="n">
-        <v>6768470</v>
+        <v>6768518</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723422</v>
+        <v>127723418</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445332</v>
+        <v>445411</v>
       </c>
       <c r="R43" t="n">
-        <v>6768518</v>
+        <v>6768470</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723592</v>
+        <v>127723534</v>
       </c>
       <c r="B44" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445370</v>
+        <v>445528</v>
       </c>
       <c r="R44" t="n">
-        <v>6768478</v>
+        <v>6768349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4834,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723604</v>
+        <v>127723521</v>
       </c>
       <c r="B45" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445370</v>
+        <v>445445</v>
       </c>
       <c r="R45" t="n">
-        <v>6768425</v>
+        <v>6768409</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,50 +4963,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723025</v>
+        <v>127723604</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>78690</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445397</v>
+        <v>445370</v>
       </c>
       <c r="R46" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,12 +5028,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5065,50 +5060,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723026</v>
+        <v>127723592</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>78690</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445387</v>
+        <v>445370</v>
       </c>
       <c r="R47" t="n">
-        <v>6768492</v>
+        <v>6768478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,45 +5157,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723534</v>
+        <v>127723025</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445528</v>
+        <v>445397</v>
       </c>
       <c r="R48" t="n">
-        <v>6768349</v>
+        <v>6768481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5232,12 +5227,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5264,45 +5259,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723521</v>
+        <v>127723026</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445445</v>
+        <v>445387</v>
       </c>
       <c r="R49" t="n">
-        <v>6768409</v>
+        <v>6768492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5364,7 +5364,7 @@
         <v>127723501</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>127723478</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723444</v>
+        <v>127723425</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445432</v>
+        <v>445321</v>
       </c>
       <c r="R52" t="n">
-        <v>6768299</v>
+        <v>6768501</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127722829</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5663,21 +5663,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445339</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768436</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5717,12 +5717,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723425</v>
+        <v>127723524</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445321</v>
+        <v>445455</v>
       </c>
       <c r="R54" t="n">
-        <v>6768501</v>
+        <v>6768391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723524</v>
+        <v>127722889</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>57663</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,34 +5857,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445455</v>
+        <v>445372</v>
       </c>
       <c r="R55" t="n">
-        <v>6768391</v>
+        <v>6768323</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5911,12 +5916,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5943,10 +5948,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722829</v>
+        <v>127723444</v>
       </c>
       <c r="B56" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5954,21 +5959,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445339</v>
+        <v>445432</v>
       </c>
       <c r="R56" t="n">
-        <v>6768436</v>
+        <v>6768299</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6008,12 +6013,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6040,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722889</v>
+        <v>127723430</v>
       </c>
       <c r="B57" t="n">
-        <v>57660</v>
+        <v>79023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6051,39 +6056,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445372</v>
+        <v>445357</v>
       </c>
       <c r="R57" t="n">
-        <v>6768323</v>
+        <v>6768451</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6142,10 +6142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723499</v>
+        <v>127723488</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445418</v>
+        <v>445340</v>
       </c>
       <c r="R58" t="n">
-        <v>6768394</v>
+        <v>6768445</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723526</v>
+        <v>127723499</v>
       </c>
       <c r="B59" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445468</v>
+        <v>445418</v>
       </c>
       <c r="R59" t="n">
-        <v>6768377</v>
+        <v>6768394</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723492</v>
+        <v>127723526</v>
       </c>
       <c r="B60" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445366</v>
+        <v>445468</v>
       </c>
       <c r="R60" t="n">
-        <v>6768409</v>
+        <v>6768377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723488</v>
+        <v>127723492</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445340</v>
+        <v>445366</v>
       </c>
       <c r="R61" t="n">
-        <v>6768445</v>
+        <v>6768409</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722872</v>
+        <v>127722914</v>
       </c>
       <c r="B62" t="n">
-        <v>57823</v>
+        <v>57666</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,27 +6541,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -6570,10 +6570,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445414</v>
+        <v>445325</v>
       </c>
       <c r="R62" t="n">
-        <v>6768450</v>
+        <v>6768463</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,6 +6606,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6635,7 +6640,7 @@
         <v>127723413</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,10 +6734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722914</v>
+        <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>57663</v>
+        <v>57826</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,27 +6745,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6769,10 +6774,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445325</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6768463</v>
+        <v>6768450</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6805,11 +6810,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723514</v>
+        <v>127723439</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445468</v>
+        <v>445382</v>
       </c>
       <c r="R65" t="n">
-        <v>6768439</v>
+        <v>6768296</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,10 +6933,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R66" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7030,10 +7030,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723506</v>
+        <v>127723455</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445509</v>
+        <v>445417</v>
       </c>
       <c r="R67" t="n">
-        <v>6768424</v>
+        <v>6768483</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723489</v>
+        <v>127723522</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445349</v>
+        <v>445457</v>
       </c>
       <c r="R68" t="n">
-        <v>6768438</v>
+        <v>6768411</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,10 +7224,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723455</v>
+        <v>127723528</v>
       </c>
       <c r="B69" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445417</v>
+        <v>445493</v>
       </c>
       <c r="R69" t="n">
-        <v>6768483</v>
+        <v>6768388</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723522</v>
+        <v>127723519</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445457</v>
+        <v>445434</v>
       </c>
       <c r="R70" t="n">
-        <v>6768411</v>
+        <v>6768437</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,10 +7418,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723519</v>
+        <v>127723496</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445434</v>
+        <v>445376</v>
       </c>
       <c r="R71" t="n">
-        <v>6768437</v>
+        <v>6768426</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7518,7 +7518,7 @@
         <v>127723511</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7612,10 +7612,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723496</v>
+        <v>127723514</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445376</v>
+        <v>445468</v>
       </c>
       <c r="R73" t="n">
-        <v>6768426</v>
+        <v>6768439</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,10 +7709,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723528</v>
+        <v>127723506</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445493</v>
+        <v>445509</v>
       </c>
       <c r="R74" t="n">
-        <v>6768388</v>
+        <v>6768424</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7809,7 +7809,7 @@
         <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
         <v>127722908</v>
       </c>
       <c r="B76" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>127723415</v>
       </c>
       <c r="B78" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723494</v>
+        <v>127723411</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445355</v>
+        <v>445410</v>
       </c>
       <c r="R79" t="n">
-        <v>6768420</v>
+        <v>6768338</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8284,12 +8284,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723537</v>
+        <v>127723494</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445488</v>
+        <v>445355</v>
       </c>
       <c r="R80" t="n">
-        <v>6768315</v>
+        <v>6768420</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8413,10 +8413,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723533</v>
+        <v>127723537</v>
       </c>
       <c r="B81" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445523</v>
+        <v>445488</v>
       </c>
       <c r="R81" t="n">
-        <v>6768356</v>
+        <v>6768315</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,10 +8510,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723432</v>
+        <v>127723533</v>
       </c>
       <c r="B82" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445360</v>
+        <v>445523</v>
       </c>
       <c r="R82" t="n">
-        <v>6768399</v>
+        <v>6768356</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8607,32 +8607,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723423</v>
+        <v>127723560</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>92631</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445325</v>
+        <v>445433</v>
       </c>
       <c r="R83" t="n">
-        <v>6768515</v>
+        <v>6768412</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723420</v>
+        <v>127722825</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445395</v>
+        <v>445386</v>
       </c>
       <c r="R84" t="n">
-        <v>6768485</v>
+        <v>6768493</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,32 +8801,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723560</v>
+        <v>127723432</v>
       </c>
       <c r="B85" t="n">
-        <v>92628</v>
+        <v>79023</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445433</v>
+        <v>445360</v>
       </c>
       <c r="R85" t="n">
-        <v>6768412</v>
+        <v>6768399</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8866,12 +8866,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8898,10 +8898,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723411</v>
+        <v>127723423</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445410</v>
+        <v>445325</v>
       </c>
       <c r="R86" t="n">
-        <v>6768338</v>
+        <v>6768515</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8995,10 +8995,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722825</v>
+        <v>127723420</v>
       </c>
       <c r="B87" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9006,21 +9006,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445386</v>
+        <v>445395</v>
       </c>
       <c r="R87" t="n">
-        <v>6768493</v>
+        <v>6768485</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9401,7 +9401,7 @@
         <v>127723436</v>
       </c>
       <c r="B91" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>127723426</v>
       </c>
       <c r="B92" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>127723452</v>
       </c>
       <c r="B93" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>127723497</v>
       </c>
       <c r="B94" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>127723504</v>
       </c>
       <c r="B95" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9886,7 +9886,7 @@
         <v>127723414</v>
       </c>
       <c r="B96" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10085,7 +10085,7 @@
         <v>127722918</v>
       </c>
       <c r="B98" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10291,10 +10291,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723605</v>
+        <v>127722864</v>
       </c>
       <c r="B100" t="n">
-        <v>78687</v>
+        <v>91341</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10302,21 +10302,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10326,10 +10326,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445403</v>
+        <v>445327</v>
       </c>
       <c r="R100" t="n">
-        <v>6768385</v>
+        <v>6768444</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10388,10 +10388,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127722864</v>
+        <v>127723490</v>
       </c>
       <c r="B101" t="n">
-        <v>91338</v>
+        <v>79023</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10399,21 +10399,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445327</v>
+        <v>445353</v>
       </c>
       <c r="R101" t="n">
-        <v>6768444</v>
+        <v>6768438</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10485,10 +10485,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723490</v>
+        <v>127723447</v>
       </c>
       <c r="B102" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445353</v>
+        <v>445458</v>
       </c>
       <c r="R102" t="n">
-        <v>6768438</v>
+        <v>6768338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10550,12 +10550,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10582,10 +10582,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723447</v>
+        <v>127723483</v>
       </c>
       <c r="B103" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445458</v>
+        <v>445310</v>
       </c>
       <c r="R103" t="n">
-        <v>6768338</v>
+        <v>6768467</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10647,12 +10647,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10679,10 +10679,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723535</v>
+        <v>127723454</v>
       </c>
       <c r="B104" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10714,10 +10714,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445518</v>
+        <v>445421</v>
       </c>
       <c r="R104" t="n">
-        <v>6768343</v>
+        <v>6768465</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10776,10 +10776,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723483</v>
+        <v>127723605</v>
       </c>
       <c r="B105" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10787,21 +10787,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445310</v>
+        <v>445403</v>
       </c>
       <c r="R105" t="n">
-        <v>6768467</v>
+        <v>6768385</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10873,10 +10873,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723454</v>
+        <v>127723440</v>
       </c>
       <c r="B106" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10908,10 +10908,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445421</v>
+        <v>445394</v>
       </c>
       <c r="R106" t="n">
-        <v>6768465</v>
+        <v>6768290</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10938,12 +10938,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10970,10 +10970,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723440</v>
+        <v>127723535</v>
       </c>
       <c r="B107" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445394</v>
+        <v>445518</v>
       </c>
       <c r="R107" t="n">
-        <v>6768290</v>
+        <v>6768343</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11070,7 +11070,7 @@
         <v>127723593</v>
       </c>
       <c r="B108" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723481</v>
+        <v>127723495</v>
       </c>
       <c r="B109" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445320</v>
+        <v>445361</v>
       </c>
       <c r="R109" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723495</v>
+        <v>127723481</v>
       </c>
       <c r="B110" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445361</v>
+        <v>445320</v>
       </c>
       <c r="R110" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B111" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R111" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723429</v>
+        <v>127722832</v>
       </c>
       <c r="B112" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445339</v>
+        <v>445457</v>
       </c>
       <c r="R112" t="n">
-        <v>6768457</v>
+        <v>6768397</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723441</v>
+        <v>127723607</v>
       </c>
       <c r="B113" t="n">
-        <v>79020</v>
+        <v>78690</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445408</v>
+        <v>445529</v>
       </c>
       <c r="R113" t="n">
-        <v>6768287</v>
+        <v>6768354</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11617,12 +11617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723607</v>
+        <v>127723532</v>
       </c>
       <c r="B114" t="n">
-        <v>78687</v>
+        <v>79023</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445529</v>
+        <v>445523</v>
       </c>
       <c r="R114" t="n">
-        <v>6768354</v>
+        <v>6768362</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723498</v>
+        <v>127723453</v>
       </c>
       <c r="B115" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445386</v>
+        <v>445418</v>
       </c>
       <c r="R115" t="n">
-        <v>6768393</v>
+        <v>6768439</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11843,10 +11843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723530</v>
+        <v>127723498</v>
       </c>
       <c r="B116" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445515</v>
+        <v>445386</v>
       </c>
       <c r="R116" t="n">
-        <v>6768378</v>
+        <v>6768393</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,10 +11940,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723532</v>
+        <v>127723530</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445523</v>
+        <v>445515</v>
       </c>
       <c r="R117" t="n">
-        <v>6768362</v>
+        <v>6768378</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723453</v>
+        <v>127723441</v>
       </c>
       <c r="B118" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445418</v>
+        <v>445408</v>
       </c>
       <c r="R118" t="n">
-        <v>6768439</v>
+        <v>6768287</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12102,12 +12102,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12137,7 +12137,7 @@
         <v>127723410</v>
       </c>
       <c r="B119" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12231,10 +12231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723443</v>
+        <v>127722831</v>
       </c>
       <c r="B120" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12242,21 +12242,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445422</v>
+        <v>445370</v>
       </c>
       <c r="R120" t="n">
-        <v>6768295</v>
+        <v>6768425</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12331,7 +12331,7 @@
         <v>127723505</v>
       </c>
       <c r="B121" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12425,10 +12425,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723438</v>
+        <v>127723503</v>
       </c>
       <c r="B122" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R122" t="n">
-        <v>6768277</v>
+        <v>6768381</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,10 +12522,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723503</v>
+        <v>127723443</v>
       </c>
       <c r="B123" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445439</v>
+        <v>445422</v>
       </c>
       <c r="R123" t="n">
-        <v>6768381</v>
+        <v>6768295</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722831</v>
+        <v>127723438</v>
       </c>
       <c r="B124" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445370</v>
+        <v>445375</v>
       </c>
       <c r="R124" t="n">
-        <v>6768425</v>
+        <v>6768277</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723518</v>
+        <v>127723479</v>
       </c>
       <c r="B2" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445431</v>
+        <v>445309</v>
       </c>
       <c r="R2" t="n">
-        <v>6768443</v>
+        <v>6768491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723434</v>
+        <v>127723421</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445345</v>
+        <v>445361</v>
       </c>
       <c r="R3" t="n">
-        <v>6768366</v>
+        <v>6768495</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723480</v>
+        <v>127723424</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445314</v>
+        <v>445311</v>
       </c>
       <c r="R4" t="n">
-        <v>6768485</v>
+        <v>6768500</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723421</v>
+        <v>127723434</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445345</v>
       </c>
       <c r="R5" t="n">
-        <v>6768495</v>
+        <v>6768366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723416</v>
+        <v>127723480</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445426</v>
+        <v>445314</v>
       </c>
       <c r="R6" t="n">
-        <v>6768417</v>
+        <v>6768485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723493</v>
+        <v>127723416</v>
       </c>
       <c r="B7" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445363</v>
+        <v>445426</v>
       </c>
       <c r="R7" t="n">
-        <v>6768410</v>
+        <v>6768417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723479</v>
+        <v>127723493</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445309</v>
+        <v>445363</v>
       </c>
       <c r="R8" t="n">
-        <v>6768491</v>
+        <v>6768410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1357,7 @@
         <v>127723531</v>
       </c>
       <c r="B9" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723424</v>
+        <v>127723518</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445311</v>
+        <v>445431</v>
       </c>
       <c r="R10" t="n">
-        <v>6768500</v>
+        <v>6768443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1551,7 +1551,7 @@
         <v>127722873</v>
       </c>
       <c r="B11" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723445</v>
+        <v>127723602</v>
       </c>
       <c r="B12" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445446</v>
+        <v>445339</v>
       </c>
       <c r="R12" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723602</v>
+        <v>127723606</v>
       </c>
       <c r="B13" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445339</v>
+        <v>445475</v>
       </c>
       <c r="R13" t="n">
-        <v>6768436</v>
+        <v>6768378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723606</v>
+        <v>127723445</v>
       </c>
       <c r="B14" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445475</v>
+        <v>445446</v>
       </c>
       <c r="R14" t="n">
-        <v>6768378</v>
+        <v>6768306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1944,7 +1944,7 @@
         <v>127723512</v>
       </c>
       <c r="B15" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723517</v>
+        <v>127723561</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445463</v>
+        <v>445519</v>
       </c>
       <c r="R16" t="n">
-        <v>6768439</v>
+        <v>6768373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723435</v>
+        <v>127723442</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445375</v>
+        <v>445407</v>
       </c>
       <c r="R17" t="n">
-        <v>6768348</v>
+        <v>6768295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723442</v>
+        <v>127723520</v>
       </c>
       <c r="B18" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445407</v>
+        <v>445439</v>
       </c>
       <c r="R18" t="n">
-        <v>6768295</v>
+        <v>6768423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723520</v>
+        <v>127723517</v>
       </c>
       <c r="B19" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445439</v>
+        <v>445463</v>
       </c>
       <c r="R19" t="n">
-        <v>6768423</v>
+        <v>6768439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723561</v>
+        <v>127723435</v>
       </c>
       <c r="B20" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445519</v>
+        <v>445375</v>
       </c>
       <c r="R20" t="n">
-        <v>6768373</v>
+        <v>6768348</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2526,7 +2526,7 @@
         <v>127723500</v>
       </c>
       <c r="B21" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723412</v>
+        <v>127723527</v>
       </c>
       <c r="B22" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445423</v>
+        <v>445476</v>
       </c>
       <c r="R22" t="n">
-        <v>6768342</v>
+        <v>6768382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723417</v>
+        <v>127723412</v>
       </c>
       <c r="B23" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445413</v>
+        <v>445423</v>
       </c>
       <c r="R23" t="n">
-        <v>6768451</v>
+        <v>6768342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723433</v>
+        <v>127723417</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445354</v>
+        <v>445413</v>
       </c>
       <c r="R24" t="n">
-        <v>6768399</v>
+        <v>6768451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723525</v>
+        <v>127723433</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445465</v>
+        <v>445354</v>
       </c>
       <c r="R25" t="n">
-        <v>6768379</v>
+        <v>6768399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723527</v>
+        <v>127723525</v>
       </c>
       <c r="B26" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445476</v>
+        <v>445465</v>
       </c>
       <c r="R26" t="n">
-        <v>6768382</v>
+        <v>6768379</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723523</v>
+        <v>127723538</v>
       </c>
       <c r="B27" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445451</v>
+        <v>445485</v>
       </c>
       <c r="R27" t="n">
-        <v>6768402</v>
+        <v>6768313</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3205,7 +3205,7 @@
         <v>127723529</v>
       </c>
       <c r="B28" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723487</v>
+        <v>127723523</v>
       </c>
       <c r="B29" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445328</v>
+        <v>445451</v>
       </c>
       <c r="R29" t="n">
-        <v>6768445</v>
+        <v>6768402</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723428</v>
+        <v>127722895</v>
       </c>
       <c r="B30" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,34 +3407,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445329</v>
+        <v>445370</v>
       </c>
       <c r="R30" t="n">
-        <v>6768465</v>
+        <v>6768276</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723538</v>
+        <v>127723487</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3528,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445485</v>
+        <v>445328</v>
       </c>
       <c r="R31" t="n">
-        <v>6768313</v>
+        <v>6768445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3590,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722895</v>
+        <v>127723428</v>
       </c>
       <c r="B32" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,39 +3606,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445370</v>
+        <v>445329</v>
       </c>
       <c r="R32" t="n">
-        <v>6768276</v>
+        <v>6768465</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3797,7 +3797,7 @@
         <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>127723431</v>
       </c>
       <c r="B35" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723446</v>
+        <v>127723482</v>
       </c>
       <c r="B36" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445453</v>
+        <v>445318</v>
       </c>
       <c r="R36" t="n">
-        <v>6768321</v>
+        <v>6768474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4088,7 +4088,7 @@
         <v>127723515</v>
       </c>
       <c r="B37" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>127723536</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723482</v>
+        <v>127723446</v>
       </c>
       <c r="B39" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445318</v>
+        <v>445453</v>
       </c>
       <c r="R39" t="n">
-        <v>6768474</v>
+        <v>6768321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723427</v>
+        <v>127723565</v>
       </c>
       <c r="B40" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445322</v>
+        <v>445406</v>
       </c>
       <c r="R40" t="n">
-        <v>6768457</v>
+        <v>6768484</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4447,6 +4447,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4473,10 +4478,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723565</v>
+        <v>127723418</v>
       </c>
       <c r="B41" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4489,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445406</v>
+        <v>445411</v>
       </c>
       <c r="R41" t="n">
-        <v>6768484</v>
+        <v>6768470</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4544,11 +4549,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4575,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723422</v>
+        <v>127723427</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445332</v>
+        <v>445322</v>
       </c>
       <c r="R42" t="n">
-        <v>6768518</v>
+        <v>6768457</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723418</v>
+        <v>127723422</v>
       </c>
       <c r="B43" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445411</v>
+        <v>445332</v>
       </c>
       <c r="R43" t="n">
-        <v>6768470</v>
+        <v>6768518</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,45 +4769,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723534</v>
+        <v>127723025</v>
       </c>
       <c r="B44" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445528</v>
+        <v>445397</v>
       </c>
       <c r="R44" t="n">
-        <v>6768349</v>
+        <v>6768481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4834,12 +4839,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,45 +4871,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723521</v>
+        <v>127723026</v>
       </c>
       <c r="B45" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445445</v>
+        <v>445387</v>
       </c>
       <c r="R45" t="n">
-        <v>6768409</v>
+        <v>6768492</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4931,12 +4941,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4966,7 +4976,7 @@
         <v>127723604</v>
       </c>
       <c r="B46" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5063,7 +5073,7 @@
         <v>127723592</v>
       </c>
       <c r="B47" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,50 +5167,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723025</v>
+        <v>127723521</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445397</v>
+        <v>445445</v>
       </c>
       <c r="R48" t="n">
-        <v>6768481</v>
+        <v>6768409</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5227,12 +5232,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5259,50 +5264,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723026</v>
+        <v>127723534</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445387</v>
+        <v>445528</v>
       </c>
       <c r="R49" t="n">
-        <v>6768492</v>
+        <v>6768349</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5361,10 +5361,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723501</v>
+        <v>127723478</v>
       </c>
       <c r="B50" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445430</v>
+        <v>445305</v>
       </c>
       <c r="R50" t="n">
-        <v>6768379</v>
+        <v>6768502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723478</v>
+        <v>127723501</v>
       </c>
       <c r="B51" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445305</v>
+        <v>445430</v>
       </c>
       <c r="R51" t="n">
-        <v>6768502</v>
+        <v>6768379</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723425</v>
+        <v>127722889</v>
       </c>
       <c r="B52" t="n">
-        <v>79023</v>
+        <v>57669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,34 +5566,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445321</v>
+        <v>445372</v>
       </c>
       <c r="R52" t="n">
-        <v>6768501</v>
+        <v>6768323</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,10 +5657,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722829</v>
+        <v>127723430</v>
       </c>
       <c r="B53" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5663,21 +5668,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5687,10 +5692,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445339</v>
+        <v>445357</v>
       </c>
       <c r="R53" t="n">
-        <v>6768436</v>
+        <v>6768451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5717,12 +5722,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5752,7 +5757,7 @@
         <v>127723524</v>
       </c>
       <c r="B54" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5846,10 +5851,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722889</v>
+        <v>127723444</v>
       </c>
       <c r="B55" t="n">
-        <v>57663</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,39 +5862,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445372</v>
+        <v>445432</v>
       </c>
       <c r="R55" t="n">
-        <v>6768323</v>
+        <v>6768299</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5948,10 +5948,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723444</v>
+        <v>127723425</v>
       </c>
       <c r="B56" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445432</v>
+        <v>445321</v>
       </c>
       <c r="R56" t="n">
-        <v>6768299</v>
+        <v>6768501</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6045,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723430</v>
+        <v>127722829</v>
       </c>
       <c r="B57" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,21 +6056,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445357</v>
+        <v>445339</v>
       </c>
       <c r="R57" t="n">
-        <v>6768451</v>
+        <v>6768436</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6142,10 +6142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723488</v>
+        <v>127723492</v>
       </c>
       <c r="B58" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445340</v>
+        <v>445366</v>
       </c>
       <c r="R58" t="n">
-        <v>6768445</v>
+        <v>6768409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,10 +6239,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723499</v>
+        <v>127723488</v>
       </c>
       <c r="B59" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445418</v>
+        <v>445340</v>
       </c>
       <c r="R59" t="n">
-        <v>6768394</v>
+        <v>6768445</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723526</v>
+        <v>127723499</v>
       </c>
       <c r="B60" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445468</v>
+        <v>445418</v>
       </c>
       <c r="R60" t="n">
-        <v>6768377</v>
+        <v>6768394</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723492</v>
+        <v>127723526</v>
       </c>
       <c r="B61" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445366</v>
+        <v>445468</v>
       </c>
       <c r="R61" t="n">
-        <v>6768409</v>
+        <v>6768377</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>127722914</v>
       </c>
       <c r="B62" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>127723413</v>
       </c>
       <c r="B63" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723439</v>
+        <v>127723506</v>
       </c>
       <c r="B65" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445382</v>
+        <v>445509</v>
       </c>
       <c r="R65" t="n">
-        <v>6768296</v>
+        <v>6768424</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6936,7 +6936,7 @@
         <v>127723489</v>
       </c>
       <c r="B66" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7030,10 +7030,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723455</v>
+        <v>127723522</v>
       </c>
       <c r="B67" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445417</v>
+        <v>445457</v>
       </c>
       <c r="R67" t="n">
-        <v>6768483</v>
+        <v>6768411</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723522</v>
+        <v>127723511</v>
       </c>
       <c r="B68" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445457</v>
+        <v>445497</v>
       </c>
       <c r="R68" t="n">
-        <v>6768411</v>
+        <v>6768438</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7227,7 +7227,7 @@
         <v>127723528</v>
       </c>
       <c r="B69" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723519</v>
+        <v>127722917</v>
       </c>
       <c r="B70" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7332,34 +7332,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445434</v>
+        <v>445329</v>
       </c>
       <c r="R70" t="n">
-        <v>6768437</v>
+        <v>6768466</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7386,12 +7391,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7418,10 +7428,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723496</v>
+        <v>127722908</v>
       </c>
       <c r="B71" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7429,34 +7439,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445376</v>
+        <v>445329</v>
       </c>
       <c r="R71" t="n">
-        <v>6768426</v>
+        <v>6768474</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7483,12 +7498,17 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7515,45 +7535,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723511</v>
+        <v>127723034</v>
       </c>
       <c r="B72" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445497</v>
+        <v>445377</v>
       </c>
       <c r="R72" t="n">
-        <v>6768438</v>
+        <v>6768394</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,10 +7637,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723514</v>
+        <v>127723519</v>
       </c>
       <c r="B73" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7647,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445468</v>
+        <v>445434</v>
       </c>
       <c r="R73" t="n">
-        <v>6768439</v>
+        <v>6768437</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,10 +7734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723506</v>
+        <v>127723514</v>
       </c>
       <c r="B74" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7744,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445509</v>
+        <v>445468</v>
       </c>
       <c r="R74" t="n">
-        <v>6768424</v>
+        <v>6768439</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7806,10 +7831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722917</v>
+        <v>127723455</v>
       </c>
       <c r="B75" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,39 +7842,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445329</v>
+        <v>445417</v>
       </c>
       <c r="R75" t="n">
-        <v>6768466</v>
+        <v>6768483</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,17 +7896,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7913,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722908</v>
+        <v>127723439</v>
       </c>
       <c r="B76" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7924,39 +7939,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445329</v>
+        <v>445382</v>
       </c>
       <c r="R76" t="n">
-        <v>6768474</v>
+        <v>6768296</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7989,11 +7999,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8020,50 +8025,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723034</v>
+        <v>127723496</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445377</v>
+        <v>445376</v>
       </c>
       <c r="R77" t="n">
-        <v>6768394</v>
+        <v>6768426</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723415</v>
+        <v>127723494</v>
       </c>
       <c r="B78" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445355</v>
       </c>
       <c r="R78" t="n">
-        <v>6768387</v>
+        <v>6768420</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723411</v>
+        <v>127722825</v>
       </c>
       <c r="B79" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445410</v>
+        <v>445386</v>
       </c>
       <c r="R79" t="n">
-        <v>6768338</v>
+        <v>6768493</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,32 +8316,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723494</v>
+        <v>127723560</v>
       </c>
       <c r="B80" t="n">
-        <v>79023</v>
+        <v>92639</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445355</v>
+        <v>445433</v>
       </c>
       <c r="R80" t="n">
-        <v>6768420</v>
+        <v>6768412</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8413,10 +8413,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723537</v>
+        <v>127723423</v>
       </c>
       <c r="B81" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445488</v>
+        <v>445325</v>
       </c>
       <c r="R81" t="n">
-        <v>6768315</v>
+        <v>6768515</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8513,7 +8513,7 @@
         <v>127723533</v>
       </c>
       <c r="B82" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,32 +8607,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723560</v>
+        <v>127723415</v>
       </c>
       <c r="B83" t="n">
-        <v>92631</v>
+        <v>79029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445433</v>
+        <v>445422</v>
       </c>
       <c r="R83" t="n">
-        <v>6768412</v>
+        <v>6768387</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722825</v>
+        <v>127723411</v>
       </c>
       <c r="B84" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445386</v>
+        <v>445410</v>
       </c>
       <c r="R84" t="n">
-        <v>6768493</v>
+        <v>6768338</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723432</v>
+        <v>127723537</v>
       </c>
       <c r="B85" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445360</v>
+        <v>445488</v>
       </c>
       <c r="R85" t="n">
-        <v>6768399</v>
+        <v>6768315</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8866,12 +8866,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8898,10 +8898,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723423</v>
+        <v>127723420</v>
       </c>
       <c r="B86" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445325</v>
+        <v>445395</v>
       </c>
       <c r="R86" t="n">
-        <v>6768515</v>
+        <v>6768485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8995,10 +8995,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723420</v>
+        <v>127723432</v>
       </c>
       <c r="B87" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445395</v>
+        <v>445360</v>
       </c>
       <c r="R87" t="n">
-        <v>6768485</v>
+        <v>6768399</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9398,10 +9398,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723436</v>
+        <v>127723504</v>
       </c>
       <c r="B91" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445366</v>
+        <v>445449</v>
       </c>
       <c r="R91" t="n">
-        <v>6768321</v>
+        <v>6768387</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9495,10 +9495,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723426</v>
+        <v>127723436</v>
       </c>
       <c r="B92" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445324</v>
+        <v>445366</v>
       </c>
       <c r="R92" t="n">
-        <v>6768470</v>
+        <v>6768321</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9595,7 +9595,7 @@
         <v>127723452</v>
       </c>
       <c r="B93" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9689,10 +9689,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723497</v>
+        <v>127723414</v>
       </c>
       <c r="B94" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445376</v>
+        <v>445429</v>
       </c>
       <c r="R94" t="n">
-        <v>6768407</v>
+        <v>6768360</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,10 +9786,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723504</v>
+        <v>127723426</v>
       </c>
       <c r="B95" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445449</v>
+        <v>445324</v>
       </c>
       <c r="R95" t="n">
-        <v>6768387</v>
+        <v>6768470</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9883,10 +9883,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723414</v>
+        <v>127723497</v>
       </c>
       <c r="B96" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445429</v>
+        <v>445376</v>
       </c>
       <c r="R96" t="n">
-        <v>6768360</v>
+        <v>6768407</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,12 +9948,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127722918</v>
+        <v>127723440</v>
       </c>
       <c r="B98" t="n">
-        <v>57666</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,39 +10093,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445382</v>
+        <v>445394</v>
       </c>
       <c r="R98" t="n">
-        <v>6768422</v>
+        <v>6768290</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10152,17 +10147,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10189,50 +10179,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723027</v>
+        <v>127723535</v>
       </c>
       <c r="B99" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445343</v>
+        <v>445518</v>
       </c>
       <c r="R99" t="n">
-        <v>6768460</v>
+        <v>6768343</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10259,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10291,10 +10276,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722864</v>
+        <v>127723483</v>
       </c>
       <c r="B100" t="n">
-        <v>91341</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10302,21 +10287,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10326,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445327</v>
+        <v>445310</v>
       </c>
       <c r="R100" t="n">
-        <v>6768444</v>
+        <v>6768467</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10388,10 +10373,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723490</v>
+        <v>127722918</v>
       </c>
       <c r="B101" t="n">
-        <v>79023</v>
+        <v>57672</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10399,34 +10384,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445353</v>
+        <v>445382</v>
       </c>
       <c r="R101" t="n">
-        <v>6768438</v>
+        <v>6768422</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10459,6 +10449,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10485,10 +10480,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723447</v>
+        <v>127722864</v>
       </c>
       <c r="B102" t="n">
-        <v>79023</v>
+        <v>91349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10496,21 +10491,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10520,10 +10515,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445458</v>
+        <v>445327</v>
       </c>
       <c r="R102" t="n">
-        <v>6768338</v>
+        <v>6768444</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10550,12 +10545,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10582,10 +10577,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723483</v>
+        <v>127723605</v>
       </c>
       <c r="B103" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10593,21 +10588,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10617,10 +10612,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445310</v>
+        <v>445403</v>
       </c>
       <c r="R103" t="n">
-        <v>6768467</v>
+        <v>6768385</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10682,7 +10677,7 @@
         <v>127723454</v>
       </c>
       <c r="B104" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10776,10 +10771,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723605</v>
+        <v>127723490</v>
       </c>
       <c r="B105" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10787,21 +10782,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10811,10 +10806,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445403</v>
+        <v>445353</v>
       </c>
       <c r="R105" t="n">
-        <v>6768385</v>
+        <v>6768438</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10873,10 +10868,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723440</v>
+        <v>127723447</v>
       </c>
       <c r="B106" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10908,10 +10903,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445394</v>
+        <v>445458</v>
       </c>
       <c r="R106" t="n">
-        <v>6768290</v>
+        <v>6768338</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10970,45 +10965,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723535</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>79023</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445518</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768343</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11070,7 +11070,7 @@
         <v>127723593</v>
       </c>
       <c r="B108" t="n">
-        <v>78690</v>
+        <v>78696</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>127723495</v>
       </c>
       <c r="B109" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>127723481</v>
       </c>
       <c r="B110" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>127723429</v>
       </c>
       <c r="B111" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>127722832</v>
       </c>
       <c r="B112" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723607</v>
+        <v>127723441</v>
       </c>
       <c r="B113" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445529</v>
+        <v>445408</v>
       </c>
       <c r="R113" t="n">
-        <v>6768354</v>
+        <v>6768287</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11617,12 +11617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723532</v>
+        <v>127723607</v>
       </c>
       <c r="B114" t="n">
-        <v>79023</v>
+        <v>78696</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445523</v>
+        <v>445529</v>
       </c>
       <c r="R114" t="n">
-        <v>6768362</v>
+        <v>6768354</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723453</v>
+        <v>127723530</v>
       </c>
       <c r="B115" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445418</v>
+        <v>445515</v>
       </c>
       <c r="R115" t="n">
-        <v>6768439</v>
+        <v>6768378</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11846,7 +11846,7 @@
         <v>127723498</v>
       </c>
       <c r="B116" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11940,10 +11940,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B117" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R117" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723441</v>
+        <v>127723453</v>
       </c>
       <c r="B118" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445408</v>
+        <v>445418</v>
       </c>
       <c r="R118" t="n">
-        <v>6768287</v>
+        <v>6768439</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12102,12 +12102,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723410</v>
+        <v>127723443</v>
       </c>
       <c r="B119" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445434</v>
+        <v>445422</v>
       </c>
       <c r="R119" t="n">
-        <v>6768336</v>
+        <v>6768295</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12234,7 +12234,7 @@
         <v>127722831</v>
       </c>
       <c r="B120" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723505</v>
+        <v>127723410</v>
       </c>
       <c r="B121" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445493</v>
+        <v>445434</v>
       </c>
       <c r="R121" t="n">
-        <v>6768418</v>
+        <v>6768336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12428,7 +12428,7 @@
         <v>127723503</v>
       </c>
       <c r="B122" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12522,10 +12522,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723443</v>
+        <v>127723438</v>
       </c>
       <c r="B123" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445422</v>
+        <v>445375</v>
       </c>
       <c r="R123" t="n">
-        <v>6768295</v>
+        <v>6768277</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723438</v>
+        <v>127723505</v>
       </c>
       <c r="B124" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445375</v>
+        <v>445493</v>
       </c>
       <c r="R124" t="n">
-        <v>6768277</v>
+        <v>6768418</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723479</v>
+        <v>127723480</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445309</v>
+        <v>445314</v>
       </c>
       <c r="R2" t="n">
-        <v>6768491</v>
+        <v>6768485</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723421</v>
+        <v>127723531</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445361</v>
+        <v>445524</v>
       </c>
       <c r="R3" t="n">
-        <v>6768495</v>
+        <v>6768371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723424</v>
+        <v>127723493</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445311</v>
+        <v>445363</v>
       </c>
       <c r="R4" t="n">
-        <v>6768500</v>
+        <v>6768410</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723434</v>
+        <v>127723518</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445345</v>
+        <v>445431</v>
       </c>
       <c r="R5" t="n">
-        <v>6768366</v>
+        <v>6768443</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723480</v>
+        <v>127723479</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445314</v>
+        <v>445309</v>
       </c>
       <c r="R6" t="n">
-        <v>6768485</v>
+        <v>6768491</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723416</v>
+        <v>127723434</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445426</v>
+        <v>445345</v>
       </c>
       <c r="R7" t="n">
-        <v>6768417</v>
+        <v>6768366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723493</v>
+        <v>127723421</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445363</v>
+        <v>445361</v>
       </c>
       <c r="R8" t="n">
-        <v>6768410</v>
+        <v>6768495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723531</v>
+        <v>127723416</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445524</v>
+        <v>445426</v>
       </c>
       <c r="R9" t="n">
-        <v>6768371</v>
+        <v>6768417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723518</v>
+        <v>127723424</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445431</v>
+        <v>445311</v>
       </c>
       <c r="R10" t="n">
-        <v>6768443</v>
+        <v>6768500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723561</v>
+        <v>127723435</v>
       </c>
       <c r="B16" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445519</v>
+        <v>445375</v>
       </c>
       <c r="R16" t="n">
-        <v>6768373</v>
+        <v>6768348</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723517</v>
+        <v>127723561</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445463</v>
+        <v>445519</v>
       </c>
       <c r="R19" t="n">
-        <v>6768439</v>
+        <v>6768373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R20" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723527</v>
+        <v>127723412</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445476</v>
+        <v>445423</v>
       </c>
       <c r="R22" t="n">
-        <v>6768382</v>
+        <v>6768342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R23" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723417</v>
+        <v>127723527</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445413</v>
+        <v>445476</v>
       </c>
       <c r="R24" t="n">
-        <v>6768451</v>
+        <v>6768382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723433</v>
+        <v>127723417</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445354</v>
+        <v>445413</v>
       </c>
       <c r="R25" t="n">
-        <v>6768399</v>
+        <v>6768451</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723525</v>
+        <v>127723433</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445465</v>
+        <v>445354</v>
       </c>
       <c r="R26" t="n">
-        <v>6768379</v>
+        <v>6768399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,7 +3105,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723538</v>
+        <v>127723523</v>
       </c>
       <c r="B27" t="n">
         <v>79029</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445485</v>
+        <v>445451</v>
       </c>
       <c r="R27" t="n">
-        <v>6768313</v>
+        <v>6768402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723523</v>
+        <v>127723538</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445451</v>
+        <v>445485</v>
       </c>
       <c r="R29" t="n">
-        <v>6768402</v>
+        <v>6768313</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3498,45 +3498,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723487</v>
+        <v>127723028</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445328</v>
+        <v>445345</v>
       </c>
       <c r="R31" t="n">
-        <v>6768445</v>
+        <v>6768382</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,12 +3568,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3595,7 +3600,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723428</v>
+        <v>127723487</v>
       </c>
       <c r="B32" t="n">
         <v>79029</v>
@@ -3630,10 +3635,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445329</v>
+        <v>445328</v>
       </c>
       <c r="R32" t="n">
-        <v>6768465</v>
+        <v>6768445</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,12 +3665,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3692,50 +3697,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723028</v>
+        <v>127723428</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445345</v>
+        <v>445329</v>
       </c>
       <c r="R33" t="n">
-        <v>6768382</v>
+        <v>6768465</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723603</v>
+        <v>127723536</v>
       </c>
       <c r="B34" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445353</v>
+        <v>445500</v>
       </c>
       <c r="R34" t="n">
-        <v>6768433</v>
+        <v>6768348</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723431</v>
+        <v>127723446</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445369</v>
+        <v>445453</v>
       </c>
       <c r="R35" t="n">
-        <v>6768408</v>
+        <v>6768321</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723482</v>
+        <v>127723603</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445318</v>
+        <v>445353</v>
       </c>
       <c r="R36" t="n">
-        <v>6768474</v>
+        <v>6768433</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723515</v>
+        <v>127723431</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445465</v>
+        <v>445369</v>
       </c>
       <c r="R37" t="n">
-        <v>6768438</v>
+        <v>6768408</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723482</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445318</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768474</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723446</v>
+        <v>127723515</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445453</v>
+        <v>445465</v>
       </c>
       <c r="R39" t="n">
-        <v>6768321</v>
+        <v>6768438</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4478,7 +4478,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723418</v>
+        <v>127723427</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445411</v>
+        <v>445322</v>
       </c>
       <c r="R41" t="n">
-        <v>6768470</v>
+        <v>6768457</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,7 +4575,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723427</v>
+        <v>127723418</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445322</v>
+        <v>445411</v>
       </c>
       <c r="R42" t="n">
-        <v>6768457</v>
+        <v>6768470</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4973,10 +4973,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723604</v>
+        <v>127723534</v>
       </c>
       <c r="B46" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4984,21 +4984,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445370</v>
+        <v>445528</v>
       </c>
       <c r="R46" t="n">
-        <v>6768425</v>
+        <v>6768349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,7 +5070,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723592</v>
+        <v>127723604</v>
       </c>
       <c r="B47" t="n">
         <v>78696</v>
@@ -5108,7 +5108,7 @@
         <v>445370</v>
       </c>
       <c r="R47" t="n">
-        <v>6768478</v>
+        <v>6768425</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5135,12 +5135,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5167,10 +5167,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723521</v>
+        <v>127723592</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5178,21 +5178,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445445</v>
+        <v>445370</v>
       </c>
       <c r="R48" t="n">
-        <v>6768409</v>
+        <v>6768478</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5232,12 +5232,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5264,7 +5264,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723534</v>
+        <v>127723521</v>
       </c>
       <c r="B49" t="n">
         <v>79029</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445528</v>
+        <v>445445</v>
       </c>
       <c r="R49" t="n">
-        <v>6768349</v>
+        <v>6768409</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723478</v>
+        <v>127723501</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445305</v>
+        <v>445430</v>
       </c>
       <c r="R50" t="n">
-        <v>6768502</v>
+        <v>6768379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723501</v>
+        <v>127723478</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445430</v>
+        <v>445305</v>
       </c>
       <c r="R51" t="n">
-        <v>6768379</v>
+        <v>6768502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722889</v>
+        <v>127722829</v>
       </c>
       <c r="B52" t="n">
-        <v>57669</v>
+        <v>79647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,39 +5566,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445372</v>
+        <v>445339</v>
       </c>
       <c r="R52" t="n">
-        <v>6768323</v>
+        <v>6768436</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5625,12 +5620,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5657,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127722889</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5668,34 +5663,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445372</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768323</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723524</v>
+        <v>127723444</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445455</v>
+        <v>445432</v>
       </c>
       <c r="R54" t="n">
-        <v>6768391</v>
+        <v>6768299</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5851,7 +5851,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723444</v>
+        <v>127723425</v>
       </c>
       <c r="B55" t="n">
         <v>79029</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445432</v>
+        <v>445321</v>
       </c>
       <c r="R55" t="n">
-        <v>6768299</v>
+        <v>6768501</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5948,7 +5948,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723425</v>
+        <v>127723524</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445321</v>
+        <v>445455</v>
       </c>
       <c r="R56" t="n">
-        <v>6768501</v>
+        <v>6768391</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6013,12 +6013,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6045,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722829</v>
+        <v>127723430</v>
       </c>
       <c r="B57" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,21 +6056,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445339</v>
+        <v>445357</v>
       </c>
       <c r="R57" t="n">
-        <v>6768436</v>
+        <v>6768451</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6142,7 +6142,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723492</v>
+        <v>127723488</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445366</v>
+        <v>445340</v>
       </c>
       <c r="R58" t="n">
-        <v>6768409</v>
+        <v>6768445</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723488</v>
+        <v>127723526</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445340</v>
+        <v>445468</v>
       </c>
       <c r="R59" t="n">
-        <v>6768445</v>
+        <v>6768377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723526</v>
+        <v>127723492</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445468</v>
+        <v>445366</v>
       </c>
       <c r="R61" t="n">
-        <v>6768377</v>
+        <v>6768409</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,39 +6541,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R62" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,11 +6601,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6637,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723413</v>
+        <v>127722872</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6648,34 +6638,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445444</v>
+        <v>445414</v>
       </c>
       <c r="R63" t="n">
-        <v>6768341</v>
+        <v>6768450</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6734,10 +6729,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722872</v>
+        <v>127722914</v>
       </c>
       <c r="B64" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6745,27 +6740,27 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -6774,10 +6769,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445325</v>
       </c>
       <c r="R64" t="n">
-        <v>6768450</v>
+        <v>6768463</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6810,6 +6805,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6836,7 +6836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723506</v>
+        <v>127723439</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445509</v>
+        <v>445382</v>
       </c>
       <c r="R65" t="n">
-        <v>6768424</v>
+        <v>6768296</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723489</v>
+        <v>127723506</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445349</v>
+        <v>445509</v>
       </c>
       <c r="R66" t="n">
-        <v>6768438</v>
+        <v>6768424</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723522</v>
+        <v>127723489</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445457</v>
+        <v>445349</v>
       </c>
       <c r="R67" t="n">
-        <v>6768411</v>
+        <v>6768438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723511</v>
+        <v>127723455</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445497</v>
+        <v>445417</v>
       </c>
       <c r="R68" t="n">
-        <v>6768438</v>
+        <v>6768483</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723528</v>
+        <v>127723522</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445493</v>
+        <v>445457</v>
       </c>
       <c r="R69" t="n">
-        <v>6768388</v>
+        <v>6768411</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127722917</v>
+        <v>127723519</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7332,39 +7332,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445329</v>
+        <v>445434</v>
       </c>
       <c r="R70" t="n">
-        <v>6768466</v>
+        <v>6768437</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7391,17 +7386,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7428,10 +7418,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127722908</v>
+        <v>127723528</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7439,39 +7429,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445329</v>
+        <v>445493</v>
       </c>
       <c r="R71" t="n">
-        <v>6768474</v>
+        <v>6768388</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7498,17 +7483,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7535,50 +7515,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723034</v>
+        <v>127723514</v>
       </c>
       <c r="B72" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445377</v>
+        <v>445468</v>
       </c>
       <c r="R72" t="n">
-        <v>6768394</v>
+        <v>6768439</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7637,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723519</v>
+        <v>127723496</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -7672,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445434</v>
+        <v>445376</v>
       </c>
       <c r="R73" t="n">
-        <v>6768437</v>
+        <v>6768426</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7734,7 +7709,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723514</v>
+        <v>127723511</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7769,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445468</v>
+        <v>445497</v>
       </c>
       <c r="R74" t="n">
-        <v>6768439</v>
+        <v>6768438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723455</v>
+        <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,34 +7817,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445417</v>
+        <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768483</v>
+        <v>6768466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7896,12 +7876,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7928,10 +7913,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723439</v>
+        <v>127722908</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7939,34 +7924,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445382</v>
+        <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768296</v>
+        <v>6768474</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7999,6 +7989,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8025,45 +8020,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723496</v>
+        <v>127723034</v>
       </c>
       <c r="B77" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445376</v>
+        <v>445377</v>
       </c>
       <c r="R77" t="n">
-        <v>6768426</v>
+        <v>6768394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,32 +8122,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723494</v>
+        <v>127723560</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445355</v>
+        <v>445433</v>
       </c>
       <c r="R78" t="n">
-        <v>6768420</v>
+        <v>6768412</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8316,32 +8316,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723560</v>
+        <v>127723415</v>
       </c>
       <c r="B80" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445433</v>
+        <v>445422</v>
       </c>
       <c r="R80" t="n">
-        <v>6768412</v>
+        <v>6768387</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8381,12 +8381,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8413,7 +8413,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723423</v>
+        <v>127723411</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445325</v>
+        <v>445410</v>
       </c>
       <c r="R81" t="n">
-        <v>6768515</v>
+        <v>6768338</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723533</v>
+        <v>127723537</v>
       </c>
       <c r="B82" t="n">
         <v>79029</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445523</v>
+        <v>445488</v>
       </c>
       <c r="R82" t="n">
-        <v>6768356</v>
+        <v>6768315</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8607,7 +8607,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723415</v>
+        <v>127723533</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445422</v>
+        <v>445523</v>
       </c>
       <c r="R83" t="n">
-        <v>6768387</v>
+        <v>6768356</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8672,12 +8672,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,7 +8704,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723411</v>
+        <v>127723432</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445410</v>
+        <v>445360</v>
       </c>
       <c r="R84" t="n">
-        <v>6768338</v>
+        <v>6768399</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,7 +8801,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723537</v>
+        <v>127723423</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445488</v>
+        <v>445325</v>
       </c>
       <c r="R85" t="n">
-        <v>6768315</v>
+        <v>6768515</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8866,12 +8866,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8898,45 +8898,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723420</v>
+        <v>127722931</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445395</v>
+        <v>445518</v>
       </c>
       <c r="R86" t="n">
-        <v>6768485</v>
+        <v>6768355</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8995,7 +9000,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723432</v>
+        <v>127723494</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9030,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445360</v>
+        <v>445355</v>
       </c>
       <c r="R87" t="n">
-        <v>6768399</v>
+        <v>6768420</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9060,12 +9065,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9092,50 +9097,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722931</v>
+        <v>127723420</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445518</v>
+        <v>445395</v>
       </c>
       <c r="R88" t="n">
-        <v>6768355</v>
+        <v>6768485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723504</v>
+        <v>127723497</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445449</v>
+        <v>445376</v>
       </c>
       <c r="R91" t="n">
-        <v>6768387</v>
+        <v>6768407</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723436</v>
+        <v>127723504</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445366</v>
+        <v>445449</v>
       </c>
       <c r="R92" t="n">
-        <v>6768321</v>
+        <v>6768387</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723452</v>
+        <v>127723426</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445473</v>
+        <v>445324</v>
       </c>
       <c r="R93" t="n">
-        <v>6768325</v>
+        <v>6768470</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723414</v>
+        <v>127723452</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445429</v>
+        <v>445473</v>
       </c>
       <c r="R94" t="n">
-        <v>6768360</v>
+        <v>6768325</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723426</v>
+        <v>127723414</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445324</v>
+        <v>445429</v>
       </c>
       <c r="R95" t="n">
-        <v>6768470</v>
+        <v>6768360</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9883,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723497</v>
+        <v>127723436</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445376</v>
+        <v>445366</v>
       </c>
       <c r="R96" t="n">
-        <v>6768407</v>
+        <v>6768321</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,12 +9948,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10082,45 +10082,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723440</v>
+        <v>127723027</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445394</v>
+        <v>445343</v>
       </c>
       <c r="R98" t="n">
-        <v>6768290</v>
+        <v>6768460</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,10 +10184,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723535</v>
+        <v>127723605</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10190,21 +10195,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10214,10 +10219,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445518</v>
+        <v>445403</v>
       </c>
       <c r="R99" t="n">
-        <v>6768343</v>
+        <v>6768385</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10276,10 +10281,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723483</v>
+        <v>127722864</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>91350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10287,21 +10292,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10311,10 +10316,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445310</v>
+        <v>445327</v>
       </c>
       <c r="R100" t="n">
-        <v>6768467</v>
+        <v>6768444</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10373,10 +10378,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127722918</v>
+        <v>127723440</v>
       </c>
       <c r="B101" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10384,39 +10389,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445382</v>
+        <v>445394</v>
       </c>
       <c r="R101" t="n">
-        <v>6768422</v>
+        <v>6768290</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,17 +10443,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10480,10 +10475,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127722864</v>
+        <v>127723490</v>
       </c>
       <c r="B102" t="n">
-        <v>91349</v>
+        <v>79029</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10491,21 +10486,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10515,10 +10510,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445327</v>
+        <v>445353</v>
       </c>
       <c r="R102" t="n">
-        <v>6768444</v>
+        <v>6768438</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10577,10 +10572,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723605</v>
+        <v>127723447</v>
       </c>
       <c r="B103" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10588,21 +10583,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10612,10 +10607,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445403</v>
+        <v>445458</v>
       </c>
       <c r="R103" t="n">
-        <v>6768385</v>
+        <v>6768338</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10642,12 +10637,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10674,7 +10669,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723454</v>
+        <v>127723535</v>
       </c>
       <c r="B104" t="n">
         <v>79029</v>
@@ -10709,10 +10704,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445421</v>
+        <v>445518</v>
       </c>
       <c r="R104" t="n">
-        <v>6768465</v>
+        <v>6768343</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10771,7 +10766,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723490</v>
+        <v>127723483</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10806,10 +10801,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445353</v>
+        <v>445310</v>
       </c>
       <c r="R105" t="n">
-        <v>6768438</v>
+        <v>6768467</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10868,7 +10863,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723447</v>
+        <v>127723454</v>
       </c>
       <c r="B106" t="n">
         <v>79029</v>
@@ -10903,10 +10898,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445458</v>
+        <v>445421</v>
       </c>
       <c r="R106" t="n">
-        <v>6768338</v>
+        <v>6768465</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10933,12 +10928,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10965,38 +10960,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127722918</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>57672</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11005,10 +11000,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445382</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768422</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11030,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11164,7 +11164,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723495</v>
+        <v>127723429</v>
       </c>
       <c r="B109" t="n">
         <v>79029</v>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445361</v>
+        <v>445339</v>
       </c>
       <c r="R109" t="n">
-        <v>6768425</v>
+        <v>6768457</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11229,12 +11229,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11261,7 +11261,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723481</v>
+        <v>127723495</v>
       </c>
       <c r="B110" t="n">
         <v>79029</v>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445320</v>
+        <v>445361</v>
       </c>
       <c r="R110" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11358,7 +11358,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723429</v>
+        <v>127723481</v>
       </c>
       <c r="B111" t="n">
         <v>79029</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445339</v>
+        <v>445320</v>
       </c>
       <c r="R111" t="n">
-        <v>6768457</v>
+        <v>6768481</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723441</v>
+        <v>127723607</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445408</v>
+        <v>445529</v>
       </c>
       <c r="R113" t="n">
-        <v>6768287</v>
+        <v>6768354</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11617,12 +11617,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723607</v>
+        <v>127723530</v>
       </c>
       <c r="B114" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445529</v>
+        <v>445515</v>
       </c>
       <c r="R114" t="n">
-        <v>6768354</v>
+        <v>6768378</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R115" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11843,7 +11843,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723498</v>
+        <v>127723453</v>
       </c>
       <c r="B116" t="n">
         <v>79029</v>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445386</v>
+        <v>445418</v>
       </c>
       <c r="R116" t="n">
-        <v>6768393</v>
+        <v>6768439</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723532</v>
+        <v>127723498</v>
       </c>
       <c r="B117" t="n">
         <v>79029</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445523</v>
+        <v>445386</v>
       </c>
       <c r="R117" t="n">
-        <v>6768362</v>
+        <v>6768393</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723453</v>
+        <v>127723441</v>
       </c>
       <c r="B118" t="n">
         <v>79029</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445418</v>
+        <v>445408</v>
       </c>
       <c r="R118" t="n">
-        <v>6768439</v>
+        <v>6768287</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12102,12 +12102,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12134,7 +12134,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723443</v>
+        <v>127723438</v>
       </c>
       <c r="B119" t="n">
         <v>79029</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445422</v>
+        <v>445375</v>
       </c>
       <c r="R119" t="n">
-        <v>6768295</v>
+        <v>6768277</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12231,10 +12231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127722831</v>
+        <v>127723410</v>
       </c>
       <c r="B120" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12242,21 +12242,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445370</v>
+        <v>445434</v>
       </c>
       <c r="R120" t="n">
-        <v>6768425</v>
+        <v>6768336</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,7 +12328,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723410</v>
+        <v>127723503</v>
       </c>
       <c r="B121" t="n">
         <v>79029</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445434</v>
+        <v>445439</v>
       </c>
       <c r="R121" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723503</v>
+        <v>127723443</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445439</v>
+        <v>445422</v>
       </c>
       <c r="R122" t="n">
-        <v>6768381</v>
+        <v>6768295</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723438</v>
+        <v>127723505</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445375</v>
+        <v>445493</v>
       </c>
       <c r="R123" t="n">
-        <v>6768277</v>
+        <v>6768418</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723505</v>
+        <v>127722831</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445493</v>
+        <v>445370</v>
       </c>
       <c r="R124" t="n">
-        <v>6768418</v>
+        <v>6768425</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723480</v>
+        <v>127723518</v>
       </c>
       <c r="B2" t="n">
         <v>79029</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445314</v>
+        <v>445431</v>
       </c>
       <c r="R2" t="n">
-        <v>6768485</v>
+        <v>6768443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723531</v>
+        <v>127723479</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445524</v>
+        <v>445309</v>
       </c>
       <c r="R3" t="n">
-        <v>6768371</v>
+        <v>6768491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723493</v>
+        <v>127723434</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445363</v>
+        <v>445345</v>
       </c>
       <c r="R4" t="n">
-        <v>6768410</v>
+        <v>6768366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723518</v>
+        <v>127723480</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445431</v>
+        <v>445314</v>
       </c>
       <c r="R5" t="n">
-        <v>6768443</v>
+        <v>6768485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723479</v>
+        <v>127723421</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445309</v>
+        <v>445361</v>
       </c>
       <c r="R6" t="n">
-        <v>6768491</v>
+        <v>6768495</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723434</v>
+        <v>127723416</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445345</v>
+        <v>445426</v>
       </c>
       <c r="R7" t="n">
-        <v>6768366</v>
+        <v>6768417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723421</v>
+        <v>127723493</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445363</v>
       </c>
       <c r="R8" t="n">
-        <v>6768495</v>
+        <v>6768410</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723416</v>
+        <v>127723531</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445426</v>
+        <v>445524</v>
       </c>
       <c r="R9" t="n">
-        <v>6768417</v>
+        <v>6768371</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2038,7 +2038,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B16" t="n">
         <v>79029</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R16" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723442</v>
+        <v>127723435</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445407</v>
+        <v>445375</v>
       </c>
       <c r="R17" t="n">
-        <v>6768295</v>
+        <v>6768348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723561</v>
+        <v>127723442</v>
       </c>
       <c r="B19" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445519</v>
+        <v>445407</v>
       </c>
       <c r="R19" t="n">
-        <v>6768373</v>
+        <v>6768295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723517</v>
+        <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>92640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445463</v>
+        <v>445519</v>
       </c>
       <c r="R20" t="n">
-        <v>6768439</v>
+        <v>6768373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3105,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723523</v>
+        <v>127722895</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3116,34 +3116,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445451</v>
+        <v>445370</v>
       </c>
       <c r="R27" t="n">
-        <v>6768402</v>
+        <v>6768276</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3170,12 +3175,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3202,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723529</v>
+        <v>127723523</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3237,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445507</v>
+        <v>445451</v>
       </c>
       <c r="R28" t="n">
-        <v>6768383</v>
+        <v>6768402</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,7 +3304,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723538</v>
+        <v>127723529</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3334,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445485</v>
+        <v>445507</v>
       </c>
       <c r="R29" t="n">
-        <v>6768313</v>
+        <v>6768383</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127722895</v>
+        <v>127723538</v>
       </c>
       <c r="B30" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3407,39 +3412,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445370</v>
+        <v>445485</v>
       </c>
       <c r="R30" t="n">
-        <v>6768276</v>
+        <v>6768313</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,50 +3498,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723028</v>
+        <v>127723487</v>
       </c>
       <c r="B31" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445345</v>
+        <v>445328</v>
       </c>
       <c r="R31" t="n">
-        <v>6768382</v>
+        <v>6768445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3568,12 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3600,45 +3595,50 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723487</v>
+        <v>127723028</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445328</v>
+        <v>445345</v>
       </c>
       <c r="R32" t="n">
-        <v>6768445</v>
+        <v>6768382</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3665,12 +3665,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723536</v>
+        <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445500</v>
+        <v>445353</v>
       </c>
       <c r="R34" t="n">
-        <v>6768348</v>
+        <v>6768433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723446</v>
+        <v>127723431</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445453</v>
+        <v>445369</v>
       </c>
       <c r="R35" t="n">
-        <v>6768321</v>
+        <v>6768408</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723603</v>
+        <v>127723536</v>
       </c>
       <c r="B36" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445353</v>
+        <v>445500</v>
       </c>
       <c r="R36" t="n">
-        <v>6768433</v>
+        <v>6768348</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723431</v>
+        <v>127723482</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445369</v>
+        <v>445318</v>
       </c>
       <c r="R37" t="n">
-        <v>6768408</v>
+        <v>6768474</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723482</v>
+        <v>127723446</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445318</v>
+        <v>445453</v>
       </c>
       <c r="R38" t="n">
-        <v>6768474</v>
+        <v>6768321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4478,7 +4478,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723427</v>
+        <v>127723422</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4513,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445322</v>
+        <v>445332</v>
       </c>
       <c r="R41" t="n">
-        <v>6768457</v>
+        <v>6768518</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,7 +4575,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723418</v>
+        <v>127723427</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445411</v>
+        <v>445322</v>
       </c>
       <c r="R42" t="n">
-        <v>6768470</v>
+        <v>6768457</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723422</v>
+        <v>127723418</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445332</v>
+        <v>445411</v>
       </c>
       <c r="R43" t="n">
-        <v>6768518</v>
+        <v>6768470</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,50 +4769,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723025</v>
+        <v>127723534</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445397</v>
+        <v>445528</v>
       </c>
       <c r="R44" t="n">
-        <v>6768481</v>
+        <v>6768349</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4839,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4871,50 +4866,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723026</v>
+        <v>127723521</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445387</v>
+        <v>445445</v>
       </c>
       <c r="R45" t="n">
-        <v>6768492</v>
+        <v>6768409</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4941,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4973,10 +4963,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723534</v>
+        <v>127723604</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4984,21 +4974,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5008,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445528</v>
+        <v>445370</v>
       </c>
       <c r="R46" t="n">
-        <v>6768349</v>
+        <v>6768425</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5070,7 +5060,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723604</v>
+        <v>127723592</v>
       </c>
       <c r="B47" t="n">
         <v>78696</v>
@@ -5108,7 +5098,7 @@
         <v>445370</v>
       </c>
       <c r="R47" t="n">
-        <v>6768425</v>
+        <v>6768478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5135,12 +5125,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5167,45 +5157,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723592</v>
+        <v>127723025</v>
       </c>
       <c r="B48" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R48" t="n">
-        <v>6768478</v>
+        <v>6768481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,45 +5259,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723521</v>
+        <v>127723026</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445445</v>
+        <v>445387</v>
       </c>
       <c r="R49" t="n">
-        <v>6768409</v>
+        <v>6768492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722829</v>
+        <v>127722889</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>57669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,34 +5566,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445339</v>
+        <v>445372</v>
       </c>
       <c r="R52" t="n">
-        <v>6768436</v>
+        <v>6768323</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5620,12 +5625,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5652,10 +5657,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722889</v>
+        <v>127723444</v>
       </c>
       <c r="B53" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5663,39 +5668,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445372</v>
+        <v>445432</v>
       </c>
       <c r="R53" t="n">
-        <v>6768323</v>
+        <v>6768299</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723444</v>
+        <v>127723430</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445432</v>
+        <v>445357</v>
       </c>
       <c r="R54" t="n">
-        <v>6768299</v>
+        <v>6768451</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723425</v>
+        <v>127722829</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5862,21 +5862,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445321</v>
+        <v>445339</v>
       </c>
       <c r="R55" t="n">
-        <v>6768501</v>
+        <v>6768436</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6045,7 +6045,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723430</v>
+        <v>127723425</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445357</v>
+        <v>445321</v>
       </c>
       <c r="R57" t="n">
-        <v>6768451</v>
+        <v>6768501</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723488</v>
+        <v>127723499</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445340</v>
+        <v>445418</v>
       </c>
       <c r="R58" t="n">
-        <v>6768445</v>
+        <v>6768394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723499</v>
+        <v>127723492</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445418</v>
+        <v>445366</v>
       </c>
       <c r="R60" t="n">
-        <v>6768394</v>
+        <v>6768409</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723492</v>
+        <v>127723488</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445366</v>
+        <v>445340</v>
       </c>
       <c r="R61" t="n">
-        <v>6768409</v>
+        <v>6768445</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723413</v>
+        <v>127722914</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,34 +6541,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445444</v>
+        <v>445325</v>
       </c>
       <c r="R62" t="n">
-        <v>6768341</v>
+        <v>6768463</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6601,6 +6606,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6729,10 +6739,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6740,39 +6750,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R64" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6805,11 +6810,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6836,7 +6836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723439</v>
+        <v>127723506</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445382</v>
+        <v>445509</v>
       </c>
       <c r="R65" t="n">
-        <v>6768296</v>
+        <v>6768424</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723506</v>
+        <v>127723489</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445509</v>
+        <v>445349</v>
       </c>
       <c r="R66" t="n">
-        <v>6768424</v>
+        <v>6768438</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723489</v>
+        <v>127723522</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445349</v>
+        <v>445457</v>
       </c>
       <c r="R67" t="n">
-        <v>6768438</v>
+        <v>6768411</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723455</v>
+        <v>127723519</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445417</v>
+        <v>445434</v>
       </c>
       <c r="R68" t="n">
-        <v>6768483</v>
+        <v>6768437</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723522</v>
+        <v>127723496</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445457</v>
+        <v>445376</v>
       </c>
       <c r="R69" t="n">
-        <v>6768411</v>
+        <v>6768426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,7 +7321,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723519</v>
+        <v>127723455</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445434</v>
+        <v>445417</v>
       </c>
       <c r="R70" t="n">
-        <v>6768437</v>
+        <v>6768483</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,7 +7418,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723528</v>
+        <v>127723511</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445493</v>
+        <v>445497</v>
       </c>
       <c r="R71" t="n">
-        <v>6768388</v>
+        <v>6768438</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723514</v>
+        <v>127723528</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445468</v>
+        <v>445493</v>
       </c>
       <c r="R72" t="n">
-        <v>6768439</v>
+        <v>6768388</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723496</v>
+        <v>127723514</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445376</v>
+        <v>445468</v>
       </c>
       <c r="R73" t="n">
-        <v>6768426</v>
+        <v>6768439</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723511</v>
+        <v>127723439</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445497</v>
+        <v>445382</v>
       </c>
       <c r="R74" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7774,12 +7774,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8122,32 +8122,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723560</v>
+        <v>127723411</v>
       </c>
       <c r="B78" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445433</v>
+        <v>445410</v>
       </c>
       <c r="R78" t="n">
-        <v>6768412</v>
+        <v>6768338</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8316,7 +8316,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723415</v>
+        <v>127723432</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445422</v>
+        <v>445360</v>
       </c>
       <c r="R80" t="n">
-        <v>6768387</v>
+        <v>6768399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723411</v>
+        <v>127723423</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445410</v>
+        <v>445325</v>
       </c>
       <c r="R81" t="n">
-        <v>6768338</v>
+        <v>6768515</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,7 +8510,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723537</v>
+        <v>127723415</v>
       </c>
       <c r="B82" t="n">
         <v>79029</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445488</v>
+        <v>445422</v>
       </c>
       <c r="R82" t="n">
-        <v>6768315</v>
+        <v>6768387</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8607,7 +8607,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723533</v>
+        <v>127723494</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445523</v>
+        <v>445355</v>
       </c>
       <c r="R83" t="n">
-        <v>6768356</v>
+        <v>6768420</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723432</v>
+        <v>127723537</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445360</v>
+        <v>445488</v>
       </c>
       <c r="R84" t="n">
-        <v>6768399</v>
+        <v>6768315</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723423</v>
+        <v>127723420</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445325</v>
+        <v>445395</v>
       </c>
       <c r="R85" t="n">
-        <v>6768515</v>
+        <v>6768485</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8898,10 +8898,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127722931</v>
+        <v>127723560</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>92640</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8909,39 +8909,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445518</v>
+        <v>445433</v>
       </c>
       <c r="R86" t="n">
-        <v>6768355</v>
+        <v>6768412</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8968,12 +8963,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,7 +8995,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723494</v>
+        <v>127723533</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9035,10 +9030,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445355</v>
+        <v>445523</v>
       </c>
       <c r="R87" t="n">
-        <v>6768420</v>
+        <v>6768356</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9097,45 +9092,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723420</v>
+        <v>127722931</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445395</v>
+        <v>445518</v>
       </c>
       <c r="R88" t="n">
-        <v>6768485</v>
+        <v>6768355</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723497</v>
+        <v>127723436</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445376</v>
+        <v>445366</v>
       </c>
       <c r="R91" t="n">
-        <v>6768407</v>
+        <v>6768321</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723504</v>
+        <v>127723426</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445449</v>
+        <v>445324</v>
       </c>
       <c r="R92" t="n">
-        <v>6768387</v>
+        <v>6768470</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723426</v>
+        <v>127723452</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445324</v>
+        <v>445473</v>
       </c>
       <c r="R93" t="n">
-        <v>6768470</v>
+        <v>6768325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723452</v>
+        <v>127723497</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9724,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445473</v>
+        <v>445376</v>
       </c>
       <c r="R94" t="n">
-        <v>6768325</v>
+        <v>6768407</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9786,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723414</v>
+        <v>127723504</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445429</v>
+        <v>445449</v>
       </c>
       <c r="R95" t="n">
-        <v>6768360</v>
+        <v>6768387</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9883,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723436</v>
+        <v>127723414</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9918,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445366</v>
+        <v>445429</v>
       </c>
       <c r="R96" t="n">
-        <v>6768321</v>
+        <v>6768360</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10082,50 +10082,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723027</v>
+        <v>127723447</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445343</v>
+        <v>445458</v>
       </c>
       <c r="R98" t="n">
-        <v>6768460</v>
+        <v>6768338</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10184,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723605</v>
+        <v>127723483</v>
       </c>
       <c r="B99" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10195,21 +10190,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10219,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445403</v>
+        <v>445310</v>
       </c>
       <c r="R99" t="n">
-        <v>6768385</v>
+        <v>6768467</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10378,10 +10373,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723440</v>
+        <v>127723605</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10389,21 +10384,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10413,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445394</v>
+        <v>445403</v>
       </c>
       <c r="R101" t="n">
-        <v>6768290</v>
+        <v>6768385</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10443,12 +10438,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10475,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723490</v>
+        <v>127723440</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10510,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445353</v>
+        <v>445394</v>
       </c>
       <c r="R102" t="n">
-        <v>6768438</v>
+        <v>6768290</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10540,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10572,7 +10567,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723447</v>
+        <v>127723490</v>
       </c>
       <c r="B103" t="n">
         <v>79029</v>
@@ -10607,10 +10602,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445458</v>
+        <v>445353</v>
       </c>
       <c r="R103" t="n">
-        <v>6768338</v>
+        <v>6768438</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10637,12 +10632,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10766,7 +10761,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723483</v>
+        <v>127723454</v>
       </c>
       <c r="B105" t="n">
         <v>79029</v>
@@ -10801,10 +10796,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445310</v>
+        <v>445421</v>
       </c>
       <c r="R105" t="n">
-        <v>6768467</v>
+        <v>6768465</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10863,10 +10858,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723454</v>
+        <v>127722918</v>
       </c>
       <c r="B106" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10874,34 +10869,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445421</v>
+        <v>445382</v>
       </c>
       <c r="R106" t="n">
-        <v>6768465</v>
+        <v>6768422</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10934,6 +10934,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10960,38 +10965,38 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127722918</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11000,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445382</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768422</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11030,17 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723593</v>
+        <v>127723495</v>
       </c>
       <c r="B108" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,21 +11078,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445417</v>
+        <v>445361</v>
       </c>
       <c r="R108" t="n">
-        <v>6768470</v>
+        <v>6768425</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,7 +11164,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723429</v>
+        <v>127723481</v>
       </c>
       <c r="B109" t="n">
         <v>79029</v>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445339</v>
+        <v>445320</v>
       </c>
       <c r="R109" t="n">
-        <v>6768457</v>
+        <v>6768481</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11229,12 +11229,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11261,7 +11261,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723495</v>
+        <v>127723429</v>
       </c>
       <c r="B110" t="n">
         <v>79029</v>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445361</v>
+        <v>445339</v>
       </c>
       <c r="R110" t="n">
-        <v>6768425</v>
+        <v>6768457</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723481</v>
+        <v>127722832</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445320</v>
+        <v>445457</v>
       </c>
       <c r="R111" t="n">
-        <v>6768481</v>
+        <v>6768397</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127722832</v>
+        <v>127723593</v>
       </c>
       <c r="B112" t="n">
-        <v>79647</v>
+        <v>78696</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445457</v>
+        <v>445417</v>
       </c>
       <c r="R112" t="n">
-        <v>6768397</v>
+        <v>6768470</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723607</v>
+        <v>127723453</v>
       </c>
       <c r="B113" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445529</v>
+        <v>445418</v>
       </c>
       <c r="R113" t="n">
-        <v>6768354</v>
+        <v>6768439</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723530</v>
+        <v>127723607</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445515</v>
+        <v>445529</v>
       </c>
       <c r="R114" t="n">
-        <v>6768378</v>
+        <v>6768354</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723532</v>
+        <v>127723498</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445523</v>
+        <v>445386</v>
       </c>
       <c r="R115" t="n">
-        <v>6768362</v>
+        <v>6768393</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11843,7 +11843,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723453</v>
+        <v>127723530</v>
       </c>
       <c r="B116" t="n">
         <v>79029</v>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445418</v>
+        <v>445515</v>
       </c>
       <c r="R116" t="n">
-        <v>6768439</v>
+        <v>6768378</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723498</v>
+        <v>127723441</v>
       </c>
       <c r="B117" t="n">
         <v>79029</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445386</v>
+        <v>445408</v>
       </c>
       <c r="R117" t="n">
-        <v>6768393</v>
+        <v>6768287</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12005,12 +12005,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12037,7 +12037,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723441</v>
+        <v>127723532</v>
       </c>
       <c r="B118" t="n">
         <v>79029</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445408</v>
+        <v>445523</v>
       </c>
       <c r="R118" t="n">
-        <v>6768287</v>
+        <v>6768362</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12102,12 +12102,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12134,7 +12134,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723438</v>
+        <v>127723410</v>
       </c>
       <c r="B119" t="n">
         <v>79029</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445375</v>
+        <v>445434</v>
       </c>
       <c r="R119" t="n">
-        <v>6768277</v>
+        <v>6768336</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723410</v>
+        <v>127723503</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445434</v>
+        <v>445439</v>
       </c>
       <c r="R120" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,7 +12328,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723503</v>
+        <v>127723443</v>
       </c>
       <c r="B121" t="n">
         <v>79029</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445439</v>
+        <v>445422</v>
       </c>
       <c r="R121" t="n">
-        <v>6768381</v>
+        <v>6768295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723443</v>
+        <v>127723505</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445422</v>
+        <v>445493</v>
       </c>
       <c r="R122" t="n">
-        <v>6768295</v>
+        <v>6768418</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723505</v>
+        <v>127723438</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445493</v>
+        <v>445375</v>
       </c>
       <c r="R123" t="n">
-        <v>6768418</v>
+        <v>6768277</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD123" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723442</v>
+        <v>127723561</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445407</v>
+        <v>445519</v>
       </c>
       <c r="R19" t="n">
-        <v>6768295</v>
+        <v>6768373</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723561</v>
+        <v>127723442</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445519</v>
+        <v>445407</v>
       </c>
       <c r="R20" t="n">
-        <v>6768373</v>
+        <v>6768295</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723525</v>
+        <v>127723417</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445465</v>
+        <v>445413</v>
       </c>
       <c r="R23" t="n">
-        <v>6768379</v>
+        <v>6768451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723527</v>
+        <v>127723433</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445476</v>
+        <v>445354</v>
       </c>
       <c r="R24" t="n">
-        <v>6768382</v>
+        <v>6768399</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723417</v>
+        <v>127723525</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445413</v>
+        <v>445465</v>
       </c>
       <c r="R25" t="n">
-        <v>6768451</v>
+        <v>6768379</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723433</v>
+        <v>127723527</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445354</v>
+        <v>445476</v>
       </c>
       <c r="R26" t="n">
-        <v>6768399</v>
+        <v>6768382</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127722895</v>
+        <v>127723529</v>
       </c>
       <c r="B27" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3116,39 +3116,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445370</v>
+        <v>445507</v>
       </c>
       <c r="R27" t="n">
-        <v>6768276</v>
+        <v>6768383</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,12 +3170,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3304,7 +3299,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723529</v>
+        <v>127723428</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3339,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445507</v>
+        <v>445329</v>
       </c>
       <c r="R29" t="n">
-        <v>6768383</v>
+        <v>6768465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3369,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3401,7 +3396,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723538</v>
+        <v>127723487</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445485</v>
+        <v>445328</v>
       </c>
       <c r="R30" t="n">
-        <v>6768313</v>
+        <v>6768445</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,7 +3493,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723487</v>
+        <v>127723538</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3533,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445328</v>
+        <v>445485</v>
       </c>
       <c r="R31" t="n">
-        <v>6768445</v>
+        <v>6768313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3595,38 +3590,38 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723028</v>
+        <v>127722895</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3635,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445345</v>
+        <v>445370</v>
       </c>
       <c r="R32" t="n">
-        <v>6768382</v>
+        <v>6768276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3697,45 +3692,50 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723428</v>
+        <v>127723028</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445329</v>
+        <v>445345</v>
       </c>
       <c r="R33" t="n">
-        <v>6768465</v>
+        <v>6768382</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723603</v>
+        <v>127723482</v>
       </c>
       <c r="B34" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445353</v>
+        <v>445318</v>
       </c>
       <c r="R34" t="n">
-        <v>6768433</v>
+        <v>6768474</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723431</v>
+        <v>127723515</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445369</v>
+        <v>445465</v>
       </c>
       <c r="R35" t="n">
-        <v>6768408</v>
+        <v>6768438</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723536</v>
+        <v>127723603</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445500</v>
+        <v>445353</v>
       </c>
       <c r="R36" t="n">
-        <v>6768348</v>
+        <v>6768433</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723482</v>
+        <v>127723431</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445318</v>
+        <v>445369</v>
       </c>
       <c r="R37" t="n">
-        <v>6768474</v>
+        <v>6768408</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723446</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445453</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723515</v>
+        <v>127723446</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445465</v>
+        <v>445453</v>
       </c>
       <c r="R39" t="n">
-        <v>6768438</v>
+        <v>6768321</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4963,45 +4963,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723604</v>
+        <v>127723025</v>
       </c>
       <c r="B46" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R46" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5028,12 +5033,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5060,45 +5065,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723592</v>
+        <v>127723026</v>
       </c>
       <c r="B47" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445370</v>
+        <v>445387</v>
       </c>
       <c r="R47" t="n">
-        <v>6768478</v>
+        <v>6768492</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,50 +5167,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723025</v>
+        <v>127723604</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445397</v>
+        <v>445370</v>
       </c>
       <c r="R48" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5227,12 +5232,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5259,50 +5264,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723026</v>
+        <v>127723592</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445387</v>
+        <v>445370</v>
       </c>
       <c r="R49" t="n">
-        <v>6768492</v>
+        <v>6768478</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722889</v>
+        <v>127723444</v>
       </c>
       <c r="B52" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,39 +5566,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445372</v>
+        <v>445432</v>
       </c>
       <c r="R52" t="n">
-        <v>6768323</v>
+        <v>6768299</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5657,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723444</v>
+        <v>127722889</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5668,34 +5663,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445432</v>
+        <v>445372</v>
       </c>
       <c r="R53" t="n">
-        <v>6768299</v>
+        <v>6768323</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723430</v>
+        <v>127723425</v>
       </c>
       <c r="B54" t="n">
         <v>79029</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445357</v>
+        <v>445321</v>
       </c>
       <c r="R54" t="n">
-        <v>6768451</v>
+        <v>6768501</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5851,10 +5851,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722829</v>
+        <v>127723430</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5862,21 +5862,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445339</v>
+        <v>445357</v>
       </c>
       <c r="R55" t="n">
-        <v>6768436</v>
+        <v>6768451</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5916,12 +5916,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5948,10 +5948,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723524</v>
+        <v>127722829</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5959,21 +5959,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5983,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445455</v>
+        <v>445339</v>
       </c>
       <c r="R56" t="n">
-        <v>6768391</v>
+        <v>6768436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723425</v>
+        <v>127723524</v>
       </c>
       <c r="B57" t="n">
         <v>79029</v>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445321</v>
+        <v>445455</v>
       </c>
       <c r="R57" t="n">
-        <v>6768501</v>
+        <v>6768391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723526</v>
+        <v>127723492</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445468</v>
+        <v>445366</v>
       </c>
       <c r="R59" t="n">
-        <v>6768377</v>
+        <v>6768409</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723492</v>
+        <v>127723488</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445366</v>
+        <v>445340</v>
       </c>
       <c r="R60" t="n">
-        <v>6768409</v>
+        <v>6768445</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723488</v>
+        <v>127723526</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445340</v>
+        <v>445468</v>
       </c>
       <c r="R61" t="n">
-        <v>6768445</v>
+        <v>6768377</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,39 +6541,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R62" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,11 +6601,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6637,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127722872</v>
+        <v>127722914</v>
       </c>
       <c r="B63" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6648,27 +6638,27 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -6677,10 +6667,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445414</v>
+        <v>445325</v>
       </c>
       <c r="R63" t="n">
-        <v>6768450</v>
+        <v>6768463</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6713,6 +6703,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6739,10 +6734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127723413</v>
+        <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6750,34 +6745,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445444</v>
+        <v>445414</v>
       </c>
       <c r="R64" t="n">
-        <v>6768341</v>
+        <v>6768450</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6836,7 +6836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723506</v>
+        <v>127723439</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445509</v>
+        <v>445382</v>
       </c>
       <c r="R65" t="n">
-        <v>6768424</v>
+        <v>6768296</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723489</v>
+        <v>127723506</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445349</v>
+        <v>445509</v>
       </c>
       <c r="R66" t="n">
-        <v>6768438</v>
+        <v>6768424</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723522</v>
+        <v>127723489</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445457</v>
+        <v>445349</v>
       </c>
       <c r="R67" t="n">
-        <v>6768411</v>
+        <v>6768438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723519</v>
+        <v>127723455</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445434</v>
+        <v>445417</v>
       </c>
       <c r="R68" t="n">
-        <v>6768437</v>
+        <v>6768483</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723496</v>
+        <v>127723519</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445376</v>
+        <v>445434</v>
       </c>
       <c r="R69" t="n">
-        <v>6768426</v>
+        <v>6768437</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723455</v>
+        <v>127722908</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7332,34 +7332,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445417</v>
+        <v>445329</v>
       </c>
       <c r="R70" t="n">
-        <v>6768483</v>
+        <v>6768474</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7386,12 +7391,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7612,10 +7622,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723514</v>
+        <v>127722917</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7623,34 +7633,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445468</v>
+        <v>445329</v>
       </c>
       <c r="R73" t="n">
-        <v>6768439</v>
+        <v>6768466</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7677,12 +7692,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7709,7 +7729,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723439</v>
+        <v>127723514</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7744,10 +7764,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445382</v>
+        <v>445468</v>
       </c>
       <c r="R74" t="n">
-        <v>6768296</v>
+        <v>6768439</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7774,12 +7794,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7806,10 +7826,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722917</v>
+        <v>127723522</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,39 +7837,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445329</v>
+        <v>445457</v>
       </c>
       <c r="R75" t="n">
-        <v>6768466</v>
+        <v>6768411</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,17 +7891,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7913,10 +7923,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722908</v>
+        <v>127723496</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7924,39 +7934,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445329</v>
+        <v>445376</v>
       </c>
       <c r="R76" t="n">
-        <v>6768474</v>
+        <v>6768426</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7983,17 +7988,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127722825</v>
+        <v>127723420</v>
       </c>
       <c r="B79" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445386</v>
+        <v>445395</v>
       </c>
       <c r="R79" t="n">
-        <v>6768493</v>
+        <v>6768485</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,7 +8316,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723432</v>
+        <v>127723415</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445360</v>
+        <v>445422</v>
       </c>
       <c r="R80" t="n">
-        <v>6768399</v>
+        <v>6768387</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8413,7 +8413,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723423</v>
+        <v>127723494</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445325</v>
+        <v>445355</v>
       </c>
       <c r="R81" t="n">
-        <v>6768515</v>
+        <v>6768420</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8478,12 +8478,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8510,7 +8510,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723415</v>
+        <v>127723537</v>
       </c>
       <c r="B82" t="n">
         <v>79029</v>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445422</v>
+        <v>445488</v>
       </c>
       <c r="R82" t="n">
-        <v>6768387</v>
+        <v>6768315</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8575,12 +8575,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8607,7 +8607,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723494</v>
+        <v>127723533</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445355</v>
+        <v>445523</v>
       </c>
       <c r="R83" t="n">
-        <v>6768420</v>
+        <v>6768356</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723537</v>
+        <v>127722825</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445488</v>
+        <v>445386</v>
       </c>
       <c r="R84" t="n">
-        <v>6768315</v>
+        <v>6768493</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8769,12 +8769,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8801,7 +8801,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723420</v>
+        <v>127723432</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445395</v>
+        <v>445360</v>
       </c>
       <c r="R85" t="n">
-        <v>6768485</v>
+        <v>6768399</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8898,32 +8898,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723560</v>
+        <v>127723423</v>
       </c>
       <c r="B86" t="n">
-        <v>92640</v>
+        <v>79029</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445433</v>
+        <v>445325</v>
       </c>
       <c r="R86" t="n">
-        <v>6768412</v>
+        <v>6768515</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8963,12 +8963,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8995,32 +8995,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723533</v>
+        <v>127723560</v>
       </c>
       <c r="B87" t="n">
-        <v>79029</v>
+        <v>92641</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9030,10 +9030,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445523</v>
+        <v>445433</v>
       </c>
       <c r="R87" t="n">
-        <v>6768356</v>
+        <v>6768412</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9092,7 +9092,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722931</v>
+        <v>127723030</v>
       </c>
       <c r="B88" t="n">
         <v>8450</v>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445518</v>
+        <v>445376</v>
       </c>
       <c r="R88" t="n">
-        <v>6768355</v>
+        <v>6768336</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722930</v>
+        <v>127722931</v>
       </c>
       <c r="B89" t="n">
         <v>8450</v>
@@ -9225,7 +9225,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445390</v>
+        <v>445518</v>
       </c>
       <c r="R89" t="n">
-        <v>6768381</v>
+        <v>6768355</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9296,7 +9296,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723030</v>
+        <v>127722930</v>
       </c>
       <c r="B90" t="n">
         <v>8450</v>
@@ -9327,7 +9327,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -9336,10 +9336,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445376</v>
+        <v>445390</v>
       </c>
       <c r="R90" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723436</v>
+        <v>127723452</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445366</v>
+        <v>445473</v>
       </c>
       <c r="R91" t="n">
-        <v>6768321</v>
+        <v>6768325</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723426</v>
+        <v>127723497</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445324</v>
+        <v>445376</v>
       </c>
       <c r="R92" t="n">
-        <v>6768470</v>
+        <v>6768407</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723452</v>
+        <v>127723414</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445473</v>
+        <v>445429</v>
       </c>
       <c r="R93" t="n">
-        <v>6768325</v>
+        <v>6768360</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,45 +9689,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723497</v>
+        <v>127723029</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445376</v>
+        <v>445351</v>
       </c>
       <c r="R94" t="n">
-        <v>6768407</v>
+        <v>6768348</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9759,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,7 +9791,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723504</v>
+        <v>127723436</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9821,10 +9826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445449</v>
+        <v>445366</v>
       </c>
       <c r="R95" t="n">
-        <v>6768387</v>
+        <v>6768321</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9856,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9883,7 +9888,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723414</v>
+        <v>127723426</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9918,10 +9923,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445429</v>
+        <v>445324</v>
       </c>
       <c r="R96" t="n">
-        <v>6768360</v>
+        <v>6768470</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9980,50 +9985,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723029</v>
+        <v>127723504</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445351</v>
+        <v>445449</v>
       </c>
       <c r="R97" t="n">
-        <v>6768348</v>
+        <v>6768387</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723447</v>
+        <v>127723605</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445458</v>
+        <v>445403</v>
       </c>
       <c r="R98" t="n">
-        <v>6768338</v>
+        <v>6768385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,12 +10147,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10179,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723483</v>
+        <v>127722864</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>91351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10190,21 +10190,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445310</v>
+        <v>445327</v>
       </c>
       <c r="R99" t="n">
-        <v>6768467</v>
+        <v>6768444</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10276,10 +10276,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722864</v>
+        <v>127723440</v>
       </c>
       <c r="B100" t="n">
-        <v>91350</v>
+        <v>79029</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10287,21 +10287,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445327</v>
+        <v>445394</v>
       </c>
       <c r="R100" t="n">
-        <v>6768444</v>
+        <v>6768290</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,10 +10373,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723605</v>
+        <v>127723490</v>
       </c>
       <c r="B101" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10384,21 +10384,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445403</v>
+        <v>445353</v>
       </c>
       <c r="R101" t="n">
-        <v>6768385</v>
+        <v>6768438</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723440</v>
+        <v>127723447</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445394</v>
+        <v>445458</v>
       </c>
       <c r="R102" t="n">
-        <v>6768290</v>
+        <v>6768338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10567,7 +10567,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723490</v>
+        <v>127723535</v>
       </c>
       <c r="B103" t="n">
         <v>79029</v>
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445353</v>
+        <v>445518</v>
       </c>
       <c r="R103" t="n">
-        <v>6768438</v>
+        <v>6768343</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723535</v>
+        <v>127723483</v>
       </c>
       <c r="B104" t="n">
         <v>79029</v>
@@ -10699,10 +10699,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445518</v>
+        <v>445310</v>
       </c>
       <c r="R104" t="n">
-        <v>6768343</v>
+        <v>6768467</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723429</v>
+        <v>127722832</v>
       </c>
       <c r="B110" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445339</v>
+        <v>445457</v>
       </c>
       <c r="R110" t="n">
-        <v>6768457</v>
+        <v>6768397</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B111" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R111" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11552,7 +11552,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723453</v>
+        <v>127723532</v>
       </c>
       <c r="B113" t="n">
         <v>79029</v>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445418</v>
+        <v>445523</v>
       </c>
       <c r="R113" t="n">
-        <v>6768439</v>
+        <v>6768362</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723607</v>
+        <v>127723453</v>
       </c>
       <c r="B114" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11660,21 +11660,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445529</v>
+        <v>445418</v>
       </c>
       <c r="R114" t="n">
-        <v>6768354</v>
+        <v>6768439</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723532</v>
+        <v>127723607</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12048,21 +12048,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445523</v>
+        <v>445529</v>
       </c>
       <c r="R118" t="n">
-        <v>6768362</v>
+        <v>6768354</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723443</v>
+        <v>127722831</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12339,21 +12339,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445422</v>
+        <v>445370</v>
       </c>
       <c r="R121" t="n">
-        <v>6768295</v>
+        <v>6768425</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722831</v>
+        <v>127723443</v>
       </c>
       <c r="B124" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445370</v>
+        <v>445422</v>
       </c>
       <c r="R124" t="n">
-        <v>6768425</v>
+        <v>6768295</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723518</v>
+        <v>127722873</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445431</v>
+        <v>445364</v>
       </c>
       <c r="R2" t="n">
-        <v>6768443</v>
+        <v>6768295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723479</v>
+        <v>127723518</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445309</v>
+        <v>445431</v>
       </c>
       <c r="R3" t="n">
-        <v>6768491</v>
+        <v>6768443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723434</v>
+        <v>127723479</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445345</v>
+        <v>445309</v>
       </c>
       <c r="R4" t="n">
-        <v>6768366</v>
+        <v>6768491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723480</v>
+        <v>127723434</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445314</v>
+        <v>445345</v>
       </c>
       <c r="R5" t="n">
-        <v>6768485</v>
+        <v>6768366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723421</v>
+        <v>127723480</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445361</v>
+        <v>445314</v>
       </c>
       <c r="R6" t="n">
-        <v>6768495</v>
+        <v>6768485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1160,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723416</v>
+        <v>127723421</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445426</v>
+        <v>445361</v>
       </c>
       <c r="R7" t="n">
-        <v>6768417</v>
+        <v>6768495</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723493</v>
+        <v>127723416</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445363</v>
+        <v>445426</v>
       </c>
       <c r="R8" t="n">
-        <v>6768410</v>
+        <v>6768417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723531</v>
+        <v>127723493</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445524</v>
+        <v>445363</v>
       </c>
       <c r="R9" t="n">
-        <v>6768371</v>
+        <v>6768410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723424</v>
+        <v>127723531</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445311</v>
+        <v>445524</v>
       </c>
       <c r="R10" t="n">
-        <v>6768500</v>
+        <v>6768371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127722873</v>
+        <v>127723424</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445364</v>
+        <v>445311</v>
       </c>
       <c r="R11" t="n">
-        <v>6768295</v>
+        <v>6768500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723602</v>
+        <v>127723445</v>
       </c>
       <c r="B12" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445339</v>
+        <v>445446</v>
       </c>
       <c r="R12" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723606</v>
+        <v>127723512</v>
       </c>
       <c r="B13" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445475</v>
+        <v>445476</v>
       </c>
       <c r="R13" t="n">
-        <v>6768378</v>
+        <v>6768436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723445</v>
+        <v>127723602</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445446</v>
+        <v>445339</v>
       </c>
       <c r="R14" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723512</v>
+        <v>127723606</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445476</v>
+        <v>445475</v>
       </c>
       <c r="R15" t="n">
-        <v>6768436</v>
+        <v>6768378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723517</v>
+        <v>127723561</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445463</v>
+        <v>445519</v>
       </c>
       <c r="R16" t="n">
-        <v>6768439</v>
+        <v>6768373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R17" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723520</v>
+        <v>127723435</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445439</v>
+        <v>445375</v>
       </c>
       <c r="R18" t="n">
-        <v>6768423</v>
+        <v>6768348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,32 +2329,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723561</v>
+        <v>127723442</v>
       </c>
       <c r="B19" t="n">
-        <v>92641</v>
+        <v>79029</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445519</v>
+        <v>445407</v>
       </c>
       <c r="R19" t="n">
-        <v>6768373</v>
+        <v>6768295</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,7 +2426,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723442</v>
+        <v>127723520</v>
       </c>
       <c r="B20" t="n">
         <v>79029</v>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445407</v>
+        <v>445439</v>
       </c>
       <c r="R20" t="n">
-        <v>6768295</v>
+        <v>6768423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723412</v>
+        <v>127723527</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445423</v>
+        <v>445476</v>
       </c>
       <c r="R22" t="n">
-        <v>6768342</v>
+        <v>6768382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723417</v>
+        <v>127723412</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445413</v>
+        <v>445423</v>
       </c>
       <c r="R23" t="n">
-        <v>6768451</v>
+        <v>6768342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723433</v>
+        <v>127723417</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445354</v>
+        <v>445413</v>
       </c>
       <c r="R24" t="n">
-        <v>6768399</v>
+        <v>6768451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723525</v>
+        <v>127723433</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445465</v>
+        <v>445354</v>
       </c>
       <c r="R25" t="n">
-        <v>6768379</v>
+        <v>6768399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2976,12 +2976,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723527</v>
+        <v>127723525</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445476</v>
+        <v>445465</v>
       </c>
       <c r="R26" t="n">
-        <v>6768382</v>
+        <v>6768379</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723529</v>
+        <v>127723523</v>
       </c>
       <c r="B27" t="n">
         <v>79029</v>
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445507</v>
+        <v>445451</v>
       </c>
       <c r="R27" t="n">
-        <v>6768383</v>
+        <v>6768402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723523</v>
+        <v>127723529</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445451</v>
+        <v>445507</v>
       </c>
       <c r="R28" t="n">
-        <v>6768402</v>
+        <v>6768383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723428</v>
+        <v>127723538</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445329</v>
+        <v>445485</v>
       </c>
       <c r="R29" t="n">
-        <v>6768465</v>
+        <v>6768313</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3493,7 +3493,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723538</v>
+        <v>127723428</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445485</v>
+        <v>445329</v>
       </c>
       <c r="R31" t="n">
-        <v>6768313</v>
+        <v>6768465</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723482</v>
+        <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445318</v>
+        <v>445353</v>
       </c>
       <c r="R34" t="n">
-        <v>6768474</v>
+        <v>6768433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723515</v>
+        <v>127723482</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445465</v>
+        <v>445318</v>
       </c>
       <c r="R35" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723603</v>
+        <v>127723431</v>
       </c>
       <c r="B36" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3999,21 +3999,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445353</v>
+        <v>445369</v>
       </c>
       <c r="R36" t="n">
-        <v>6768433</v>
+        <v>6768408</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723431</v>
+        <v>127723536</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445369</v>
+        <v>445500</v>
       </c>
       <c r="R37" t="n">
-        <v>6768408</v>
+        <v>6768348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723446</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445453</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768321</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,7 +4279,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723446</v>
+        <v>127723515</v>
       </c>
       <c r="B39" t="n">
         <v>79029</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445453</v>
+        <v>445465</v>
       </c>
       <c r="R39" t="n">
-        <v>6768321</v>
+        <v>6768438</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4344,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4769,10 +4769,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723534</v>
+        <v>127723604</v>
       </c>
       <c r="B44" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4780,21 +4780,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445528</v>
+        <v>445370</v>
       </c>
       <c r="R44" t="n">
-        <v>6768349</v>
+        <v>6768425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4866,10 +4866,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723521</v>
+        <v>127723592</v>
       </c>
       <c r="B45" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4877,21 +4877,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4901,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445445</v>
+        <v>445370</v>
       </c>
       <c r="R45" t="n">
-        <v>6768409</v>
+        <v>6768478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4963,50 +4963,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723025</v>
+        <v>127723534</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445397</v>
+        <v>445528</v>
       </c>
       <c r="R46" t="n">
-        <v>6768481</v>
+        <v>6768349</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5033,12 +5028,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5065,50 +5060,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723026</v>
+        <v>127723521</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445387</v>
+        <v>445445</v>
       </c>
       <c r="R47" t="n">
-        <v>6768492</v>
+        <v>6768409</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5135,12 +5125,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5167,45 +5157,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723604</v>
+        <v>127723025</v>
       </c>
       <c r="B48" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R48" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5232,12 +5227,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5264,45 +5259,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723592</v>
+        <v>127723026</v>
       </c>
       <c r="B49" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445370</v>
+        <v>445387</v>
       </c>
       <c r="R49" t="n">
-        <v>6768478</v>
+        <v>6768492</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127722889</v>
+        <v>127723430</v>
       </c>
       <c r="B53" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5663,39 +5663,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445372</v>
+        <v>445357</v>
       </c>
       <c r="R53" t="n">
-        <v>6768323</v>
+        <v>6768451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5851,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723430</v>
+        <v>127722829</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5862,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5886,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445357</v>
+        <v>445339</v>
       </c>
       <c r="R55" t="n">
-        <v>6768451</v>
+        <v>6768436</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5916,12 +5911,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5948,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722829</v>
+        <v>127723524</v>
       </c>
       <c r="B56" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5959,21 +5954,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445339</v>
+        <v>445455</v>
       </c>
       <c r="R56" t="n">
-        <v>6768436</v>
+        <v>6768391</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6045,10 +6040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723524</v>
+        <v>127722889</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,34 +6051,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445455</v>
+        <v>445372</v>
       </c>
       <c r="R57" t="n">
-        <v>6768391</v>
+        <v>6768323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6142,7 +6142,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723499</v>
+        <v>127723492</v>
       </c>
       <c r="B58" t="n">
         <v>79029</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445418</v>
+        <v>445366</v>
       </c>
       <c r="R58" t="n">
-        <v>6768394</v>
+        <v>6768409</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723492</v>
+        <v>127723499</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445366</v>
+        <v>445418</v>
       </c>
       <c r="R59" t="n">
-        <v>6768409</v>
+        <v>6768394</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723488</v>
+        <v>127723526</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445340</v>
+        <v>445468</v>
       </c>
       <c r="R60" t="n">
-        <v>6768445</v>
+        <v>6768377</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,7 +6433,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723526</v>
+        <v>127723488</v>
       </c>
       <c r="B61" t="n">
         <v>79029</v>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445468</v>
+        <v>445340</v>
       </c>
       <c r="R61" t="n">
-        <v>6768377</v>
+        <v>6768445</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6836,7 +6836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723439</v>
+        <v>127723522</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445382</v>
+        <v>445457</v>
       </c>
       <c r="R65" t="n">
-        <v>6768296</v>
+        <v>6768411</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723506</v>
+        <v>127723514</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445509</v>
+        <v>445468</v>
       </c>
       <c r="R66" t="n">
-        <v>6768424</v>
+        <v>6768439</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723489</v>
+        <v>127723439</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445349</v>
+        <v>445382</v>
       </c>
       <c r="R67" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723455</v>
+        <v>127723506</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445417</v>
+        <v>445509</v>
       </c>
       <c r="R68" t="n">
-        <v>6768483</v>
+        <v>6768424</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723519</v>
+        <v>127723489</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445434</v>
+        <v>445349</v>
       </c>
       <c r="R69" t="n">
-        <v>6768437</v>
+        <v>6768438</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127722908</v>
+        <v>127723455</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7332,39 +7332,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445329</v>
+        <v>445417</v>
       </c>
       <c r="R70" t="n">
-        <v>6768474</v>
+        <v>6768483</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7391,17 +7386,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7428,7 +7418,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723511</v>
+        <v>127723519</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7463,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445497</v>
+        <v>445434</v>
       </c>
       <c r="R71" t="n">
-        <v>6768438</v>
+        <v>6768437</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7525,7 +7515,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723528</v>
+        <v>127723496</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7560,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445493</v>
+        <v>445376</v>
       </c>
       <c r="R72" t="n">
-        <v>6768388</v>
+        <v>6768426</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7622,10 +7612,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127722917</v>
+        <v>127723511</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7633,39 +7623,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445329</v>
+        <v>445497</v>
       </c>
       <c r="R73" t="n">
-        <v>6768466</v>
+        <v>6768438</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7692,17 +7677,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7729,7 +7709,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723514</v>
+        <v>127723528</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7764,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445468</v>
+        <v>445493</v>
       </c>
       <c r="R74" t="n">
-        <v>6768439</v>
+        <v>6768388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7826,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723522</v>
+        <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7837,34 +7817,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445457</v>
+        <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768411</v>
+        <v>6768466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7891,12 +7876,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7923,10 +7913,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723496</v>
+        <v>127722908</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7934,34 +7924,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445376</v>
+        <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768426</v>
+        <v>6768474</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7988,12 +7983,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8122,32 +8122,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723411</v>
+        <v>127723560</v>
       </c>
       <c r="B78" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445410</v>
+        <v>445433</v>
       </c>
       <c r="R78" t="n">
-        <v>6768338</v>
+        <v>6768412</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8187,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8219,7 +8219,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723420</v>
+        <v>127723415</v>
       </c>
       <c r="B79" t="n">
         <v>79029</v>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445395</v>
+        <v>445422</v>
       </c>
       <c r="R79" t="n">
-        <v>6768485</v>
+        <v>6768387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,7 +8316,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723415</v>
+        <v>127723411</v>
       </c>
       <c r="B80" t="n">
         <v>79029</v>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445422</v>
+        <v>445410</v>
       </c>
       <c r="R80" t="n">
-        <v>6768387</v>
+        <v>6768338</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722825</v>
+        <v>127723432</v>
       </c>
       <c r="B84" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445386</v>
+        <v>445360</v>
       </c>
       <c r="R84" t="n">
-        <v>6768493</v>
+        <v>6768399</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,7 +8801,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723432</v>
+        <v>127723423</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445360</v>
+        <v>445325</v>
       </c>
       <c r="R85" t="n">
-        <v>6768399</v>
+        <v>6768515</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8898,7 +8898,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723423</v>
+        <v>127723420</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8933,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445325</v>
+        <v>445395</v>
       </c>
       <c r="R86" t="n">
-        <v>6768515</v>
+        <v>6768485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8995,10 +8995,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723560</v>
+        <v>127722931</v>
       </c>
       <c r="B87" t="n">
-        <v>92641</v>
+        <v>8450</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9006,34 +9006,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445433</v>
+        <v>445518</v>
       </c>
       <c r="R87" t="n">
-        <v>6768412</v>
+        <v>6768355</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9060,12 +9065,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9092,7 +9097,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723030</v>
+        <v>127722930</v>
       </c>
       <c r="B88" t="n">
         <v>8450</v>
@@ -9123,7 +9128,7 @@
       <c r="I88" t="inlineStr"/>
       <c r="M88" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9132,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445376</v>
+        <v>445390</v>
       </c>
       <c r="R88" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9162,12 +9167,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9194,7 +9199,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127722931</v>
+        <v>127723030</v>
       </c>
       <c r="B89" t="n">
         <v>8450</v>
@@ -9234,10 +9239,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445518</v>
+        <v>445376</v>
       </c>
       <c r="R89" t="n">
-        <v>6768355</v>
+        <v>6768336</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9296,50 +9301,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722930</v>
+        <v>127722825</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445390</v>
+        <v>445386</v>
       </c>
       <c r="R90" t="n">
-        <v>6768381</v>
+        <v>6768493</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723452</v>
+        <v>127723436</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445473</v>
+        <v>445366</v>
       </c>
       <c r="R91" t="n">
-        <v>6768325</v>
+        <v>6768321</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,12 +9463,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723497</v>
+        <v>127723426</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445376</v>
+        <v>445324</v>
       </c>
       <c r="R92" t="n">
-        <v>6768407</v>
+        <v>6768470</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723414</v>
+        <v>127723452</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445429</v>
+        <v>445473</v>
       </c>
       <c r="R93" t="n">
-        <v>6768360</v>
+        <v>6768325</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,50 +9689,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723029</v>
+        <v>127723497</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445351</v>
+        <v>445376</v>
       </c>
       <c r="R94" t="n">
-        <v>6768348</v>
+        <v>6768407</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9759,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9791,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723436</v>
+        <v>127723504</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9826,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445366</v>
+        <v>445449</v>
       </c>
       <c r="R95" t="n">
-        <v>6768321</v>
+        <v>6768387</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9888,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723426</v>
+        <v>127723414</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9923,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445324</v>
+        <v>445429</v>
       </c>
       <c r="R96" t="n">
-        <v>6768470</v>
+        <v>6768360</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9985,45 +9980,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723504</v>
+        <v>127723029</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445449</v>
+        <v>445351</v>
       </c>
       <c r="R97" t="n">
-        <v>6768387</v>
+        <v>6768348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723605</v>
+        <v>127723440</v>
       </c>
       <c r="B98" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445403</v>
+        <v>445394</v>
       </c>
       <c r="R98" t="n">
-        <v>6768385</v>
+        <v>6768290</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,12 +10147,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10179,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127722864</v>
+        <v>127723490</v>
       </c>
       <c r="B99" t="n">
-        <v>91351</v>
+        <v>79029</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10190,21 +10190,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445327</v>
+        <v>445353</v>
       </c>
       <c r="R99" t="n">
-        <v>6768444</v>
+        <v>6768438</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723440</v>
+        <v>127723447</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445394</v>
+        <v>445458</v>
       </c>
       <c r="R100" t="n">
-        <v>6768290</v>
+        <v>6768338</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723490</v>
+        <v>127723535</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445353</v>
+        <v>445518</v>
       </c>
       <c r="R101" t="n">
-        <v>6768438</v>
+        <v>6768343</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723447</v>
+        <v>127723483</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445458</v>
+        <v>445310</v>
       </c>
       <c r="R102" t="n">
-        <v>6768338</v>
+        <v>6768467</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,7 +10567,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723535</v>
+        <v>127723454</v>
       </c>
       <c r="B103" t="n">
         <v>79029</v>
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445518</v>
+        <v>445421</v>
       </c>
       <c r="R103" t="n">
-        <v>6768343</v>
+        <v>6768465</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10664,10 +10664,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723483</v>
+        <v>127722918</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10675,34 +10675,39 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445310</v>
+        <v>445382</v>
       </c>
       <c r="R104" t="n">
-        <v>6768467</v>
+        <v>6768422</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10735,6 +10740,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10761,45 +10771,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723454</v>
+        <v>127723027</v>
       </c>
       <c r="B105" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445421</v>
+        <v>445343</v>
       </c>
       <c r="R105" t="n">
-        <v>6768465</v>
+        <v>6768460</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10826,12 +10841,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10858,10 +10873,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127722918</v>
+        <v>127722864</v>
       </c>
       <c r="B106" t="n">
-        <v>57672</v>
+        <v>91352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10869,39 +10884,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445382</v>
+        <v>445327</v>
       </c>
       <c r="R106" t="n">
-        <v>6768422</v>
+        <v>6768444</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10934,11 +10944,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10965,50 +10970,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127723605</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445403</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768385</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723532</v>
+        <v>127723607</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445523</v>
+        <v>445529</v>
       </c>
       <c r="R113" t="n">
-        <v>6768362</v>
+        <v>6768354</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,7 +11649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723453</v>
+        <v>127723498</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445418</v>
+        <v>445386</v>
       </c>
       <c r="R114" t="n">
-        <v>6768439</v>
+        <v>6768393</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723498</v>
+        <v>127723530</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445386</v>
+        <v>445515</v>
       </c>
       <c r="R115" t="n">
-        <v>6768393</v>
+        <v>6768378</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11843,7 +11843,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723530</v>
+        <v>127723441</v>
       </c>
       <c r="B116" t="n">
         <v>79029</v>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445515</v>
+        <v>445408</v>
       </c>
       <c r="R116" t="n">
-        <v>6768378</v>
+        <v>6768287</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11908,12 +11908,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11940,7 +11940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723441</v>
+        <v>127723532</v>
       </c>
       <c r="B117" t="n">
         <v>79029</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445408</v>
+        <v>445523</v>
       </c>
       <c r="R117" t="n">
-        <v>6768287</v>
+        <v>6768362</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12005,12 +12005,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723607</v>
+        <v>127723453</v>
       </c>
       <c r="B118" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12048,21 +12048,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445529</v>
+        <v>445418</v>
       </c>
       <c r="R118" t="n">
-        <v>6768354</v>
+        <v>6768439</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723505</v>
+        <v>127723443</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445493</v>
+        <v>445422</v>
       </c>
       <c r="R122" t="n">
-        <v>6768418</v>
+        <v>6768295</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723438</v>
+        <v>127723505</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445375</v>
+        <v>445493</v>
       </c>
       <c r="R123" t="n">
-        <v>6768277</v>
+        <v>6768418</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12587,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12619,7 +12619,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723443</v>
+        <v>127723438</v>
       </c>
       <c r="B124" t="n">
         <v>79029</v>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445422</v>
+        <v>445375</v>
       </c>
       <c r="R124" t="n">
-        <v>6768295</v>
+        <v>6768277</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127722873</v>
+        <v>127723518</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445364</v>
+        <v>445431</v>
       </c>
       <c r="R2" t="n">
-        <v>6768295</v>
+        <v>6768443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723518</v>
+        <v>127723424</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445431</v>
+        <v>445311</v>
       </c>
       <c r="R3" t="n">
-        <v>6768443</v>
+        <v>6768500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723434</v>
+        <v>127723421</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445345</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>6768366</v>
+        <v>6768495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723480</v>
+        <v>127723531</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445314</v>
+        <v>445524</v>
       </c>
       <c r="R6" t="n">
-        <v>6768485</v>
+        <v>6768371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723421</v>
+        <v>127723480</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445361</v>
+        <v>445314</v>
       </c>
       <c r="R7" t="n">
-        <v>6768495</v>
+        <v>6768485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1230,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723416</v>
+        <v>127723434</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445426</v>
+        <v>445345</v>
       </c>
       <c r="R8" t="n">
-        <v>6768417</v>
+        <v>6768366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723493</v>
+        <v>127723416</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445363</v>
+        <v>445426</v>
       </c>
       <c r="R9" t="n">
-        <v>6768410</v>
+        <v>6768417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1424,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723531</v>
+        <v>127723493</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445524</v>
+        <v>445363</v>
       </c>
       <c r="R10" t="n">
-        <v>6768371</v>
+        <v>6768410</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723424</v>
+        <v>127722873</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1559,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445311</v>
+        <v>445364</v>
       </c>
       <c r="R11" t="n">
-        <v>6768500</v>
+        <v>6768295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723445</v>
+        <v>127723602</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445446</v>
+        <v>445339</v>
       </c>
       <c r="R12" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723512</v>
+        <v>127723606</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445476</v>
+        <v>445475</v>
       </c>
       <c r="R13" t="n">
-        <v>6768436</v>
+        <v>6768378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723602</v>
+        <v>127723512</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445339</v>
+        <v>445476</v>
       </c>
       <c r="R14" t="n">
         <v>6768436</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723606</v>
+        <v>127723445</v>
       </c>
       <c r="B15" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445475</v>
+        <v>445446</v>
       </c>
       <c r="R15" t="n">
-        <v>6768378</v>
+        <v>6768306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723517</v>
+        <v>127723442</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445463</v>
+        <v>445407</v>
       </c>
       <c r="R17" t="n">
-        <v>6768439</v>
+        <v>6768295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723442</v>
+        <v>127723517</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445407</v>
+        <v>445463</v>
       </c>
       <c r="R19" t="n">
-        <v>6768295</v>
+        <v>6768439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723527</v>
+        <v>127723525</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445476</v>
+        <v>445465</v>
       </c>
       <c r="R22" t="n">
-        <v>6768382</v>
+        <v>6768379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723412</v>
+        <v>127723527</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445423</v>
+        <v>445476</v>
       </c>
       <c r="R23" t="n">
-        <v>6768342</v>
+        <v>6768382</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723525</v>
+        <v>127723412</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445465</v>
+        <v>445423</v>
       </c>
       <c r="R26" t="n">
-        <v>6768379</v>
+        <v>6768342</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,45 +3105,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723523</v>
+        <v>127723028</v>
       </c>
       <c r="B27" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445451</v>
+        <v>445345</v>
       </c>
       <c r="R27" t="n">
-        <v>6768402</v>
+        <v>6768382</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3170,12 +3175,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3202,7 +3207,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723529</v>
+        <v>127723538</v>
       </c>
       <c r="B28" t="n">
         <v>79029</v>
@@ -3237,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445507</v>
+        <v>445485</v>
       </c>
       <c r="R28" t="n">
-        <v>6768383</v>
+        <v>6768313</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,7 +3304,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723538</v>
+        <v>127723523</v>
       </c>
       <c r="B29" t="n">
         <v>79029</v>
@@ -3334,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445485</v>
+        <v>445451</v>
       </c>
       <c r="R29" t="n">
-        <v>6768313</v>
+        <v>6768402</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,7 +3401,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723487</v>
+        <v>127723428</v>
       </c>
       <c r="B30" t="n">
         <v>79029</v>
@@ -3431,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445328</v>
+        <v>445329</v>
       </c>
       <c r="R30" t="n">
-        <v>6768445</v>
+        <v>6768465</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3461,12 +3466,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3493,7 +3498,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723428</v>
+        <v>127723487</v>
       </c>
       <c r="B31" t="n">
         <v>79029</v>
@@ -3528,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445329</v>
+        <v>445328</v>
       </c>
       <c r="R31" t="n">
-        <v>6768465</v>
+        <v>6768445</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3558,12 +3563,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3590,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722895</v>
+        <v>127723529</v>
       </c>
       <c r="B32" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3601,39 +3606,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445370</v>
+        <v>445507</v>
       </c>
       <c r="R32" t="n">
-        <v>6768276</v>
+        <v>6768383</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3692,38 +3692,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723028</v>
+        <v>127722895</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>57669</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445345</v>
+        <v>445370</v>
       </c>
       <c r="R33" t="n">
-        <v>6768382</v>
+        <v>6768276</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723603</v>
+        <v>127723515</v>
       </c>
       <c r="B34" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445353</v>
+        <v>445465</v>
       </c>
       <c r="R34" t="n">
-        <v>6768433</v>
+        <v>6768438</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723431</v>
+        <v>127723446</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445369</v>
+        <v>445453</v>
       </c>
       <c r="R36" t="n">
-        <v>6768408</v>
+        <v>6768321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723536</v>
+        <v>127723431</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445500</v>
+        <v>445369</v>
       </c>
       <c r="R37" t="n">
-        <v>6768348</v>
+        <v>6768408</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723446</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445453</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723515</v>
+        <v>127723603</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445465</v>
+        <v>445353</v>
       </c>
       <c r="R39" t="n">
-        <v>6768438</v>
+        <v>6768433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4575,7 +4575,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723427</v>
+        <v>127723418</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445322</v>
+        <v>445411</v>
       </c>
       <c r="R42" t="n">
-        <v>6768457</v>
+        <v>6768470</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723418</v>
+        <v>127723427</v>
       </c>
       <c r="B43" t="n">
         <v>79029</v>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445411</v>
+        <v>445322</v>
       </c>
       <c r="R43" t="n">
-        <v>6768470</v>
+        <v>6768457</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723534</v>
+        <v>127723521</v>
       </c>
       <c r="B46" t="n">
         <v>79029</v>
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445528</v>
+        <v>445445</v>
       </c>
       <c r="R46" t="n">
-        <v>6768349</v>
+        <v>6768409</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723521</v>
+        <v>127723534</v>
       </c>
       <c r="B47" t="n">
         <v>79029</v>
@@ -5095,10 +5095,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445445</v>
+        <v>445528</v>
       </c>
       <c r="R47" t="n">
-        <v>6768409</v>
+        <v>6768349</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5157,7 +5157,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723025</v>
+        <v>127723026</v>
       </c>
       <c r="B48" t="n">
         <v>8450</v>
@@ -5197,10 +5197,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445397</v>
+        <v>445387</v>
       </c>
       <c r="R48" t="n">
-        <v>6768481</v>
+        <v>6768492</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723026</v>
+        <v>127723025</v>
       </c>
       <c r="B49" t="n">
         <v>8450</v>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445387</v>
+        <v>445397</v>
       </c>
       <c r="R49" t="n">
-        <v>6768492</v>
+        <v>6768481</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5361,7 +5361,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723501</v>
+        <v>127723478</v>
       </c>
       <c r="B50" t="n">
         <v>79029</v>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445430</v>
+        <v>445305</v>
       </c>
       <c r="R50" t="n">
-        <v>6768379</v>
+        <v>6768502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723478</v>
+        <v>127723501</v>
       </c>
       <c r="B51" t="n">
         <v>79029</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445305</v>
+        <v>445430</v>
       </c>
       <c r="R51" t="n">
-        <v>6768502</v>
+        <v>6768379</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723444</v>
+        <v>127722829</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445432</v>
+        <v>445339</v>
       </c>
       <c r="R52" t="n">
-        <v>6768299</v>
+        <v>6768436</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5652,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127723425</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445321</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768501</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723425</v>
+        <v>127722889</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,34 +5760,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445321</v>
+        <v>445372</v>
       </c>
       <c r="R54" t="n">
-        <v>6768501</v>
+        <v>6768323</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5846,10 +5851,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722829</v>
+        <v>127723524</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,21 +5862,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5881,10 +5886,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445339</v>
+        <v>445455</v>
       </c>
       <c r="R55" t="n">
-        <v>6768436</v>
+        <v>6768391</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,7 +5948,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723524</v>
+        <v>127723430</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -5978,10 +5983,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445455</v>
+        <v>445357</v>
       </c>
       <c r="R56" t="n">
-        <v>6768391</v>
+        <v>6768451</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6008,12 +6013,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6040,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722889</v>
+        <v>127723444</v>
       </c>
       <c r="B57" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6051,39 +6056,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445372</v>
+        <v>445432</v>
       </c>
       <c r="R57" t="n">
-        <v>6768323</v>
+        <v>6768299</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6239,7 +6239,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723499</v>
+        <v>127723526</v>
       </c>
       <c r="B59" t="n">
         <v>79029</v>
@@ -6274,10 +6274,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445418</v>
+        <v>445468</v>
       </c>
       <c r="R59" t="n">
-        <v>6768394</v>
+        <v>6768377</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723526</v>
+        <v>127723499</v>
       </c>
       <c r="B60" t="n">
         <v>79029</v>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445468</v>
+        <v>445418</v>
       </c>
       <c r="R60" t="n">
-        <v>6768377</v>
+        <v>6768394</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6836,7 +6836,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723522</v>
+        <v>127723496</v>
       </c>
       <c r="B65" t="n">
         <v>79029</v>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445457</v>
+        <v>445376</v>
       </c>
       <c r="R65" t="n">
-        <v>6768411</v>
+        <v>6768426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6933,7 +6933,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723514</v>
+        <v>127723519</v>
       </c>
       <c r="B66" t="n">
         <v>79029</v>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445468</v>
+        <v>445434</v>
       </c>
       <c r="R66" t="n">
-        <v>6768439</v>
+        <v>6768437</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R67" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7095,12 +7095,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7127,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723506</v>
+        <v>127723522</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445509</v>
+        <v>445457</v>
       </c>
       <c r="R68" t="n">
-        <v>6768424</v>
+        <v>6768411</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723489</v>
+        <v>127723439</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445349</v>
+        <v>445382</v>
       </c>
       <c r="R69" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7321,7 +7321,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723455</v>
+        <v>127723514</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445417</v>
+        <v>445468</v>
       </c>
       <c r="R70" t="n">
-        <v>6768483</v>
+        <v>6768439</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,7 +7418,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723519</v>
+        <v>127723455</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445434</v>
+        <v>445417</v>
       </c>
       <c r="R71" t="n">
-        <v>6768437</v>
+        <v>6768483</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7515,7 +7515,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723496</v>
+        <v>127723528</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445376</v>
+        <v>445493</v>
       </c>
       <c r="R72" t="n">
-        <v>6768426</v>
+        <v>6768388</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723511</v>
+        <v>127723506</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445497</v>
+        <v>445509</v>
       </c>
       <c r="R73" t="n">
-        <v>6768438</v>
+        <v>6768424</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,7 +7709,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723528</v>
+        <v>127723511</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445493</v>
+        <v>445497</v>
       </c>
       <c r="R74" t="n">
-        <v>6768388</v>
+        <v>6768438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723560</v>
+        <v>127723030</v>
       </c>
       <c r="B78" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8133,34 +8133,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445433</v>
+        <v>445376</v>
       </c>
       <c r="R78" t="n">
-        <v>6768412</v>
+        <v>6768336</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8192,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8219,45 +8224,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723415</v>
+        <v>127722931</v>
       </c>
       <c r="B79" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445422</v>
+        <v>445518</v>
       </c>
       <c r="R79" t="n">
-        <v>6768387</v>
+        <v>6768355</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,32 +8326,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723411</v>
+        <v>127723560</v>
       </c>
       <c r="B80" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8361,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445410</v>
+        <v>445433</v>
       </c>
       <c r="R80" t="n">
-        <v>6768338</v>
+        <v>6768412</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8381,12 +8391,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8413,7 +8423,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723494</v>
+        <v>127723432</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8448,10 +8458,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445355</v>
+        <v>445360</v>
       </c>
       <c r="R81" t="n">
-        <v>6768420</v>
+        <v>6768399</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8478,12 +8488,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8510,7 +8520,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723537</v>
+        <v>127723411</v>
       </c>
       <c r="B82" t="n">
         <v>79029</v>
@@ -8545,10 +8555,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445488</v>
+        <v>445410</v>
       </c>
       <c r="R82" t="n">
-        <v>6768315</v>
+        <v>6768338</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8575,12 +8585,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8607,7 +8617,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723533</v>
+        <v>127723415</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8642,10 +8652,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445523</v>
+        <v>445422</v>
       </c>
       <c r="R83" t="n">
-        <v>6768356</v>
+        <v>6768387</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8672,12 +8682,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,7 +8714,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723432</v>
+        <v>127723420</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8739,10 +8749,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445360</v>
+        <v>445395</v>
       </c>
       <c r="R84" t="n">
-        <v>6768399</v>
+        <v>6768485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,7 +8811,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723423</v>
+        <v>127723494</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8836,10 +8846,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445325</v>
+        <v>445355</v>
       </c>
       <c r="R85" t="n">
-        <v>6768515</v>
+        <v>6768420</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8866,12 +8876,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8898,7 +8908,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723420</v>
+        <v>127723423</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8933,10 +8943,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445395</v>
+        <v>445325</v>
       </c>
       <c r="R86" t="n">
-        <v>6768485</v>
+        <v>6768515</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8995,50 +9005,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127722931</v>
+        <v>127723537</v>
       </c>
       <c r="B87" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445518</v>
+        <v>445488</v>
       </c>
       <c r="R87" t="n">
-        <v>6768355</v>
+        <v>6768315</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9065,12 +9070,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9097,50 +9102,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722930</v>
+        <v>127722825</v>
       </c>
       <c r="B88" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445390</v>
+        <v>445386</v>
       </c>
       <c r="R88" t="n">
-        <v>6768381</v>
+        <v>6768493</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9167,12 +9167,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9199,50 +9199,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723030</v>
+        <v>127723533</v>
       </c>
       <c r="B89" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445376</v>
+        <v>445523</v>
       </c>
       <c r="R89" t="n">
-        <v>6768336</v>
+        <v>6768356</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9269,12 +9264,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9301,45 +9296,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722825</v>
+        <v>127722930</v>
       </c>
       <c r="B90" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445386</v>
+        <v>445390</v>
       </c>
       <c r="R90" t="n">
-        <v>6768493</v>
+        <v>6768381</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723426</v>
+        <v>127723452</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445324</v>
+        <v>445473</v>
       </c>
       <c r="R92" t="n">
-        <v>6768470</v>
+        <v>6768325</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,7 +9592,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723452</v>
+        <v>127723504</v>
       </c>
       <c r="B93" t="n">
         <v>79029</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445473</v>
+        <v>445449</v>
       </c>
       <c r="R93" t="n">
-        <v>6768325</v>
+        <v>6768387</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9786,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723504</v>
+        <v>127723426</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9821,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445449</v>
+        <v>445324</v>
       </c>
       <c r="R95" t="n">
-        <v>6768387</v>
+        <v>6768470</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10082,7 +10082,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723440</v>
+        <v>127723454</v>
       </c>
       <c r="B98" t="n">
         <v>79029</v>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445394</v>
+        <v>445421</v>
       </c>
       <c r="R98" t="n">
-        <v>6768290</v>
+        <v>6768465</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,12 +10147,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10179,7 +10179,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723490</v>
+        <v>127723447</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445353</v>
+        <v>445458</v>
       </c>
       <c r="R99" t="n">
-        <v>6768438</v>
+        <v>6768338</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723447</v>
+        <v>127723535</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445458</v>
+        <v>445518</v>
       </c>
       <c r="R100" t="n">
-        <v>6768338</v>
+        <v>6768343</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723535</v>
+        <v>127723483</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445518</v>
+        <v>445310</v>
       </c>
       <c r="R101" t="n">
-        <v>6768343</v>
+        <v>6768467</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723483</v>
+        <v>127723440</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445310</v>
+        <v>445394</v>
       </c>
       <c r="R102" t="n">
-        <v>6768467</v>
+        <v>6768290</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723454</v>
+        <v>127722918</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,34 +10578,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445421</v>
+        <v>445382</v>
       </c>
       <c r="R103" t="n">
-        <v>6768465</v>
+        <v>6768422</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10638,6 +10643,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10664,38 +10674,38 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127722918</v>
+        <v>127723027</v>
       </c>
       <c r="B104" t="n">
-        <v>57672</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -10704,10 +10714,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445382</v>
+        <v>445343</v>
       </c>
       <c r="R104" t="n">
-        <v>6768422</v>
+        <v>6768460</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10734,17 +10744,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10771,50 +10776,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723027</v>
+        <v>127723605</v>
       </c>
       <c r="B105" t="n">
-        <v>8450</v>
+        <v>78696</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445343</v>
+        <v>445403</v>
       </c>
       <c r="R105" t="n">
-        <v>6768460</v>
+        <v>6768385</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10841,12 +10841,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10970,10 +10970,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723605</v>
+        <v>127723490</v>
       </c>
       <c r="B107" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10981,21 +10981,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11005,10 +11005,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445403</v>
+        <v>445353</v>
       </c>
       <c r="R107" t="n">
-        <v>6768385</v>
+        <v>6768438</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723495</v>
+        <v>127723593</v>
       </c>
       <c r="B108" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,21 +11078,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445361</v>
+        <v>445417</v>
       </c>
       <c r="R108" t="n">
-        <v>6768425</v>
+        <v>6768470</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B110" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R110" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11358,7 +11358,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723429</v>
+        <v>127723495</v>
       </c>
       <c r="B111" t="n">
         <v>79029</v>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445339</v>
+        <v>445361</v>
       </c>
       <c r="R111" t="n">
-        <v>6768457</v>
+        <v>6768425</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723593</v>
+        <v>127722832</v>
       </c>
       <c r="B112" t="n">
-        <v>78696</v>
+        <v>79647</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445417</v>
+        <v>445457</v>
       </c>
       <c r="R112" t="n">
-        <v>6768470</v>
+        <v>6768397</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11649,7 +11649,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723498</v>
+        <v>127723453</v>
       </c>
       <c r="B114" t="n">
         <v>79029</v>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445386</v>
+        <v>445418</v>
       </c>
       <c r="R114" t="n">
-        <v>6768393</v>
+        <v>6768439</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,7 +11746,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B115" t="n">
         <v>79029</v>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R115" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11940,7 +11940,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723532</v>
+        <v>127723530</v>
       </c>
       <c r="B117" t="n">
         <v>79029</v>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445523</v>
+        <v>445515</v>
       </c>
       <c r="R117" t="n">
-        <v>6768362</v>
+        <v>6768378</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,7 +12037,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723453</v>
+        <v>127723498</v>
       </c>
       <c r="B118" t="n">
         <v>79029</v>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445418</v>
+        <v>445386</v>
       </c>
       <c r="R118" t="n">
-        <v>6768439</v>
+        <v>6768393</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723410</v>
+        <v>127723443</v>
       </c>
       <c r="B119" t="n">
         <v>79029</v>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445434</v>
+        <v>445422</v>
       </c>
       <c r="R119" t="n">
-        <v>6768336</v>
+        <v>6768295</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723503</v>
+        <v>127723410</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445439</v>
+        <v>445434</v>
       </c>
       <c r="R120" t="n">
-        <v>6768381</v>
+        <v>6768336</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127722831</v>
+        <v>127723505</v>
       </c>
       <c r="B121" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12339,21 +12339,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445370</v>
+        <v>445493</v>
       </c>
       <c r="R121" t="n">
-        <v>6768425</v>
+        <v>6768418</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723443</v>
+        <v>127723438</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445422</v>
+        <v>445375</v>
       </c>
       <c r="R122" t="n">
-        <v>6768295</v>
+        <v>6768277</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723505</v>
+        <v>127723503</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445493</v>
+        <v>445439</v>
       </c>
       <c r="R123" t="n">
-        <v>6768418</v>
+        <v>6768381</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723438</v>
+        <v>127722831</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445375</v>
+        <v>445370</v>
       </c>
       <c r="R124" t="n">
-        <v>6768277</v>
+        <v>6768425</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R14" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R15" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723561</v>
+        <v>127723435</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445519</v>
+        <v>445375</v>
       </c>
       <c r="R16" t="n">
-        <v>6768373</v>
+        <v>6768348</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R18" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723517</v>
+        <v>127723520</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445463</v>
+        <v>445439</v>
       </c>
       <c r="R19" t="n">
-        <v>6768439</v>
+        <v>6768423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723520</v>
+        <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445439</v>
+        <v>445519</v>
       </c>
       <c r="R20" t="n">
-        <v>6768423</v>
+        <v>6768373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723560</v>
+        <v>127722930</v>
       </c>
       <c r="B80" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8337,34 +8337,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445433</v>
+        <v>445390</v>
       </c>
       <c r="R80" t="n">
-        <v>6768412</v>
+        <v>6768381</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8423,7 +8428,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723432</v>
+        <v>127723533</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8458,10 +8463,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445360</v>
+        <v>445523</v>
       </c>
       <c r="R81" t="n">
-        <v>6768399</v>
+        <v>6768356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8488,12 +8493,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8520,32 +8525,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723411</v>
+        <v>127723560</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8555,10 +8560,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445410</v>
+        <v>445433</v>
       </c>
       <c r="R82" t="n">
-        <v>6768338</v>
+        <v>6768412</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8585,12 +8590,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8617,7 +8622,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723415</v>
+        <v>127723432</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8652,10 +8657,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445422</v>
+        <v>445360</v>
       </c>
       <c r="R83" t="n">
-        <v>6768387</v>
+        <v>6768399</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8714,7 +8719,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723420</v>
+        <v>127723411</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8749,10 +8754,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445395</v>
+        <v>445410</v>
       </c>
       <c r="R84" t="n">
-        <v>6768485</v>
+        <v>6768338</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8811,7 +8816,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723494</v>
+        <v>127723415</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445355</v>
+        <v>445422</v>
       </c>
       <c r="R85" t="n">
-        <v>6768420</v>
+        <v>6768387</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8876,12 +8881,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8908,7 +8913,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723423</v>
+        <v>127723420</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445325</v>
+        <v>445395</v>
       </c>
       <c r="R86" t="n">
-        <v>6768515</v>
+        <v>6768485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9005,7 +9010,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723537</v>
+        <v>127723494</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9040,10 +9045,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445488</v>
+        <v>445355</v>
       </c>
       <c r="R87" t="n">
-        <v>6768315</v>
+        <v>6768420</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9107,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722825</v>
+        <v>127723423</v>
       </c>
       <c r="B88" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9118,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9142,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445386</v>
+        <v>445325</v>
       </c>
       <c r="R88" t="n">
-        <v>6768493</v>
+        <v>6768515</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9199,7 +9204,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723533</v>
+        <v>127723537</v>
       </c>
       <c r="B89" t="n">
         <v>79029</v>
@@ -9234,10 +9239,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445523</v>
+        <v>445488</v>
       </c>
       <c r="R89" t="n">
-        <v>6768356</v>
+        <v>6768315</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9296,50 +9301,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722930</v>
+        <v>127722825</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445390</v>
+        <v>445386</v>
       </c>
       <c r="R90" t="n">
-        <v>6768381</v>
+        <v>6768493</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723436</v>
+        <v>127723426</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445366</v>
+        <v>445324</v>
       </c>
       <c r="R91" t="n">
-        <v>6768321</v>
+        <v>6768470</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723452</v>
+        <v>127723414</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445473</v>
+        <v>445429</v>
       </c>
       <c r="R92" t="n">
-        <v>6768325</v>
+        <v>6768360</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,45 +9592,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723504</v>
+        <v>127723029</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445449</v>
+        <v>445351</v>
       </c>
       <c r="R93" t="n">
-        <v>6768387</v>
+        <v>6768348</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9662,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,7 +9694,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723497</v>
+        <v>127723436</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9724,10 +9729,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445376</v>
+        <v>445366</v>
       </c>
       <c r="R94" t="n">
-        <v>6768407</v>
+        <v>6768321</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9759,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,7 +9791,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723426</v>
+        <v>127723452</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9821,10 +9826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445324</v>
+        <v>445473</v>
       </c>
       <c r="R95" t="n">
-        <v>6768470</v>
+        <v>6768325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9856,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9883,7 +9888,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723414</v>
+        <v>127723504</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9918,10 +9923,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445429</v>
+        <v>445449</v>
       </c>
       <c r="R96" t="n">
-        <v>6768360</v>
+        <v>6768387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,12 +9953,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9980,50 +9985,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723029</v>
+        <v>127723497</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445351</v>
+        <v>445376</v>
       </c>
       <c r="R97" t="n">
-        <v>6768348</v>
+        <v>6768407</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723454</v>
+        <v>127723605</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445421</v>
+        <v>445403</v>
       </c>
       <c r="R98" t="n">
-        <v>6768465</v>
+        <v>6768385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723447</v>
+        <v>127723454</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445458</v>
+        <v>445421</v>
       </c>
       <c r="R99" t="n">
-        <v>6768338</v>
+        <v>6768465</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723535</v>
+        <v>127723447</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445518</v>
+        <v>445458</v>
       </c>
       <c r="R100" t="n">
-        <v>6768343</v>
+        <v>6768338</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723483</v>
+        <v>127723535</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445310</v>
+        <v>445518</v>
       </c>
       <c r="R101" t="n">
-        <v>6768467</v>
+        <v>6768343</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723440</v>
+        <v>127723483</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445394</v>
+        <v>445310</v>
       </c>
       <c r="R102" t="n">
-        <v>6768290</v>
+        <v>6768467</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722918</v>
+        <v>127723440</v>
       </c>
       <c r="B103" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,39 +10578,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445382</v>
+        <v>445394</v>
       </c>
       <c r="R103" t="n">
-        <v>6768422</v>
+        <v>6768290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10637,17 +10632,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10674,50 +10664,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723027</v>
+        <v>127723490</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445343</v>
+        <v>445353</v>
       </c>
       <c r="R104" t="n">
-        <v>6768460</v>
+        <v>6768438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10744,12 +10729,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10776,10 +10761,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723605</v>
+        <v>127722918</v>
       </c>
       <c r="B105" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10787,34 +10772,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445403</v>
+        <v>445382</v>
       </c>
       <c r="R105" t="n">
-        <v>6768385</v>
+        <v>6768422</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10847,6 +10837,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10970,45 +10965,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723490</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445353</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768438</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R14" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R15" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723435</v>
+        <v>127723561</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445375</v>
+        <v>445519</v>
       </c>
       <c r="R16" t="n">
-        <v>6768348</v>
+        <v>6768373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723517</v>
+        <v>127723435</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445463</v>
+        <v>445375</v>
       </c>
       <c r="R18" t="n">
-        <v>6768439</v>
+        <v>6768348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723520</v>
+        <v>127723517</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445439</v>
+        <v>445463</v>
       </c>
       <c r="R19" t="n">
-        <v>6768423</v>
+        <v>6768439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723561</v>
+        <v>127723520</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445519</v>
+        <v>445439</v>
       </c>
       <c r="R20" t="n">
-        <v>6768373</v>
+        <v>6768423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723525</v>
+        <v>127723412</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445465</v>
+        <v>445423</v>
       </c>
       <c r="R22" t="n">
-        <v>6768379</v>
+        <v>6768342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723527</v>
+        <v>127723525</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445476</v>
+        <v>445465</v>
       </c>
       <c r="R23" t="n">
-        <v>6768382</v>
+        <v>6768379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723417</v>
+        <v>127723527</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445413</v>
+        <v>445476</v>
       </c>
       <c r="R24" t="n">
-        <v>6768451</v>
+        <v>6768382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723433</v>
+        <v>127723417</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445354</v>
+        <v>445413</v>
       </c>
       <c r="R25" t="n">
-        <v>6768399</v>
+        <v>6768451</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723412</v>
+        <v>127723433</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445423</v>
+        <v>445354</v>
       </c>
       <c r="R26" t="n">
-        <v>6768342</v>
+        <v>6768399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723515</v>
+        <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445465</v>
+        <v>445353</v>
       </c>
       <c r="R34" t="n">
-        <v>6768438</v>
+        <v>6768433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723482</v>
+        <v>127723515</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445318</v>
+        <v>445465</v>
       </c>
       <c r="R35" t="n">
-        <v>6768474</v>
+        <v>6768438</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723446</v>
+        <v>127723482</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445453</v>
+        <v>445318</v>
       </c>
       <c r="R36" t="n">
-        <v>6768321</v>
+        <v>6768474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723431</v>
+        <v>127723446</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445369</v>
+        <v>445453</v>
       </c>
       <c r="R37" t="n">
-        <v>6768408</v>
+        <v>6768321</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723431</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445369</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768408</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723603</v>
+        <v>127723536</v>
       </c>
       <c r="B39" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445353</v>
+        <v>445500</v>
       </c>
       <c r="R39" t="n">
-        <v>6768433</v>
+        <v>6768348</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723565</v>
+        <v>127723422</v>
       </c>
       <c r="B40" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445406</v>
+        <v>445332</v>
       </c>
       <c r="R40" t="n">
-        <v>6768484</v>
+        <v>6768518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4447,11 +4447,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4478,7 +4473,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723422</v>
+        <v>127723418</v>
       </c>
       <c r="B41" t="n">
         <v>79029</v>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445332</v>
+        <v>445411</v>
       </c>
       <c r="R41" t="n">
-        <v>6768518</v>
+        <v>6768470</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723418</v>
+        <v>127723565</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445411</v>
+        <v>445406</v>
       </c>
       <c r="R42" t="n">
-        <v>6768470</v>
+        <v>6768484</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127722829</v>
+        <v>127723524</v>
       </c>
       <c r="B52" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445339</v>
+        <v>445455</v>
       </c>
       <c r="R52" t="n">
-        <v>6768436</v>
+        <v>6768391</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723425</v>
+        <v>127723430</v>
       </c>
       <c r="B53" t="n">
         <v>79029</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445321</v>
+        <v>445357</v>
       </c>
       <c r="R53" t="n">
-        <v>6768501</v>
+        <v>6768451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127722889</v>
+        <v>127723444</v>
       </c>
       <c r="B54" t="n">
-        <v>57669</v>
+        <v>79029</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,39 +5760,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445372</v>
+        <v>445432</v>
       </c>
       <c r="R54" t="n">
-        <v>6768323</v>
+        <v>6768299</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5851,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723524</v>
+        <v>127722829</v>
       </c>
       <c r="B55" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5862,21 +5857,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5886,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445455</v>
+        <v>445339</v>
       </c>
       <c r="R55" t="n">
-        <v>6768391</v>
+        <v>6768436</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5948,7 +5943,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723430</v>
+        <v>127723425</v>
       </c>
       <c r="B56" t="n">
         <v>79029</v>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445357</v>
+        <v>445321</v>
       </c>
       <c r="R56" t="n">
-        <v>6768451</v>
+        <v>6768501</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6045,10 +6040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723444</v>
+        <v>127722889</v>
       </c>
       <c r="B57" t="n">
-        <v>79029</v>
+        <v>57669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,34 +6051,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445432</v>
+        <v>445372</v>
       </c>
       <c r="R57" t="n">
-        <v>6768299</v>
+        <v>6768323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -8326,10 +8326,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127722930</v>
+        <v>127723560</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8337,39 +8337,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445390</v>
+        <v>445433</v>
       </c>
       <c r="R80" t="n">
-        <v>6768381</v>
+        <v>6768412</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8428,7 +8423,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723533</v>
+        <v>127723432</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8463,10 +8458,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445523</v>
+        <v>445360</v>
       </c>
       <c r="R81" t="n">
-        <v>6768356</v>
+        <v>6768399</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8493,12 +8488,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8525,32 +8520,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723560</v>
+        <v>127723411</v>
       </c>
       <c r="B82" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8560,10 +8555,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445433</v>
+        <v>445410</v>
       </c>
       <c r="R82" t="n">
-        <v>6768412</v>
+        <v>6768338</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8590,12 +8585,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8622,7 +8617,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723432</v>
+        <v>127723415</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8657,10 +8652,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445360</v>
+        <v>445422</v>
       </c>
       <c r="R83" t="n">
-        <v>6768399</v>
+        <v>6768387</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8719,7 +8714,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723411</v>
+        <v>127723420</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445410</v>
+        <v>445395</v>
       </c>
       <c r="R84" t="n">
-        <v>6768338</v>
+        <v>6768485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8816,7 +8811,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723415</v>
+        <v>127723494</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445422</v>
+        <v>445355</v>
       </c>
       <c r="R85" t="n">
-        <v>6768387</v>
+        <v>6768420</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8881,12 +8876,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8913,7 +8908,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723420</v>
+        <v>127723423</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445395</v>
+        <v>445325</v>
       </c>
       <c r="R86" t="n">
-        <v>6768485</v>
+        <v>6768515</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9010,7 +9005,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723494</v>
+        <v>127723537</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9045,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445355</v>
+        <v>445488</v>
       </c>
       <c r="R87" t="n">
-        <v>6768420</v>
+        <v>6768315</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9107,10 +9102,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723423</v>
+        <v>127722825</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9118,21 +9113,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9142,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445325</v>
+        <v>445386</v>
       </c>
       <c r="R88" t="n">
-        <v>6768515</v>
+        <v>6768493</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9204,7 +9199,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723537</v>
+        <v>127723533</v>
       </c>
       <c r="B89" t="n">
         <v>79029</v>
@@ -9239,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445488</v>
+        <v>445523</v>
       </c>
       <c r="R89" t="n">
-        <v>6768315</v>
+        <v>6768356</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9301,45 +9296,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722825</v>
+        <v>127722930</v>
       </c>
       <c r="B90" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445386</v>
+        <v>445390</v>
       </c>
       <c r="R90" t="n">
-        <v>6768493</v>
+        <v>6768381</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723443</v>
+        <v>127722831</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445422</v>
+        <v>445370</v>
       </c>
       <c r="R119" t="n">
-        <v>6768295</v>
+        <v>6768425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723410</v>
+        <v>127723503</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445434</v>
+        <v>445439</v>
       </c>
       <c r="R120" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,7 +12328,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723505</v>
+        <v>127723443</v>
       </c>
       <c r="B121" t="n">
         <v>79029</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445493</v>
+        <v>445422</v>
       </c>
       <c r="R121" t="n">
-        <v>6768418</v>
+        <v>6768295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723438</v>
+        <v>127723410</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445375</v>
+        <v>445434</v>
       </c>
       <c r="R122" t="n">
-        <v>6768277</v>
+        <v>6768336</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723503</v>
+        <v>127723505</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445439</v>
+        <v>445493</v>
       </c>
       <c r="R123" t="n">
-        <v>6768381</v>
+        <v>6768418</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722831</v>
+        <v>127723438</v>
       </c>
       <c r="B124" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445370</v>
+        <v>445375</v>
       </c>
       <c r="R124" t="n">
-        <v>6768425</v>
+        <v>6768277</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723518</v>
+        <v>127722873</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445431</v>
+        <v>445364</v>
       </c>
       <c r="R2" t="n">
-        <v>6768443</v>
+        <v>6768295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723424</v>
+        <v>127723479</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445311</v>
+        <v>445309</v>
       </c>
       <c r="R3" t="n">
-        <v>6768500</v>
+        <v>6768491</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,7 +874,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723479</v>
+        <v>127723421</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445309</v>
+        <v>445361</v>
       </c>
       <c r="R4" t="n">
-        <v>6768491</v>
+        <v>6768495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,7 +971,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723421</v>
+        <v>127723531</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445524</v>
       </c>
       <c r="R5" t="n">
-        <v>6768495</v>
+        <v>6768371</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1031,12 +1036,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,7 +1068,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723531</v>
+        <v>127723480</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445524</v>
+        <v>445314</v>
       </c>
       <c r="R6" t="n">
-        <v>6768371</v>
+        <v>6768485</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723480</v>
+        <v>127723434</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445314</v>
+        <v>445345</v>
       </c>
       <c r="R7" t="n">
-        <v>6768485</v>
+        <v>6768366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1225,12 +1230,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1257,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723434</v>
+        <v>127723416</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445345</v>
+        <v>445426</v>
       </c>
       <c r="R8" t="n">
-        <v>6768366</v>
+        <v>6768417</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723416</v>
+        <v>127723493</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445426</v>
+        <v>445363</v>
       </c>
       <c r="R9" t="n">
-        <v>6768417</v>
+        <v>6768410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,7 +1456,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723493</v>
+        <v>127723518</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445363</v>
+        <v>445431</v>
       </c>
       <c r="R10" t="n">
-        <v>6768410</v>
+        <v>6768443</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127722873</v>
+        <v>127723424</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445364</v>
+        <v>445311</v>
       </c>
       <c r="R11" t="n">
-        <v>6768295</v>
+        <v>6768500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R14" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R15" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R22" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723525</v>
+        <v>127723527</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445465</v>
+        <v>445476</v>
       </c>
       <c r="R23" t="n">
-        <v>6768379</v>
+        <v>6768382</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723527</v>
+        <v>127723417</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445476</v>
+        <v>445413</v>
       </c>
       <c r="R24" t="n">
-        <v>6768382</v>
+        <v>6768451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723417</v>
+        <v>127723433</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445413</v>
+        <v>445354</v>
       </c>
       <c r="R25" t="n">
-        <v>6768451</v>
+        <v>6768399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723433</v>
+        <v>127723412</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445354</v>
+        <v>445423</v>
       </c>
       <c r="R26" t="n">
-        <v>6768399</v>
+        <v>6768342</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723603</v>
+        <v>127723515</v>
       </c>
       <c r="B34" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445353</v>
+        <v>445465</v>
       </c>
       <c r="R34" t="n">
-        <v>6768433</v>
+        <v>6768438</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723515</v>
+        <v>127723482</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445465</v>
+        <v>445318</v>
       </c>
       <c r="R35" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723482</v>
+        <v>127723446</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445318</v>
+        <v>445453</v>
       </c>
       <c r="R36" t="n">
-        <v>6768474</v>
+        <v>6768321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723446</v>
+        <v>127723431</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445453</v>
+        <v>445369</v>
       </c>
       <c r="R37" t="n">
-        <v>6768321</v>
+        <v>6768408</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723431</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445369</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768408</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723536</v>
+        <v>127723603</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445500</v>
+        <v>445353</v>
       </c>
       <c r="R39" t="n">
-        <v>6768348</v>
+        <v>6768433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723496</v>
+        <v>127722917</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6847,34 +6847,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445376</v>
+        <v>445329</v>
       </c>
       <c r="R65" t="n">
-        <v>6768426</v>
+        <v>6768466</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6906,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723519</v>
+        <v>127722908</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6944,34 +6954,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445434</v>
+        <v>445329</v>
       </c>
       <c r="R66" t="n">
-        <v>6768437</v>
+        <v>6768474</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6998,12 +7013,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7030,7 +7050,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723489</v>
+        <v>127723496</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7085,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445349</v>
+        <v>445376</v>
       </c>
       <c r="R67" t="n">
-        <v>6768438</v>
+        <v>6768426</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7147,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723522</v>
+        <v>127723519</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445457</v>
+        <v>445434</v>
       </c>
       <c r="R68" t="n">
-        <v>6768411</v>
+        <v>6768437</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7244,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R69" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7309,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7321,7 +7341,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723514</v>
+        <v>127723522</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7356,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445468</v>
+        <v>445457</v>
       </c>
       <c r="R70" t="n">
-        <v>6768439</v>
+        <v>6768411</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,7 +7438,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723455</v>
+        <v>127723439</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7453,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445417</v>
+        <v>445382</v>
       </c>
       <c r="R71" t="n">
-        <v>6768483</v>
+        <v>6768296</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7483,12 +7503,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7515,7 +7535,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723528</v>
+        <v>127723514</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7550,10 +7570,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445493</v>
+        <v>445468</v>
       </c>
       <c r="R72" t="n">
-        <v>6768388</v>
+        <v>6768439</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,7 +7632,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723506</v>
+        <v>127723455</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -7647,10 +7667,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445509</v>
+        <v>445417</v>
       </c>
       <c r="R73" t="n">
-        <v>6768424</v>
+        <v>6768483</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,7 +7729,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723511</v>
+        <v>127723528</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7744,10 +7764,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445497</v>
+        <v>445493</v>
       </c>
       <c r="R74" t="n">
-        <v>6768438</v>
+        <v>6768388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7806,10 +7826,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722917</v>
+        <v>127723506</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,39 +7837,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445329</v>
+        <v>445509</v>
       </c>
       <c r="R75" t="n">
-        <v>6768466</v>
+        <v>6768424</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,17 +7891,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7913,10 +7923,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722908</v>
+        <v>127723511</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7924,39 +7934,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445329</v>
+        <v>445497</v>
       </c>
       <c r="R76" t="n">
-        <v>6768474</v>
+        <v>6768438</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7983,17 +7988,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723426</v>
+        <v>127723436</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445324</v>
+        <v>445366</v>
       </c>
       <c r="R91" t="n">
-        <v>6768470</v>
+        <v>6768321</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723414</v>
+        <v>127723452</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445429</v>
+        <v>445473</v>
       </c>
       <c r="R92" t="n">
-        <v>6768360</v>
+        <v>6768325</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,50 +9592,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723029</v>
+        <v>127723504</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445351</v>
+        <v>445449</v>
       </c>
       <c r="R93" t="n">
-        <v>6768348</v>
+        <v>6768387</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9662,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9694,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723436</v>
+        <v>127723497</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9729,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445366</v>
+        <v>445376</v>
       </c>
       <c r="R94" t="n">
-        <v>6768321</v>
+        <v>6768407</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9759,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9791,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723452</v>
+        <v>127723426</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9826,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445473</v>
+        <v>445324</v>
       </c>
       <c r="R95" t="n">
-        <v>6768325</v>
+        <v>6768470</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9888,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723504</v>
+        <v>127723414</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9923,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445449</v>
+        <v>445429</v>
       </c>
       <c r="R96" t="n">
-        <v>6768387</v>
+        <v>6768360</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9953,12 +9948,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9985,45 +9980,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723497</v>
+        <v>127723029</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445376</v>
+        <v>445351</v>
       </c>
       <c r="R97" t="n">
-        <v>6768407</v>
+        <v>6768348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723605</v>
+        <v>127723454</v>
       </c>
       <c r="B98" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445403</v>
+        <v>445421</v>
       </c>
       <c r="R98" t="n">
-        <v>6768385</v>
+        <v>6768465</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723454</v>
+        <v>127723447</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445421</v>
+        <v>445458</v>
       </c>
       <c r="R99" t="n">
-        <v>6768465</v>
+        <v>6768338</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723447</v>
+        <v>127723535</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445458</v>
+        <v>445518</v>
       </c>
       <c r="R100" t="n">
-        <v>6768338</v>
+        <v>6768343</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723535</v>
+        <v>127723483</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445518</v>
+        <v>445310</v>
       </c>
       <c r="R101" t="n">
-        <v>6768343</v>
+        <v>6768467</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723483</v>
+        <v>127723440</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445310</v>
+        <v>445394</v>
       </c>
       <c r="R102" t="n">
-        <v>6768467</v>
+        <v>6768290</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723440</v>
+        <v>127722918</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,34 +10578,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445394</v>
+        <v>445382</v>
       </c>
       <c r="R103" t="n">
-        <v>6768290</v>
+        <v>6768422</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10632,12 +10637,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10664,45 +10674,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723490</v>
+        <v>127723027</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445353</v>
+        <v>445343</v>
       </c>
       <c r="R104" t="n">
-        <v>6768438</v>
+        <v>6768460</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10729,12 +10744,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10761,10 +10776,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127722918</v>
+        <v>127723605</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>78696</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10772,39 +10787,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445382</v>
+        <v>445403</v>
       </c>
       <c r="R105" t="n">
-        <v>6768422</v>
+        <v>6768385</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10837,11 +10847,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10965,50 +10970,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127723490</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445353</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768438</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -1844,7 +1844,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B14" t="n">
         <v>79029</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R14" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,7 +1941,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B15" t="n">
         <v>79029</v>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R15" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723561</v>
+        <v>127723442</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445519</v>
+        <v>445407</v>
       </c>
       <c r="R16" t="n">
-        <v>6768373</v>
+        <v>6768295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723442</v>
+        <v>127723517</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445407</v>
+        <v>445463</v>
       </c>
       <c r="R17" t="n">
-        <v>6768295</v>
+        <v>6768439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723435</v>
+        <v>127723520</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R18" t="n">
-        <v>6768348</v>
+        <v>6768423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723517</v>
+        <v>127723435</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445463</v>
+        <v>445375</v>
       </c>
       <c r="R19" t="n">
-        <v>6768439</v>
+        <v>6768348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723520</v>
+        <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445439</v>
+        <v>445519</v>
       </c>
       <c r="R20" t="n">
-        <v>6768423</v>
+        <v>6768373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723525</v>
+        <v>127723412</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445465</v>
+        <v>445423</v>
       </c>
       <c r="R22" t="n">
-        <v>6768379</v>
+        <v>6768342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723527</v>
+        <v>127723525</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445476</v>
+        <v>445465</v>
       </c>
       <c r="R23" t="n">
-        <v>6768382</v>
+        <v>6768379</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723417</v>
+        <v>127723527</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445413</v>
+        <v>445476</v>
       </c>
       <c r="R24" t="n">
-        <v>6768451</v>
+        <v>6768382</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723433</v>
+        <v>127723417</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445354</v>
+        <v>445413</v>
       </c>
       <c r="R25" t="n">
-        <v>6768399</v>
+        <v>6768451</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723412</v>
+        <v>127723433</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445423</v>
+        <v>445354</v>
       </c>
       <c r="R26" t="n">
-        <v>6768342</v>
+        <v>6768399</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723515</v>
+        <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445465</v>
+        <v>445353</v>
       </c>
       <c r="R34" t="n">
-        <v>6768438</v>
+        <v>6768433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723482</v>
+        <v>127723515</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445318</v>
+        <v>445465</v>
       </c>
       <c r="R35" t="n">
-        <v>6768474</v>
+        <v>6768438</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723446</v>
+        <v>127723482</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445453</v>
+        <v>445318</v>
       </c>
       <c r="R36" t="n">
-        <v>6768321</v>
+        <v>6768474</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723431</v>
+        <v>127723446</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445369</v>
+        <v>445453</v>
       </c>
       <c r="R37" t="n">
-        <v>6768408</v>
+        <v>6768321</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723431</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445369</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768408</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723603</v>
+        <v>127723536</v>
       </c>
       <c r="B39" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445353</v>
+        <v>445500</v>
       </c>
       <c r="R39" t="n">
-        <v>6768433</v>
+        <v>6768348</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723413</v>
+        <v>127722914</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,34 +6541,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445444</v>
+        <v>445325</v>
       </c>
       <c r="R62" t="n">
-        <v>6768341</v>
+        <v>6768463</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6601,6 +6606,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6627,10 +6637,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,39 +6648,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R63" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6703,11 +6708,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8326,10 +8326,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723560</v>
+        <v>127722930</v>
       </c>
       <c r="B80" t="n">
-        <v>92642</v>
+        <v>8450</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8337,34 +8337,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445433</v>
+        <v>445390</v>
       </c>
       <c r="R80" t="n">
-        <v>6768412</v>
+        <v>6768381</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8423,7 +8428,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723432</v>
+        <v>127723533</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8458,10 +8463,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445360</v>
+        <v>445523</v>
       </c>
       <c r="R81" t="n">
-        <v>6768399</v>
+        <v>6768356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8488,12 +8493,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8520,32 +8525,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723411</v>
+        <v>127723560</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8555,10 +8560,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445410</v>
+        <v>445433</v>
       </c>
       <c r="R82" t="n">
-        <v>6768338</v>
+        <v>6768412</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8585,12 +8590,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8617,7 +8622,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723415</v>
+        <v>127723432</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8652,10 +8657,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445422</v>
+        <v>445360</v>
       </c>
       <c r="R83" t="n">
-        <v>6768387</v>
+        <v>6768399</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8714,7 +8719,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723420</v>
+        <v>127723411</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8749,10 +8754,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445395</v>
+        <v>445410</v>
       </c>
       <c r="R84" t="n">
-        <v>6768485</v>
+        <v>6768338</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8811,7 +8816,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723494</v>
+        <v>127723415</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445355</v>
+        <v>445422</v>
       </c>
       <c r="R85" t="n">
-        <v>6768420</v>
+        <v>6768387</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8876,12 +8881,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8908,7 +8913,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723423</v>
+        <v>127723420</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445325</v>
+        <v>445395</v>
       </c>
       <c r="R86" t="n">
-        <v>6768515</v>
+        <v>6768485</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9005,7 +9010,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723537</v>
+        <v>127723494</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9040,10 +9045,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445488</v>
+        <v>445355</v>
       </c>
       <c r="R87" t="n">
-        <v>6768315</v>
+        <v>6768420</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9107,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722825</v>
+        <v>127723423</v>
       </c>
       <c r="B88" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9118,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9142,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445386</v>
+        <v>445325</v>
       </c>
       <c r="R88" t="n">
-        <v>6768493</v>
+        <v>6768515</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9199,7 +9204,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723533</v>
+        <v>127723537</v>
       </c>
       <c r="B89" t="n">
         <v>79029</v>
@@ -9234,10 +9239,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445523</v>
+        <v>445488</v>
       </c>
       <c r="R89" t="n">
-        <v>6768356</v>
+        <v>6768315</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9296,50 +9301,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722930</v>
+        <v>127722825</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79647</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445390</v>
+        <v>445386</v>
       </c>
       <c r="R90" t="n">
-        <v>6768381</v>
+        <v>6768493</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723436</v>
+        <v>127723426</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445366</v>
+        <v>445324</v>
       </c>
       <c r="R91" t="n">
-        <v>6768321</v>
+        <v>6768470</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723452</v>
+        <v>127723414</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445473</v>
+        <v>445429</v>
       </c>
       <c r="R92" t="n">
-        <v>6768325</v>
+        <v>6768360</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,45 +9592,50 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723504</v>
+        <v>127723029</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445449</v>
+        <v>445351</v>
       </c>
       <c r="R93" t="n">
-        <v>6768387</v>
+        <v>6768348</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9662,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,7 +9694,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723497</v>
+        <v>127723436</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9724,10 +9729,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445376</v>
+        <v>445366</v>
       </c>
       <c r="R94" t="n">
-        <v>6768407</v>
+        <v>6768321</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9759,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,7 +9791,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723426</v>
+        <v>127723452</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9821,10 +9826,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445324</v>
+        <v>445473</v>
       </c>
       <c r="R95" t="n">
-        <v>6768470</v>
+        <v>6768325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9856,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9883,7 +9888,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723414</v>
+        <v>127723504</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9918,10 +9923,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445429</v>
+        <v>445449</v>
       </c>
       <c r="R96" t="n">
-        <v>6768360</v>
+        <v>6768387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,12 +9953,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9980,50 +9985,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723029</v>
+        <v>127723497</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445351</v>
+        <v>445376</v>
       </c>
       <c r="R97" t="n">
-        <v>6768348</v>
+        <v>6768407</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723454</v>
+        <v>127723605</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445421</v>
+        <v>445403</v>
       </c>
       <c r="R98" t="n">
-        <v>6768465</v>
+        <v>6768385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723447</v>
+        <v>127723454</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445458</v>
+        <v>445421</v>
       </c>
       <c r="R99" t="n">
-        <v>6768338</v>
+        <v>6768465</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723535</v>
+        <v>127723447</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445518</v>
+        <v>445458</v>
       </c>
       <c r="R100" t="n">
-        <v>6768343</v>
+        <v>6768338</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723483</v>
+        <v>127723535</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445310</v>
+        <v>445518</v>
       </c>
       <c r="R101" t="n">
-        <v>6768467</v>
+        <v>6768343</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723440</v>
+        <v>127723483</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445394</v>
+        <v>445310</v>
       </c>
       <c r="R102" t="n">
-        <v>6768290</v>
+        <v>6768467</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722918</v>
+        <v>127723440</v>
       </c>
       <c r="B103" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,39 +10578,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445382</v>
+        <v>445394</v>
       </c>
       <c r="R103" t="n">
-        <v>6768422</v>
+        <v>6768290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10637,17 +10632,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10674,50 +10664,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723027</v>
+        <v>127723490</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445343</v>
+        <v>445353</v>
       </c>
       <c r="R104" t="n">
-        <v>6768460</v>
+        <v>6768438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10744,12 +10729,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10776,10 +10761,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723605</v>
+        <v>127722918</v>
       </c>
       <c r="B105" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10787,34 +10772,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445403</v>
+        <v>445382</v>
       </c>
       <c r="R105" t="n">
-        <v>6768385</v>
+        <v>6768422</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10847,6 +10837,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10970,45 +10965,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723490</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445353</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768438</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723442</v>
+        <v>127723561</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445407</v>
+        <v>445519</v>
       </c>
       <c r="R16" t="n">
-        <v>6768295</v>
+        <v>6768373</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723517</v>
+        <v>127723442</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445463</v>
+        <v>445407</v>
       </c>
       <c r="R17" t="n">
-        <v>6768439</v>
+        <v>6768295</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723520</v>
+        <v>127723435</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445439</v>
+        <v>445375</v>
       </c>
       <c r="R18" t="n">
-        <v>6768423</v>
+        <v>6768348</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723435</v>
+        <v>127723517</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445375</v>
+        <v>445463</v>
       </c>
       <c r="R19" t="n">
-        <v>6768348</v>
+        <v>6768439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723561</v>
+        <v>127723520</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445519</v>
+        <v>445439</v>
       </c>
       <c r="R20" t="n">
-        <v>6768373</v>
+        <v>6768423</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723603</v>
+        <v>127723515</v>
       </c>
       <c r="B34" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445353</v>
+        <v>445465</v>
       </c>
       <c r="R34" t="n">
-        <v>6768433</v>
+        <v>6768438</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,7 +3891,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723515</v>
+        <v>127723482</v>
       </c>
       <c r="B35" t="n">
         <v>79029</v>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445465</v>
+        <v>445318</v>
       </c>
       <c r="R35" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3988,7 +3988,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723482</v>
+        <v>127723446</v>
       </c>
       <c r="B36" t="n">
         <v>79029</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445318</v>
+        <v>445453</v>
       </c>
       <c r="R36" t="n">
-        <v>6768474</v>
+        <v>6768321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4085,7 +4085,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723446</v>
+        <v>127723431</v>
       </c>
       <c r="B37" t="n">
         <v>79029</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445453</v>
+        <v>445369</v>
       </c>
       <c r="R37" t="n">
-        <v>6768321</v>
+        <v>6768408</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723431</v>
+        <v>127723536</v>
       </c>
       <c r="B38" t="n">
         <v>79029</v>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445369</v>
+        <v>445500</v>
       </c>
       <c r="R38" t="n">
-        <v>6768408</v>
+        <v>6768348</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723536</v>
+        <v>127723603</v>
       </c>
       <c r="B39" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445500</v>
+        <v>445353</v>
       </c>
       <c r="R39" t="n">
-        <v>6768348</v>
+        <v>6768433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,39 +6541,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R62" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,11 +6601,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6637,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723413</v>
+        <v>127722914</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6648,34 +6638,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445444</v>
+        <v>445325</v>
       </c>
       <c r="R63" t="n">
-        <v>6768341</v>
+        <v>6768463</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6708,6 +6703,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127722917</v>
+        <v>127723496</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6847,39 +6847,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445329</v>
+        <v>445376</v>
       </c>
       <c r="R65" t="n">
-        <v>6768466</v>
+        <v>6768426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6906,17 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6943,10 +6933,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722908</v>
+        <v>127723519</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,39 +6944,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445329</v>
+        <v>445434</v>
       </c>
       <c r="R66" t="n">
-        <v>6768474</v>
+        <v>6768437</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7013,17 +6998,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7050,7 +7030,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723496</v>
+        <v>127723489</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7085,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445376</v>
+        <v>445349</v>
       </c>
       <c r="R67" t="n">
-        <v>6768426</v>
+        <v>6768438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7147,7 +7127,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723519</v>
+        <v>127723522</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7182,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445434</v>
+        <v>445457</v>
       </c>
       <c r="R68" t="n">
-        <v>6768437</v>
+        <v>6768411</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7244,7 +7224,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723489</v>
+        <v>127723439</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7279,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445349</v>
+        <v>445382</v>
       </c>
       <c r="R69" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7309,12 +7289,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,7 +7321,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723522</v>
+        <v>127723514</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7376,10 +7356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445457</v>
+        <v>445468</v>
       </c>
       <c r="R70" t="n">
-        <v>6768411</v>
+        <v>6768439</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7438,7 +7418,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723439</v>
+        <v>127723455</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7473,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445382</v>
+        <v>445417</v>
       </c>
       <c r="R71" t="n">
-        <v>6768296</v>
+        <v>6768483</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7503,12 +7483,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7535,7 +7515,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723514</v>
+        <v>127723528</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7570,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445468</v>
+        <v>445493</v>
       </c>
       <c r="R72" t="n">
-        <v>6768439</v>
+        <v>6768388</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7632,7 +7612,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723455</v>
+        <v>127723506</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -7667,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445417</v>
+        <v>445509</v>
       </c>
       <c r="R73" t="n">
-        <v>6768483</v>
+        <v>6768424</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7729,7 +7709,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723528</v>
+        <v>127723511</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7764,10 +7744,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445493</v>
+        <v>445497</v>
       </c>
       <c r="R74" t="n">
-        <v>6768388</v>
+        <v>6768438</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7826,10 +7806,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723506</v>
+        <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7837,34 +7817,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445509</v>
+        <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768424</v>
+        <v>6768466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7891,12 +7876,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7923,10 +7913,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723511</v>
+        <v>127722908</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7934,34 +7924,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445497</v>
+        <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7988,12 +7983,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723605</v>
+        <v>127723454</v>
       </c>
       <c r="B98" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445403</v>
+        <v>445421</v>
       </c>
       <c r="R98" t="n">
-        <v>6768385</v>
+        <v>6768465</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723454</v>
+        <v>127723447</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445421</v>
+        <v>445458</v>
       </c>
       <c r="R99" t="n">
-        <v>6768465</v>
+        <v>6768338</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723447</v>
+        <v>127723535</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445458</v>
+        <v>445518</v>
       </c>
       <c r="R100" t="n">
-        <v>6768338</v>
+        <v>6768343</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723535</v>
+        <v>127723483</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445518</v>
+        <v>445310</v>
       </c>
       <c r="R101" t="n">
-        <v>6768343</v>
+        <v>6768467</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723483</v>
+        <v>127723440</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445310</v>
+        <v>445394</v>
       </c>
       <c r="R102" t="n">
-        <v>6768467</v>
+        <v>6768290</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723440</v>
+        <v>127722918</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,34 +10578,39 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445394</v>
+        <v>445382</v>
       </c>
       <c r="R103" t="n">
-        <v>6768290</v>
+        <v>6768422</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10632,12 +10637,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10664,45 +10674,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723490</v>
+        <v>127723027</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445353</v>
+        <v>445343</v>
       </c>
       <c r="R104" t="n">
-        <v>6768438</v>
+        <v>6768460</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10729,12 +10744,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10761,10 +10776,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127722918</v>
+        <v>127723605</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>78696</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10772,39 +10787,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445382</v>
+        <v>445403</v>
       </c>
       <c r="R105" t="n">
-        <v>6768422</v>
+        <v>6768385</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10837,11 +10847,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10965,50 +10970,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127723490</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445353</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768438</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723607</v>
+        <v>127723498</v>
       </c>
       <c r="B113" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445529</v>
+        <v>445386</v>
       </c>
       <c r="R113" t="n">
-        <v>6768354</v>
+        <v>6768393</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723498</v>
+        <v>127723607</v>
       </c>
       <c r="B118" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12048,21 +12048,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445386</v>
+        <v>445529</v>
       </c>
       <c r="R118" t="n">
-        <v>6768393</v>
+        <v>6768354</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127722831</v>
+        <v>127723443</v>
       </c>
       <c r="B119" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445370</v>
+        <v>445422</v>
       </c>
       <c r="R119" t="n">
-        <v>6768425</v>
+        <v>6768295</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723503</v>
+        <v>127723410</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445439</v>
+        <v>445434</v>
       </c>
       <c r="R120" t="n">
-        <v>6768381</v>
+        <v>6768336</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,7 +12328,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723443</v>
+        <v>127723505</v>
       </c>
       <c r="B121" t="n">
         <v>79029</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445422</v>
+        <v>445493</v>
       </c>
       <c r="R121" t="n">
-        <v>6768295</v>
+        <v>6768418</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723410</v>
+        <v>127723438</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445434</v>
+        <v>445375</v>
       </c>
       <c r="R122" t="n">
-        <v>6768336</v>
+        <v>6768277</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723505</v>
+        <v>127723503</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445493</v>
+        <v>445439</v>
       </c>
       <c r="R123" t="n">
-        <v>6768418</v>
+        <v>6768381</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723438</v>
+        <v>127722831</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445375</v>
+        <v>445370</v>
       </c>
       <c r="R124" t="n">
-        <v>6768277</v>
+        <v>6768425</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127722873</v>
+        <v>127723518</v>
       </c>
       <c r="B2" t="n">
-        <v>57832</v>
+        <v>79029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445364</v>
+        <v>445431</v>
       </c>
       <c r="R2" t="n">
-        <v>6768295</v>
+        <v>6768443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723479</v>
+        <v>127723424</v>
       </c>
       <c r="B3" t="n">
         <v>79029</v>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445309</v>
+        <v>445311</v>
       </c>
       <c r="R3" t="n">
-        <v>6768491</v>
+        <v>6768500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723421</v>
+        <v>127723479</v>
       </c>
       <c r="B4" t="n">
         <v>79029</v>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445361</v>
+        <v>445309</v>
       </c>
       <c r="R4" t="n">
-        <v>6768495</v>
+        <v>6768491</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723531</v>
+        <v>127723421</v>
       </c>
       <c r="B5" t="n">
         <v>79029</v>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445524</v>
+        <v>445361</v>
       </c>
       <c r="R5" t="n">
-        <v>6768371</v>
+        <v>6768495</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723480</v>
+        <v>127723531</v>
       </c>
       <c r="B6" t="n">
         <v>79029</v>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445314</v>
+        <v>445524</v>
       </c>
       <c r="R6" t="n">
-        <v>6768485</v>
+        <v>6768371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723434</v>
+        <v>127723480</v>
       </c>
       <c r="B7" t="n">
         <v>79029</v>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445345</v>
+        <v>445314</v>
       </c>
       <c r="R7" t="n">
-        <v>6768366</v>
+        <v>6768485</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1230,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723416</v>
+        <v>127723434</v>
       </c>
       <c r="B8" t="n">
         <v>79029</v>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445426</v>
+        <v>445345</v>
       </c>
       <c r="R8" t="n">
-        <v>6768417</v>
+        <v>6768366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723493</v>
+        <v>127723416</v>
       </c>
       <c r="B9" t="n">
         <v>79029</v>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445363</v>
+        <v>445426</v>
       </c>
       <c r="R9" t="n">
-        <v>6768410</v>
+        <v>6768417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1424,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723518</v>
+        <v>127723493</v>
       </c>
       <c r="B10" t="n">
         <v>79029</v>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445431</v>
+        <v>445363</v>
       </c>
       <c r="R10" t="n">
-        <v>6768443</v>
+        <v>6768410</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723424</v>
+        <v>127722873</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>57832</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1559,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445311</v>
+        <v>445364</v>
       </c>
       <c r="R11" t="n">
-        <v>6768500</v>
+        <v>6768295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723561</v>
+        <v>127723442</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445519</v>
+        <v>445407</v>
       </c>
       <c r="R16" t="n">
-        <v>6768373</v>
+        <v>6768295</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,7 +2135,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723442</v>
+        <v>127723517</v>
       </c>
       <c r="B17" t="n">
         <v>79029</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445407</v>
+        <v>445463</v>
       </c>
       <c r="R17" t="n">
-        <v>6768295</v>
+        <v>6768439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723435</v>
+        <v>127723520</v>
       </c>
       <c r="B18" t="n">
         <v>79029</v>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R18" t="n">
-        <v>6768348</v>
+        <v>6768423</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723517</v>
+        <v>127723435</v>
       </c>
       <c r="B19" t="n">
         <v>79029</v>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445463</v>
+        <v>445375</v>
       </c>
       <c r="R19" t="n">
-        <v>6768439</v>
+        <v>6768348</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723520</v>
+        <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>79029</v>
+        <v>92642</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445439</v>
+        <v>445519</v>
       </c>
       <c r="R20" t="n">
-        <v>6768423</v>
+        <v>6768373</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B22" t="n">
         <v>79029</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R22" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,7 +2717,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723525</v>
+        <v>127723527</v>
       </c>
       <c r="B23" t="n">
         <v>79029</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445465</v>
+        <v>445476</v>
       </c>
       <c r="R23" t="n">
-        <v>6768379</v>
+        <v>6768382</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723527</v>
+        <v>127723417</v>
       </c>
       <c r="B24" t="n">
         <v>79029</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445476</v>
+        <v>445413</v>
       </c>
       <c r="R24" t="n">
-        <v>6768382</v>
+        <v>6768451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2879,12 +2879,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2911,7 +2911,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723417</v>
+        <v>127723433</v>
       </c>
       <c r="B25" t="n">
         <v>79029</v>
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445413</v>
+        <v>445354</v>
       </c>
       <c r="R25" t="n">
-        <v>6768451</v>
+        <v>6768399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,7 +3008,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723433</v>
+        <v>127723412</v>
       </c>
       <c r="B26" t="n">
         <v>79029</v>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445354</v>
+        <v>445423</v>
       </c>
       <c r="R26" t="n">
-        <v>6768399</v>
+        <v>6768342</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723413</v>
+        <v>127722914</v>
       </c>
       <c r="B62" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,34 +6541,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445444</v>
+        <v>445325</v>
       </c>
       <c r="R62" t="n">
-        <v>6768341</v>
+        <v>6768463</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6601,6 +6606,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6627,10 +6637,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6638,39 +6648,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R63" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6703,11 +6708,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723496</v>
+        <v>127722917</v>
       </c>
       <c r="B65" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6847,34 +6847,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445376</v>
+        <v>445329</v>
       </c>
       <c r="R65" t="n">
-        <v>6768426</v>
+        <v>6768466</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6901,12 +6906,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6933,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723519</v>
+        <v>127722908</v>
       </c>
       <c r="B66" t="n">
-        <v>79029</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6944,34 +6954,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445434</v>
+        <v>445329</v>
       </c>
       <c r="R66" t="n">
-        <v>6768437</v>
+        <v>6768474</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6998,12 +7013,17 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7030,7 +7050,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723489</v>
+        <v>127723496</v>
       </c>
       <c r="B67" t="n">
         <v>79029</v>
@@ -7065,10 +7085,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445349</v>
+        <v>445376</v>
       </c>
       <c r="R67" t="n">
-        <v>6768438</v>
+        <v>6768426</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,7 +7147,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723522</v>
+        <v>127723519</v>
       </c>
       <c r="B68" t="n">
         <v>79029</v>
@@ -7162,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445457</v>
+        <v>445434</v>
       </c>
       <c r="R68" t="n">
-        <v>6768411</v>
+        <v>6768437</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,7 +7244,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B69" t="n">
         <v>79029</v>
@@ -7259,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R69" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7309,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7321,7 +7341,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723514</v>
+        <v>127723522</v>
       </c>
       <c r="B70" t="n">
         <v>79029</v>
@@ -7356,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445468</v>
+        <v>445457</v>
       </c>
       <c r="R70" t="n">
-        <v>6768439</v>
+        <v>6768411</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,7 +7438,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723455</v>
+        <v>127723439</v>
       </c>
       <c r="B71" t="n">
         <v>79029</v>
@@ -7453,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445417</v>
+        <v>445382</v>
       </c>
       <c r="R71" t="n">
-        <v>6768483</v>
+        <v>6768296</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7483,12 +7503,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7515,7 +7535,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723528</v>
+        <v>127723514</v>
       </c>
       <c r="B72" t="n">
         <v>79029</v>
@@ -7550,10 +7570,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445493</v>
+        <v>445468</v>
       </c>
       <c r="R72" t="n">
-        <v>6768388</v>
+        <v>6768439</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,7 +7632,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723506</v>
+        <v>127723455</v>
       </c>
       <c r="B73" t="n">
         <v>79029</v>
@@ -7647,10 +7667,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445509</v>
+        <v>445417</v>
       </c>
       <c r="R73" t="n">
-        <v>6768424</v>
+        <v>6768483</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,7 +7729,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723511</v>
+        <v>127723528</v>
       </c>
       <c r="B74" t="n">
         <v>79029</v>
@@ -7744,10 +7764,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445497</v>
+        <v>445493</v>
       </c>
       <c r="R74" t="n">
-        <v>6768438</v>
+        <v>6768388</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7806,10 +7826,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722917</v>
+        <v>127723506</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7817,39 +7837,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445329</v>
+        <v>445509</v>
       </c>
       <c r="R75" t="n">
-        <v>6768466</v>
+        <v>6768424</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,17 +7891,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7913,10 +7923,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722908</v>
+        <v>127723511</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7924,39 +7934,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445329</v>
+        <v>445497</v>
       </c>
       <c r="R76" t="n">
-        <v>6768474</v>
+        <v>6768438</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7983,17 +7988,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8326,10 +8326,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127722930</v>
+        <v>127723560</v>
       </c>
       <c r="B80" t="n">
-        <v>8450</v>
+        <v>92642</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8337,39 +8337,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445390</v>
+        <v>445433</v>
       </c>
       <c r="R80" t="n">
-        <v>6768381</v>
+        <v>6768412</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8428,7 +8423,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723533</v>
+        <v>127723432</v>
       </c>
       <c r="B81" t="n">
         <v>79029</v>
@@ -8463,10 +8458,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445523</v>
+        <v>445360</v>
       </c>
       <c r="R81" t="n">
-        <v>6768356</v>
+        <v>6768399</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8493,12 +8488,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8525,32 +8520,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723560</v>
+        <v>127723411</v>
       </c>
       <c r="B82" t="n">
-        <v>92642</v>
+        <v>79029</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8560,10 +8555,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445433</v>
+        <v>445410</v>
       </c>
       <c r="R82" t="n">
-        <v>6768412</v>
+        <v>6768338</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8590,12 +8585,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8622,7 +8617,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723432</v>
+        <v>127723415</v>
       </c>
       <c r="B83" t="n">
         <v>79029</v>
@@ -8657,10 +8652,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445360</v>
+        <v>445422</v>
       </c>
       <c r="R83" t="n">
-        <v>6768399</v>
+        <v>6768387</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8719,7 +8714,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723411</v>
+        <v>127723420</v>
       </c>
       <c r="B84" t="n">
         <v>79029</v>
@@ -8754,10 +8749,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445410</v>
+        <v>445395</v>
       </c>
       <c r="R84" t="n">
-        <v>6768338</v>
+        <v>6768485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8816,7 +8811,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723415</v>
+        <v>127723494</v>
       </c>
       <c r="B85" t="n">
         <v>79029</v>
@@ -8851,10 +8846,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445422</v>
+        <v>445355</v>
       </c>
       <c r="R85" t="n">
-        <v>6768387</v>
+        <v>6768420</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8881,12 +8876,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8913,7 +8908,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723420</v>
+        <v>127723423</v>
       </c>
       <c r="B86" t="n">
         <v>79029</v>
@@ -8948,10 +8943,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445395</v>
+        <v>445325</v>
       </c>
       <c r="R86" t="n">
-        <v>6768485</v>
+        <v>6768515</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9010,7 +9005,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723494</v>
+        <v>127723537</v>
       </c>
       <c r="B87" t="n">
         <v>79029</v>
@@ -9045,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445355</v>
+        <v>445488</v>
       </c>
       <c r="R87" t="n">
-        <v>6768420</v>
+        <v>6768315</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9107,10 +9102,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127723423</v>
+        <v>127722825</v>
       </c>
       <c r="B88" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9118,21 +9113,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9142,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445325</v>
+        <v>445386</v>
       </c>
       <c r="R88" t="n">
-        <v>6768515</v>
+        <v>6768493</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9204,7 +9199,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723537</v>
+        <v>127723533</v>
       </c>
       <c r="B89" t="n">
         <v>79029</v>
@@ -9239,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445488</v>
+        <v>445523</v>
       </c>
       <c r="R89" t="n">
-        <v>6768315</v>
+        <v>6768356</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9301,45 +9296,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722825</v>
+        <v>127722930</v>
       </c>
       <c r="B90" t="n">
-        <v>79647</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445386</v>
+        <v>445390</v>
       </c>
       <c r="R90" t="n">
-        <v>6768493</v>
+        <v>6768381</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,7 +9398,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723426</v>
+        <v>127723436</v>
       </c>
       <c r="B91" t="n">
         <v>79029</v>
@@ -9433,10 +9433,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445324</v>
+        <v>445366</v>
       </c>
       <c r="R91" t="n">
-        <v>6768470</v>
+        <v>6768321</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9495,7 +9495,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723414</v>
+        <v>127723452</v>
       </c>
       <c r="B92" t="n">
         <v>79029</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445429</v>
+        <v>445473</v>
       </c>
       <c r="R92" t="n">
-        <v>6768360</v>
+        <v>6768325</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,50 +9592,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723029</v>
+        <v>127723504</v>
       </c>
       <c r="B93" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445351</v>
+        <v>445449</v>
       </c>
       <c r="R93" t="n">
-        <v>6768348</v>
+        <v>6768387</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9662,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9694,7 +9689,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723436</v>
+        <v>127723497</v>
       </c>
       <c r="B94" t="n">
         <v>79029</v>
@@ -9729,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445366</v>
+        <v>445376</v>
       </c>
       <c r="R94" t="n">
-        <v>6768321</v>
+        <v>6768407</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9759,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9791,7 +9786,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723452</v>
+        <v>127723426</v>
       </c>
       <c r="B95" t="n">
         <v>79029</v>
@@ -9826,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445473</v>
+        <v>445324</v>
       </c>
       <c r="R95" t="n">
-        <v>6768325</v>
+        <v>6768470</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9888,7 +9883,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723504</v>
+        <v>127723414</v>
       </c>
       <c r="B96" t="n">
         <v>79029</v>
@@ -9923,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445449</v>
+        <v>445429</v>
       </c>
       <c r="R96" t="n">
-        <v>6768387</v>
+        <v>6768360</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9953,12 +9948,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9985,45 +9980,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723497</v>
+        <v>127723029</v>
       </c>
       <c r="B97" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445376</v>
+        <v>445351</v>
       </c>
       <c r="R97" t="n">
-        <v>6768407</v>
+        <v>6768348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +10050,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723454</v>
+        <v>127723605</v>
       </c>
       <c r="B98" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445421</v>
+        <v>445403</v>
       </c>
       <c r="R98" t="n">
-        <v>6768465</v>
+        <v>6768385</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,7 +10179,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723447</v>
+        <v>127723454</v>
       </c>
       <c r="B99" t="n">
         <v>79029</v>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445458</v>
+        <v>445421</v>
       </c>
       <c r="R99" t="n">
-        <v>6768338</v>
+        <v>6768465</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,7 +10276,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723535</v>
+        <v>127723447</v>
       </c>
       <c r="B100" t="n">
         <v>79029</v>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445518</v>
+        <v>445458</v>
       </c>
       <c r="R100" t="n">
-        <v>6768343</v>
+        <v>6768338</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,7 +10373,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723483</v>
+        <v>127723535</v>
       </c>
       <c r="B101" t="n">
         <v>79029</v>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445310</v>
+        <v>445518</v>
       </c>
       <c r="R101" t="n">
-        <v>6768467</v>
+        <v>6768343</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,7 +10470,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723440</v>
+        <v>127723483</v>
       </c>
       <c r="B102" t="n">
         <v>79029</v>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445394</v>
+        <v>445310</v>
       </c>
       <c r="R102" t="n">
-        <v>6768290</v>
+        <v>6768467</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722918</v>
+        <v>127723440</v>
       </c>
       <c r="B103" t="n">
-        <v>57672</v>
+        <v>79029</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,39 +10578,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445382</v>
+        <v>445394</v>
       </c>
       <c r="R103" t="n">
-        <v>6768422</v>
+        <v>6768290</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10637,17 +10632,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10674,50 +10664,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723027</v>
+        <v>127723490</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>79029</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445343</v>
+        <v>445353</v>
       </c>
       <c r="R104" t="n">
-        <v>6768460</v>
+        <v>6768438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10744,12 +10729,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10776,10 +10761,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723605</v>
+        <v>127722918</v>
       </c>
       <c r="B105" t="n">
-        <v>78696</v>
+        <v>57672</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10787,34 +10772,39 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445403</v>
+        <v>445382</v>
       </c>
       <c r="R105" t="n">
-        <v>6768385</v>
+        <v>6768422</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10847,6 +10837,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10970,45 +10965,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723490</v>
+        <v>127723027</v>
       </c>
       <c r="B107" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445353</v>
+        <v>445343</v>
       </c>
       <c r="R107" t="n">
-        <v>6768438</v>
+        <v>6768460</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723443</v>
+        <v>127722831</v>
       </c>
       <c r="B119" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445422</v>
+        <v>445370</v>
       </c>
       <c r="R119" t="n">
-        <v>6768295</v>
+        <v>6768425</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,7 +12231,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723410</v>
+        <v>127723503</v>
       </c>
       <c r="B120" t="n">
         <v>79029</v>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445434</v>
+        <v>445439</v>
       </c>
       <c r="R120" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,7 +12328,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723505</v>
+        <v>127723443</v>
       </c>
       <c r="B121" t="n">
         <v>79029</v>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445493</v>
+        <v>445422</v>
       </c>
       <c r="R121" t="n">
-        <v>6768418</v>
+        <v>6768295</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12393,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,7 +12425,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723438</v>
+        <v>127723410</v>
       </c>
       <c r="B122" t="n">
         <v>79029</v>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445375</v>
+        <v>445434</v>
       </c>
       <c r="R122" t="n">
-        <v>6768277</v>
+        <v>6768336</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12522,7 +12522,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723503</v>
+        <v>127723505</v>
       </c>
       <c r="B123" t="n">
         <v>79029</v>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445439</v>
+        <v>445493</v>
       </c>
       <c r="R123" t="n">
-        <v>6768381</v>
+        <v>6768418</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127722831</v>
+        <v>127723438</v>
       </c>
       <c r="B124" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12630,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445370</v>
+        <v>445375</v>
       </c>
       <c r="R124" t="n">
-        <v>6768425</v>
+        <v>6768277</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723518</v>
+        <v>127722873</v>
       </c>
       <c r="B2" t="n">
-        <v>79029</v>
+        <v>57833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445431</v>
+        <v>445364</v>
       </c>
       <c r="R2" t="n">
-        <v>6768443</v>
+        <v>6768295</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723424</v>
+        <v>127723518</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445311</v>
+        <v>445431</v>
       </c>
       <c r="R3" t="n">
-        <v>6768500</v>
+        <v>6768443</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,7 +877,7 @@
         <v>127723479</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723421</v>
+        <v>127723434</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445361</v>
+        <v>445345</v>
       </c>
       <c r="R5" t="n">
-        <v>6768495</v>
+        <v>6768366</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723531</v>
+        <v>127723416</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445524</v>
+        <v>445426</v>
       </c>
       <c r="R6" t="n">
-        <v>6768371</v>
+        <v>6768417</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1128,12 +1133,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1163,7 +1168,7 @@
         <v>127723480</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723434</v>
+        <v>127723421</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445345</v>
+        <v>445361</v>
       </c>
       <c r="R8" t="n">
-        <v>6768366</v>
+        <v>6768495</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723416</v>
+        <v>127723493</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445426</v>
+        <v>445363</v>
       </c>
       <c r="R9" t="n">
-        <v>6768417</v>
+        <v>6768410</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723493</v>
+        <v>127723531</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445363</v>
+        <v>445524</v>
       </c>
       <c r="R10" t="n">
-        <v>6768410</v>
+        <v>6768371</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127722873</v>
+        <v>127723424</v>
       </c>
       <c r="B11" t="n">
-        <v>57832</v>
+        <v>79032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445364</v>
+        <v>445311</v>
       </c>
       <c r="R11" t="n">
-        <v>6768295</v>
+        <v>6768500</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,7 +1653,7 @@
         <v>127723602</v>
       </c>
       <c r="B12" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>127723606</v>
       </c>
       <c r="B13" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723512</v>
+        <v>127723445</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445476</v>
+        <v>445446</v>
       </c>
       <c r="R14" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723445</v>
+        <v>127723512</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445446</v>
+        <v>445476</v>
       </c>
       <c r="R15" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2006,12 +2006,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723442</v>
+        <v>127723517</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445407</v>
+        <v>445463</v>
       </c>
       <c r="R16" t="n">
-        <v>6768295</v>
+        <v>6768439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723517</v>
+        <v>127723435</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445463</v>
+        <v>445375</v>
       </c>
       <c r="R17" t="n">
-        <v>6768439</v>
+        <v>6768348</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723520</v>
+        <v>127723442</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445439</v>
+        <v>445407</v>
       </c>
       <c r="R18" t="n">
-        <v>6768423</v>
+        <v>6768295</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2329,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723435</v>
+        <v>127723520</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445375</v>
+        <v>445439</v>
       </c>
       <c r="R19" t="n">
-        <v>6768348</v>
+        <v>6768423</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2429,7 +2429,7 @@
         <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>127723500</v>
       </c>
       <c r="B21" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723525</v>
+        <v>127723527</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445465</v>
+        <v>445476</v>
       </c>
       <c r="R22" t="n">
-        <v>6768379</v>
+        <v>6768382</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723527</v>
+        <v>127723412</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445476</v>
+        <v>445423</v>
       </c>
       <c r="R23" t="n">
-        <v>6768382</v>
+        <v>6768342</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2817,7 +2817,7 @@
         <v>127723417</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>127723433</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723412</v>
+        <v>127723525</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445423</v>
+        <v>445465</v>
       </c>
       <c r="R26" t="n">
-        <v>6768342</v>
+        <v>6768379</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,50 +3105,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723028</v>
+        <v>127723523</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445345</v>
+        <v>445451</v>
       </c>
       <c r="R27" t="n">
-        <v>6768382</v>
+        <v>6768402</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3175,12 +3170,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3207,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723538</v>
+        <v>127723529</v>
       </c>
       <c r="B28" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3242,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445485</v>
+        <v>445507</v>
       </c>
       <c r="R28" t="n">
-        <v>6768313</v>
+        <v>6768383</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3304,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723523</v>
+        <v>127723538</v>
       </c>
       <c r="B29" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3339,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445451</v>
+        <v>445485</v>
       </c>
       <c r="R29" t="n">
-        <v>6768402</v>
+        <v>6768313</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723428</v>
+        <v>127723487</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3436,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445329</v>
+        <v>445328</v>
       </c>
       <c r="R30" t="n">
-        <v>6768465</v>
+        <v>6768445</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3466,12 +3461,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3498,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723487</v>
+        <v>127723428</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3533,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445328</v>
+        <v>445329</v>
       </c>
       <c r="R31" t="n">
-        <v>6768445</v>
+        <v>6768465</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3563,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3595,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127723529</v>
+        <v>127722895</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>57670</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,34 +3601,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445507</v>
+        <v>445370</v>
       </c>
       <c r="R32" t="n">
-        <v>6768383</v>
+        <v>6768276</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3660,12 +3660,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3692,38 +3692,38 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127722895</v>
+        <v>127723028</v>
       </c>
       <c r="B33" t="n">
-        <v>57669</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445370</v>
+        <v>445345</v>
       </c>
       <c r="R33" t="n">
-        <v>6768276</v>
+        <v>6768382</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,10 +3794,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723515</v>
+        <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>78699</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3805,21 +3805,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3829,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445465</v>
+        <v>445353</v>
       </c>
       <c r="R34" t="n">
-        <v>6768438</v>
+        <v>6768433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723482</v>
+        <v>127723446</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445318</v>
+        <v>445453</v>
       </c>
       <c r="R35" t="n">
-        <v>6768474</v>
+        <v>6768321</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723446</v>
+        <v>127723431</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445453</v>
+        <v>445369</v>
       </c>
       <c r="R36" t="n">
-        <v>6768321</v>
+        <v>6768408</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723431</v>
+        <v>127723536</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445369</v>
+        <v>445500</v>
       </c>
       <c r="R37" t="n">
-        <v>6768408</v>
+        <v>6768348</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4150,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723536</v>
+        <v>127723482</v>
       </c>
       <c r="B38" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445500</v>
+        <v>445318</v>
       </c>
       <c r="R38" t="n">
-        <v>6768348</v>
+        <v>6768474</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723603</v>
+        <v>127723515</v>
       </c>
       <c r="B39" t="n">
-        <v>78696</v>
+        <v>79032</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4290,21 +4290,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445353</v>
+        <v>445465</v>
       </c>
       <c r="R39" t="n">
-        <v>6768433</v>
+        <v>6768438</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4379,7 +4379,7 @@
         <v>127723422</v>
       </c>
       <c r="B40" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>127723418</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4573,7 +4573,7 @@
         <v>127723565</v>
       </c>
       <c r="B42" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>127723427</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,45 +4769,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723604</v>
+        <v>127723025</v>
       </c>
       <c r="B44" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R44" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4834,12 +4839,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,45 +4871,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723592</v>
+        <v>127723026</v>
       </c>
       <c r="B45" t="n">
-        <v>78696</v>
+        <v>8450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445370</v>
+        <v>445387</v>
       </c>
       <c r="R45" t="n">
-        <v>6768478</v>
+        <v>6768492</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,10 +4973,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723521</v>
+        <v>127723604</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>78699</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4974,21 +4984,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4998,10 +5008,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445445</v>
+        <v>445370</v>
       </c>
       <c r="R46" t="n">
-        <v>6768409</v>
+        <v>6768425</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5060,10 +5070,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723534</v>
+        <v>127723592</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>78699</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5071,21 +5081,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5095,10 +5105,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445528</v>
+        <v>445370</v>
       </c>
       <c r="R47" t="n">
-        <v>6768349</v>
+        <v>6768478</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5125,12 +5135,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5157,50 +5167,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723026</v>
+        <v>127723534</v>
       </c>
       <c r="B48" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445387</v>
+        <v>445528</v>
       </c>
       <c r="R48" t="n">
-        <v>6768492</v>
+        <v>6768349</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5227,12 +5232,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5259,50 +5264,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723025</v>
+        <v>127723521</v>
       </c>
       <c r="B49" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445397</v>
+        <v>445445</v>
       </c>
       <c r="R49" t="n">
-        <v>6768481</v>
+        <v>6768409</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5329,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5361,10 +5361,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723478</v>
+        <v>127723501</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445305</v>
+        <v>445430</v>
       </c>
       <c r="R50" t="n">
-        <v>6768502</v>
+        <v>6768379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723501</v>
+        <v>127723478</v>
       </c>
       <c r="B51" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445430</v>
+        <v>445305</v>
       </c>
       <c r="R51" t="n">
-        <v>6768379</v>
+        <v>6768502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723524</v>
+        <v>127723444</v>
       </c>
       <c r="B52" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445455</v>
+        <v>445432</v>
       </c>
       <c r="R52" t="n">
-        <v>6768391</v>
+        <v>6768299</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5655,7 +5655,7 @@
         <v>127723430</v>
       </c>
       <c r="B53" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723444</v>
+        <v>127722829</v>
       </c>
       <c r="B54" t="n">
-        <v>79029</v>
+        <v>79650</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445432</v>
+        <v>445339</v>
       </c>
       <c r="R54" t="n">
-        <v>6768299</v>
+        <v>6768436</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722829</v>
+        <v>127722889</v>
       </c>
       <c r="B55" t="n">
-        <v>79647</v>
+        <v>57670</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,34 +5857,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445339</v>
+        <v>445372</v>
       </c>
       <c r="R55" t="n">
-        <v>6768436</v>
+        <v>6768323</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5911,12 +5916,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -5946,7 +5951,7 @@
         <v>127723425</v>
       </c>
       <c r="B56" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6040,10 +6045,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722889</v>
+        <v>127723524</v>
       </c>
       <c r="B57" t="n">
-        <v>57669</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6051,39 +6056,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445372</v>
+        <v>445455</v>
       </c>
       <c r="R57" t="n">
-        <v>6768323</v>
+        <v>6768391</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6142,10 +6142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723492</v>
+        <v>127723499</v>
       </c>
       <c r="B58" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445366</v>
+        <v>445418</v>
       </c>
       <c r="R58" t="n">
-        <v>6768409</v>
+        <v>6768394</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6242,7 +6242,7 @@
         <v>127723526</v>
       </c>
       <c r="B59" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723499</v>
+        <v>127723492</v>
       </c>
       <c r="B60" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445418</v>
+        <v>445366</v>
       </c>
       <c r="R60" t="n">
-        <v>6768394</v>
+        <v>6768409</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6436,7 +6436,7 @@
         <v>127723488</v>
       </c>
       <c r="B61" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6530,10 +6530,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127722914</v>
+        <v>127723413</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6541,39 +6541,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445325</v>
+        <v>445444</v>
       </c>
       <c r="R62" t="n">
-        <v>6768463</v>
+        <v>6768341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6606,11 +6601,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6637,10 +6627,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127723413</v>
+        <v>127722914</v>
       </c>
       <c r="B63" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6648,34 +6638,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445444</v>
+        <v>445325</v>
       </c>
       <c r="R63" t="n">
-        <v>6768341</v>
+        <v>6768463</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6708,6 +6703,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6737,7 +6737,7 @@
         <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127722917</v>
+        <v>127723514</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6847,39 +6847,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445329</v>
+        <v>445468</v>
       </c>
       <c r="R65" t="n">
-        <v>6768466</v>
+        <v>6768439</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6906,17 +6901,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6943,10 +6933,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127722908</v>
+        <v>127723455</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>79032</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,39 +6944,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445329</v>
+        <v>445417</v>
       </c>
       <c r="R66" t="n">
-        <v>6768474</v>
+        <v>6768483</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7013,17 +6998,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7050,10 +7030,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723496</v>
+        <v>127723519</v>
       </c>
       <c r="B67" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7085,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445376</v>
+        <v>445434</v>
       </c>
       <c r="R67" t="n">
-        <v>6768426</v>
+        <v>6768437</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7147,10 +7127,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723519</v>
+        <v>127723496</v>
       </c>
       <c r="B68" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7182,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445434</v>
+        <v>445376</v>
       </c>
       <c r="R68" t="n">
-        <v>6768437</v>
+        <v>6768426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7244,10 +7224,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723489</v>
+        <v>127723439</v>
       </c>
       <c r="B69" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7279,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445349</v>
+        <v>445382</v>
       </c>
       <c r="R69" t="n">
-        <v>6768438</v>
+        <v>6768296</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7309,12 +7289,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723522</v>
+        <v>127723506</v>
       </c>
       <c r="B70" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7376,10 +7356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445457</v>
+        <v>445509</v>
       </c>
       <c r="R70" t="n">
-        <v>6768411</v>
+        <v>6768424</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7438,10 +7418,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B71" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7473,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R71" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7503,12 +7483,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7535,10 +7515,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723514</v>
+        <v>127723522</v>
       </c>
       <c r="B72" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7570,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445468</v>
+        <v>445457</v>
       </c>
       <c r="R72" t="n">
-        <v>6768439</v>
+        <v>6768411</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7632,10 +7612,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723455</v>
+        <v>127723511</v>
       </c>
       <c r="B73" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7667,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445417</v>
+        <v>445497</v>
       </c>
       <c r="R73" t="n">
-        <v>6768483</v>
+        <v>6768438</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7732,7 +7712,7 @@
         <v>127723528</v>
       </c>
       <c r="B74" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7826,45 +7806,50 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723506</v>
+        <v>127723034</v>
       </c>
       <c r="B75" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445509</v>
+        <v>445377</v>
       </c>
       <c r="R75" t="n">
-        <v>6768424</v>
+        <v>6768394</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7923,10 +7908,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723511</v>
+        <v>127722917</v>
       </c>
       <c r="B76" t="n">
-        <v>79029</v>
+        <v>57673</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7934,34 +7919,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445497</v>
+        <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768438</v>
+        <v>6768466</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7988,12 +7978,17 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8020,38 +8015,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723034</v>
+        <v>127722908</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>57673</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8060,10 +8055,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445377</v>
+        <v>445329</v>
       </c>
       <c r="R77" t="n">
-        <v>6768394</v>
+        <v>6768474</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8090,12 +8085,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8122,50 +8122,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723030</v>
+        <v>127723415</v>
       </c>
       <c r="B78" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445376</v>
+        <v>445422</v>
       </c>
       <c r="R78" t="n">
-        <v>6768336</v>
+        <v>6768387</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8224,50 +8219,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127722931</v>
+        <v>127723533</v>
       </c>
       <c r="B79" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445518</v>
+        <v>445523</v>
       </c>
       <c r="R79" t="n">
-        <v>6768355</v>
+        <v>6768356</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8294,12 +8284,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8326,32 +8316,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723560</v>
+        <v>127723432</v>
       </c>
       <c r="B80" t="n">
-        <v>92642</v>
+        <v>79032</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8361,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445433</v>
+        <v>445360</v>
       </c>
       <c r="R80" t="n">
-        <v>6768412</v>
+        <v>6768399</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8391,12 +8381,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8423,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723432</v>
+        <v>127723560</v>
       </c>
       <c r="B81" t="n">
-        <v>79029</v>
+        <v>92650</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8458,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445360</v>
+        <v>445433</v>
       </c>
       <c r="R81" t="n">
-        <v>6768399</v>
+        <v>6768412</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8488,12 +8478,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8520,45 +8510,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723411</v>
+        <v>127722931</v>
       </c>
       <c r="B82" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445410</v>
+        <v>445518</v>
       </c>
       <c r="R82" t="n">
-        <v>6768338</v>
+        <v>6768355</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8617,45 +8612,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723415</v>
+        <v>127722930</v>
       </c>
       <c r="B83" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445422</v>
+        <v>445390</v>
       </c>
       <c r="R83" t="n">
-        <v>6768387</v>
+        <v>6768381</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8682,12 +8682,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8714,45 +8714,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723420</v>
+        <v>127723030</v>
       </c>
       <c r="B84" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445395</v>
+        <v>445376</v>
       </c>
       <c r="R84" t="n">
-        <v>6768485</v>
+        <v>6768336</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8811,10 +8816,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723494</v>
+        <v>127723411</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8846,10 +8851,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445355</v>
+        <v>445410</v>
       </c>
       <c r="R85" t="n">
-        <v>6768420</v>
+        <v>6768338</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8876,12 +8881,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8908,10 +8913,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723423</v>
+        <v>127723494</v>
       </c>
       <c r="B86" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8943,10 +8948,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445325</v>
+        <v>445355</v>
       </c>
       <c r="R86" t="n">
-        <v>6768515</v>
+        <v>6768420</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8973,12 +8978,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9008,7 +9013,7 @@
         <v>127723537</v>
       </c>
       <c r="B87" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9105,7 +9110,7 @@
         <v>127722825</v>
       </c>
       <c r="B88" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9199,10 +9204,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723533</v>
+        <v>127723423</v>
       </c>
       <c r="B89" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9234,10 +9239,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445523</v>
+        <v>445325</v>
       </c>
       <c r="R89" t="n">
-        <v>6768356</v>
+        <v>6768515</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9264,12 +9269,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9296,50 +9301,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127722930</v>
+        <v>127723420</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445390</v>
+        <v>445395</v>
       </c>
       <c r="R90" t="n">
-        <v>6768381</v>
+        <v>6768485</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9366,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9401,7 +9401,7 @@
         <v>127723436</v>
       </c>
       <c r="B91" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9495,10 +9495,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723452</v>
+        <v>127723497</v>
       </c>
       <c r="B92" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445473</v>
+        <v>445376</v>
       </c>
       <c r="R92" t="n">
-        <v>6768325</v>
+        <v>6768407</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9595,7 +9595,7 @@
         <v>127723504</v>
       </c>
       <c r="B93" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9689,45 +9689,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723497</v>
+        <v>127723029</v>
       </c>
       <c r="B94" t="n">
-        <v>79029</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445376</v>
+        <v>445351</v>
       </c>
       <c r="R94" t="n">
-        <v>6768407</v>
+        <v>6768348</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9759,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9789,7 +9794,7 @@
         <v>127723426</v>
       </c>
       <c r="B95" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9883,10 +9888,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723414</v>
+        <v>127723452</v>
       </c>
       <c r="B96" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9918,10 +9923,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445429</v>
+        <v>445473</v>
       </c>
       <c r="R96" t="n">
-        <v>6768360</v>
+        <v>6768325</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,12 +9953,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -9980,50 +9985,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723029</v>
+        <v>127723414</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445351</v>
+        <v>445429</v>
       </c>
       <c r="R97" t="n">
-        <v>6768348</v>
+        <v>6768360</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10085,7 +10085,7 @@
         <v>127723605</v>
       </c>
       <c r="B98" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723454</v>
+        <v>127723440</v>
       </c>
       <c r="B99" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445421</v>
+        <v>445394</v>
       </c>
       <c r="R99" t="n">
-        <v>6768465</v>
+        <v>6768290</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,10 +10276,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723447</v>
+        <v>127723490</v>
       </c>
       <c r="B100" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10311,10 +10311,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445458</v>
+        <v>445353</v>
       </c>
       <c r="R100" t="n">
-        <v>6768338</v>
+        <v>6768438</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,10 +10373,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723535</v>
+        <v>127723454</v>
       </c>
       <c r="B101" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10408,10 +10408,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445518</v>
+        <v>445421</v>
       </c>
       <c r="R101" t="n">
-        <v>6768343</v>
+        <v>6768465</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10470,10 +10470,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723483</v>
+        <v>127723447</v>
       </c>
       <c r="B102" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10505,10 +10505,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445310</v>
+        <v>445458</v>
       </c>
       <c r="R102" t="n">
-        <v>6768467</v>
+        <v>6768338</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10535,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10567,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723440</v>
+        <v>127723535</v>
       </c>
       <c r="B103" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10602,10 +10602,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445394</v>
+        <v>445518</v>
       </c>
       <c r="R103" t="n">
-        <v>6768290</v>
+        <v>6768343</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10632,12 +10632,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10664,10 +10664,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723490</v>
+        <v>127723483</v>
       </c>
       <c r="B104" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10699,10 +10699,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445353</v>
+        <v>445310</v>
       </c>
       <c r="R104" t="n">
-        <v>6768438</v>
+        <v>6768467</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10761,10 +10761,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127722918</v>
+        <v>127722864</v>
       </c>
       <c r="B105" t="n">
-        <v>57672</v>
+        <v>91360</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10772,39 +10772,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445382</v>
+        <v>445327</v>
       </c>
       <c r="R105" t="n">
-        <v>6768422</v>
+        <v>6768444</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10837,11 +10832,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10868,10 +10858,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127722864</v>
+        <v>127722918</v>
       </c>
       <c r="B106" t="n">
-        <v>91352</v>
+        <v>57673</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10879,34 +10869,39 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445327</v>
+        <v>445382</v>
       </c>
       <c r="R106" t="n">
-        <v>6768444</v>
+        <v>6768422</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10939,6 +10934,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11070,7 +11070,7 @@
         <v>127723593</v>
       </c>
       <c r="B108" t="n">
-        <v>78696</v>
+        <v>78699</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723481</v>
+        <v>127723495</v>
       </c>
       <c r="B109" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445320</v>
+        <v>445361</v>
       </c>
       <c r="R109" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723429</v>
+        <v>127723481</v>
       </c>
       <c r="B110" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445339</v>
+        <v>445320</v>
       </c>
       <c r="R110" t="n">
-        <v>6768457</v>
+        <v>6768481</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11326,12 +11326,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723495</v>
+        <v>127722832</v>
       </c>
       <c r="B111" t="n">
-        <v>79029</v>
+        <v>79650</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445361</v>
+        <v>445457</v>
       </c>
       <c r="R111" t="n">
-        <v>6768425</v>
+        <v>6768397</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B112" t="n">
-        <v>79647</v>
+        <v>79032</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R112" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723498</v>
+        <v>127723607</v>
       </c>
       <c r="B113" t="n">
-        <v>79029</v>
+        <v>78699</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445386</v>
+        <v>445529</v>
       </c>
       <c r="R113" t="n">
-        <v>6768393</v>
+        <v>6768354</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723453</v>
+        <v>127723530</v>
       </c>
       <c r="B114" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445418</v>
+        <v>445515</v>
       </c>
       <c r="R114" t="n">
-        <v>6768439</v>
+        <v>6768378</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723532</v>
+        <v>127723441</v>
       </c>
       <c r="B115" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445523</v>
+        <v>445408</v>
       </c>
       <c r="R115" t="n">
-        <v>6768362</v>
+        <v>6768287</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11811,12 +11811,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11843,10 +11843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723441</v>
+        <v>127723532</v>
       </c>
       <c r="B116" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445408</v>
+        <v>445523</v>
       </c>
       <c r="R116" t="n">
-        <v>6768287</v>
+        <v>6768362</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11908,12 +11908,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -11940,10 +11940,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723530</v>
+        <v>127723453</v>
       </c>
       <c r="B117" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445515</v>
+        <v>445418</v>
       </c>
       <c r="R117" t="n">
-        <v>6768378</v>
+        <v>6768439</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723607</v>
+        <v>127723498</v>
       </c>
       <c r="B118" t="n">
-        <v>78696</v>
+        <v>79032</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12048,21 +12048,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445529</v>
+        <v>445386</v>
       </c>
       <c r="R118" t="n">
-        <v>6768354</v>
+        <v>6768393</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127722831</v>
+        <v>127723443</v>
       </c>
       <c r="B119" t="n">
-        <v>79647</v>
+        <v>79032</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12145,21 +12145,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445370</v>
+        <v>445422</v>
       </c>
       <c r="R119" t="n">
-        <v>6768425</v>
+        <v>6768295</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12199,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,10 +12231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723503</v>
+        <v>127723438</v>
       </c>
       <c r="B120" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445439</v>
+        <v>445375</v>
       </c>
       <c r="R120" t="n">
-        <v>6768381</v>
+        <v>6768277</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12296,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723443</v>
+        <v>127723410</v>
       </c>
       <c r="B121" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445422</v>
+        <v>445434</v>
       </c>
       <c r="R121" t="n">
-        <v>6768295</v>
+        <v>6768336</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12425,10 +12425,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723410</v>
+        <v>127723503</v>
       </c>
       <c r="B122" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12460,10 +12460,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445434</v>
+        <v>445439</v>
       </c>
       <c r="R122" t="n">
-        <v>6768336</v>
+        <v>6768381</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12490,12 +12490,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12522,10 +12522,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127723505</v>
+        <v>127722831</v>
       </c>
       <c r="B123" t="n">
-        <v>79029</v>
+        <v>79650</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12533,21 +12533,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12557,10 +12557,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445493</v>
+        <v>445370</v>
       </c>
       <c r="R123" t="n">
-        <v>6768418</v>
+        <v>6768425</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12619,10 +12619,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723438</v>
+        <v>127723505</v>
       </c>
       <c r="B124" t="n">
-        <v>79029</v>
+        <v>79032</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445375</v>
+        <v>445493</v>
       </c>
       <c r="R124" t="n">
-        <v>6768277</v>
+        <v>6768418</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12684,12 +12684,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD124" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723422</v>
+        <v>127723565</v>
       </c>
       <c r="B40" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445332</v>
+        <v>445406</v>
       </c>
       <c r="R40" t="n">
-        <v>6768518</v>
+        <v>6768484</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4447,6 +4447,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4473,7 +4478,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723418</v>
+        <v>127723422</v>
       </c>
       <c r="B41" t="n">
         <v>79032</v>
@@ -4508,10 +4513,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445411</v>
+        <v>445332</v>
       </c>
       <c r="R41" t="n">
-        <v>6768470</v>
+        <v>6768518</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4575,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723565</v>
+        <v>127723418</v>
       </c>
       <c r="B42" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4586,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4610,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445406</v>
+        <v>445411</v>
       </c>
       <c r="R42" t="n">
-        <v>6768484</v>
+        <v>6768470</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4641,11 +4646,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5361,7 +5361,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723501</v>
+        <v>127723478</v>
       </c>
       <c r="B50" t="n">
         <v>79032</v>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445430</v>
+        <v>445305</v>
       </c>
       <c r="R50" t="n">
-        <v>6768379</v>
+        <v>6768502</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,7 +5458,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723478</v>
+        <v>127723501</v>
       </c>
       <c r="B51" t="n">
         <v>79032</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445305</v>
+        <v>445430</v>
       </c>
       <c r="R51" t="n">
-        <v>6768502</v>
+        <v>6768379</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723444</v>
+        <v>127723425</v>
       </c>
       <c r="B52" t="n">
         <v>79032</v>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445432</v>
+        <v>445321</v>
       </c>
       <c r="R52" t="n">
-        <v>6768299</v>
+        <v>6768501</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127723524</v>
       </c>
       <c r="B53" t="n">
         <v>79032</v>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445455</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768391</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5717,12 +5717,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127722829</v>
+        <v>127723444</v>
       </c>
       <c r="B54" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5760,21 +5760,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445339</v>
+        <v>445432</v>
       </c>
       <c r="R54" t="n">
-        <v>6768436</v>
+        <v>6768299</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127722889</v>
+        <v>127723430</v>
       </c>
       <c r="B55" t="n">
-        <v>57670</v>
+        <v>79032</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5857,39 +5857,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445372</v>
+        <v>445357</v>
       </c>
       <c r="R55" t="n">
-        <v>6768323</v>
+        <v>6768451</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5948,10 +5943,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127723425</v>
+        <v>127722829</v>
       </c>
       <c r="B56" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5959,21 +5954,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5983,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445321</v>
+        <v>445339</v>
       </c>
       <c r="R56" t="n">
-        <v>6768501</v>
+        <v>6768436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6013,12 +6008,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6045,10 +6040,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127723524</v>
+        <v>127722889</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>57670</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6056,34 +6051,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445455</v>
+        <v>445372</v>
       </c>
       <c r="R57" t="n">
-        <v>6768391</v>
+        <v>6768323</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6110,12 +6110,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7806,38 +7806,38 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127723034</v>
+        <v>127722917</v>
       </c>
       <c r="B75" t="n">
-        <v>8450</v>
+        <v>57673</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -7846,10 +7846,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445377</v>
+        <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768394</v>
+        <v>6768466</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7876,12 +7876,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7908,7 +7913,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722917</v>
+        <v>127722908</v>
       </c>
       <c r="B76" t="n">
         <v>57673</v>
@@ -7951,7 +7956,7 @@
         <v>445329</v>
       </c>
       <c r="R76" t="n">
-        <v>6768466</v>
+        <v>6768474</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7988,7 +7993,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8015,38 +8020,38 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127722908</v>
+        <v>127723034</v>
       </c>
       <c r="B77" t="n">
-        <v>57673</v>
+        <v>8450</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8055,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445329</v>
+        <v>445377</v>
       </c>
       <c r="R77" t="n">
-        <v>6768474</v>
+        <v>6768394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8085,17 +8090,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9398,45 +9398,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723436</v>
+        <v>127723029</v>
       </c>
       <c r="B91" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445366</v>
+        <v>445351</v>
       </c>
       <c r="R91" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9495,7 +9500,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723497</v>
+        <v>127723436</v>
       </c>
       <c r="B92" t="n">
         <v>79032</v>
@@ -9530,10 +9535,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445376</v>
+        <v>445366</v>
       </c>
       <c r="R92" t="n">
-        <v>6768407</v>
+        <v>6768321</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9565,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9592,7 +9597,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723504</v>
+        <v>127723497</v>
       </c>
       <c r="B93" t="n">
         <v>79032</v>
@@ -9627,10 +9632,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445449</v>
+        <v>445376</v>
       </c>
       <c r="R93" t="n">
-        <v>6768387</v>
+        <v>6768407</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9689,50 +9694,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723029</v>
+        <v>127723504</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79032</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445351</v>
+        <v>445449</v>
       </c>
       <c r="R94" t="n">
-        <v>6768348</v>
+        <v>6768387</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9759,12 +9759,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723593</v>
+        <v>127723495</v>
       </c>
       <c r="B108" t="n">
-        <v>78699</v>
+        <v>79032</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11078,21 +11078,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445417</v>
+        <v>445361</v>
       </c>
       <c r="R108" t="n">
-        <v>6768470</v>
+        <v>6768425</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,7 +11164,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723495</v>
+        <v>127723481</v>
       </c>
       <c r="B109" t="n">
         <v>79032</v>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445361</v>
+        <v>445320</v>
       </c>
       <c r="R109" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11261,10 +11261,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127723481</v>
+        <v>127722832</v>
       </c>
       <c r="B110" t="n">
-        <v>79032</v>
+        <v>79650</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11272,21 +11272,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11296,10 +11296,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445320</v>
+        <v>445457</v>
       </c>
       <c r="R110" t="n">
-        <v>6768481</v>
+        <v>6768397</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11358,10 +11358,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127722832</v>
+        <v>127723429</v>
       </c>
       <c r="B111" t="n">
-        <v>79650</v>
+        <v>79032</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11369,21 +11369,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11393,10 +11393,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445457</v>
+        <v>445339</v>
       </c>
       <c r="R111" t="n">
-        <v>6768397</v>
+        <v>6768457</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11455,10 +11455,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723429</v>
+        <v>127723593</v>
       </c>
       <c r="B112" t="n">
-        <v>79032</v>
+        <v>78699</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11466,21 +11466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445339</v>
+        <v>445417</v>
       </c>
       <c r="R112" t="n">
-        <v>6768457</v>
+        <v>6768470</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11520,12 +11520,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD112" t="b">

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127722873</v>
+        <v>127723518</v>
       </c>
       <c r="B2" t="n">
-        <v>57833</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445364</v>
+        <v>445431</v>
       </c>
       <c r="R2" t="n">
-        <v>6768295</v>
+        <v>6768443</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723518</v>
+        <v>127723480</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445431</v>
+        <v>445314</v>
       </c>
       <c r="R3" t="n">
-        <v>6768443</v>
+        <v>6768485</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723479</v>
+        <v>127723421</v>
       </c>
       <c r="B4" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445309</v>
+        <v>445361</v>
       </c>
       <c r="R4" t="n">
-        <v>6768491</v>
+        <v>6768495</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723434</v>
+        <v>127723493</v>
       </c>
       <c r="B5" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445345</v>
+        <v>445363</v>
       </c>
       <c r="R5" t="n">
-        <v>6768366</v>
+        <v>6768410</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723416</v>
+        <v>127723531</v>
       </c>
       <c r="B6" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445426</v>
+        <v>445524</v>
       </c>
       <c r="R6" t="n">
-        <v>6768417</v>
+        <v>6768371</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1133,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723480</v>
+        <v>127723479</v>
       </c>
       <c r="B7" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445314</v>
+        <v>445309</v>
       </c>
       <c r="R7" t="n">
-        <v>6768485</v>
+        <v>6768491</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723421</v>
+        <v>127723434</v>
       </c>
       <c r="B8" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445361</v>
+        <v>445345</v>
       </c>
       <c r="R8" t="n">
-        <v>6768495</v>
+        <v>6768366</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723493</v>
+        <v>127723416</v>
       </c>
       <c r="B9" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445363</v>
+        <v>445426</v>
       </c>
       <c r="R9" t="n">
-        <v>6768410</v>
+        <v>6768417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1424,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723531</v>
+        <v>127723424</v>
       </c>
       <c r="B10" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445524</v>
+        <v>445311</v>
       </c>
       <c r="R10" t="n">
-        <v>6768371</v>
+        <v>6768500</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1521,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1553,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127723424</v>
+        <v>127722873</v>
       </c>
       <c r="B11" t="n">
-        <v>79032</v>
+        <v>57844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,34 +1559,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445311</v>
+        <v>445364</v>
       </c>
       <c r="R11" t="n">
-        <v>6768500</v>
+        <v>6768295</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723602</v>
+        <v>127723445</v>
       </c>
       <c r="B12" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445339</v>
+        <v>445446</v>
       </c>
       <c r="R12" t="n">
-        <v>6768436</v>
+        <v>6768306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723606</v>
+        <v>127723512</v>
       </c>
       <c r="B13" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445475</v>
+        <v>445476</v>
       </c>
       <c r="R13" t="n">
-        <v>6768378</v>
+        <v>6768436</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723445</v>
+        <v>127723602</v>
       </c>
       <c r="B14" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445446</v>
+        <v>445339</v>
       </c>
       <c r="R14" t="n">
-        <v>6768306</v>
+        <v>6768436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1909,12 +1909,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723512</v>
+        <v>127723606</v>
       </c>
       <c r="B15" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445476</v>
+        <v>445475</v>
       </c>
       <c r="R15" t="n">
-        <v>6768436</v>
+        <v>6768378</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>127723517</v>
       </c>
       <c r="B16" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>127723435</v>
       </c>
       <c r="B17" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>127723442</v>
       </c>
       <c r="B18" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>127723520</v>
       </c>
       <c r="B19" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>127723561</v>
       </c>
       <c r="B20" t="n">
-        <v>92650</v>
+        <v>92661</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>127723500</v>
       </c>
       <c r="B21" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723527</v>
+        <v>127723412</v>
       </c>
       <c r="B22" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445476</v>
+        <v>445423</v>
       </c>
       <c r="R22" t="n">
-        <v>6768382</v>
+        <v>6768342</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2685,12 +2685,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2717,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723412</v>
+        <v>127723527</v>
       </c>
       <c r="B23" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445423</v>
+        <v>445476</v>
       </c>
       <c r="R23" t="n">
-        <v>6768342</v>
+        <v>6768382</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2817,7 +2817,7 @@
         <v>127723417</v>
       </c>
       <c r="B24" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>127723433</v>
       </c>
       <c r="B25" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>127723525</v>
       </c>
       <c r="B26" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>127723523</v>
       </c>
       <c r="B27" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723529</v>
+        <v>127723487</v>
       </c>
       <c r="B28" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445507</v>
+        <v>445328</v>
       </c>
       <c r="R28" t="n">
-        <v>6768383</v>
+        <v>6768445</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3299,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723538</v>
+        <v>127723428</v>
       </c>
       <c r="B29" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445485</v>
+        <v>445329</v>
       </c>
       <c r="R29" t="n">
-        <v>6768313</v>
+        <v>6768465</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723487</v>
+        <v>127723529</v>
       </c>
       <c r="B30" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445328</v>
+        <v>445507</v>
       </c>
       <c r="R30" t="n">
-        <v>6768445</v>
+        <v>6768383</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3493,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723428</v>
+        <v>127723538</v>
       </c>
       <c r="B31" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445329</v>
+        <v>445485</v>
       </c>
       <c r="R31" t="n">
-        <v>6768465</v>
+        <v>6768313</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3593,7 +3593,7 @@
         <v>127722895</v>
       </c>
       <c r="B32" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,7 +3797,7 @@
         <v>127723603</v>
       </c>
       <c r="B34" t="n">
-        <v>78699</v>
+        <v>78710</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723446</v>
+        <v>127723536</v>
       </c>
       <c r="B35" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445453</v>
+        <v>445500</v>
       </c>
       <c r="R35" t="n">
-        <v>6768321</v>
+        <v>6768348</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3956,12 +3956,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3988,10 +3988,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723431</v>
+        <v>127723446</v>
       </c>
       <c r="B36" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445369</v>
+        <v>445453</v>
       </c>
       <c r="R36" t="n">
-        <v>6768408</v>
+        <v>6768321</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,10 +4085,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723536</v>
+        <v>127723515</v>
       </c>
       <c r="B37" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445500</v>
+        <v>445465</v>
       </c>
       <c r="R37" t="n">
-        <v>6768348</v>
+        <v>6768438</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4182,10 +4182,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723482</v>
+        <v>127723431</v>
       </c>
       <c r="B38" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445318</v>
+        <v>445369</v>
       </c>
       <c r="R38" t="n">
-        <v>6768474</v>
+        <v>6768408</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4247,12 +4247,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4279,10 +4279,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723515</v>
+        <v>127723482</v>
       </c>
       <c r="B39" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445465</v>
+        <v>445318</v>
       </c>
       <c r="R39" t="n">
-        <v>6768438</v>
+        <v>6768474</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723565</v>
+        <v>127723422</v>
       </c>
       <c r="B40" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,21 +4387,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445406</v>
+        <v>445332</v>
       </c>
       <c r="R40" t="n">
-        <v>6768484</v>
+        <v>6768518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4447,11 +4447,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4478,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723422</v>
+        <v>127723427</v>
       </c>
       <c r="B41" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4513,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445332</v>
+        <v>445322</v>
       </c>
       <c r="R41" t="n">
-        <v>6768518</v>
+        <v>6768457</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4575,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723418</v>
+        <v>127723565</v>
       </c>
       <c r="B42" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4586,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4610,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445411</v>
+        <v>445406</v>
       </c>
       <c r="R42" t="n">
-        <v>6768470</v>
+        <v>6768484</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4646,6 +4641,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4672,10 +4672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723427</v>
+        <v>127723418</v>
       </c>
       <c r="B43" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4707,10 +4707,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445322</v>
+        <v>445411</v>
       </c>
       <c r="R43" t="n">
-        <v>6768457</v>
+        <v>6768470</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,50 +4769,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723025</v>
+        <v>127723604</v>
       </c>
       <c r="B44" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445397</v>
+        <v>445370</v>
       </c>
       <c r="R44" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4839,12 +4834,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4871,50 +4866,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723026</v>
+        <v>127723592</v>
       </c>
       <c r="B45" t="n">
-        <v>8450</v>
+        <v>78710</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445387</v>
+        <v>445370</v>
       </c>
       <c r="R45" t="n">
-        <v>6768492</v>
+        <v>6768478</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4973,45 +4963,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723604</v>
+        <v>127723025</v>
       </c>
       <c r="B46" t="n">
-        <v>78699</v>
+        <v>8450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445370</v>
+        <v>445397</v>
       </c>
       <c r="R46" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5038,12 +5033,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5070,45 +5065,50 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723592</v>
+        <v>127723026</v>
       </c>
       <c r="B47" t="n">
-        <v>78699</v>
+        <v>8450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445370</v>
+        <v>445387</v>
       </c>
       <c r="R47" t="n">
-        <v>6768478</v>
+        <v>6768492</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,10 +5167,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723534</v>
+        <v>127723521</v>
       </c>
       <c r="B48" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5202,10 +5202,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445528</v>
+        <v>445445</v>
       </c>
       <c r="R48" t="n">
-        <v>6768349</v>
+        <v>6768409</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5264,10 +5264,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723521</v>
+        <v>127723534</v>
       </c>
       <c r="B49" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5299,10 +5299,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445445</v>
+        <v>445528</v>
       </c>
       <c r="R49" t="n">
-        <v>6768409</v>
+        <v>6768349</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5361,10 +5361,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723478</v>
+        <v>127723501</v>
       </c>
       <c r="B50" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5396,10 +5396,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445305</v>
+        <v>445430</v>
       </c>
       <c r="R50" t="n">
-        <v>6768502</v>
+        <v>6768379</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5458,10 +5458,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723501</v>
+        <v>127723478</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445430</v>
+        <v>445305</v>
       </c>
       <c r="R51" t="n">
-        <v>6768379</v>
+        <v>6768502</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5555,10 +5555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723425</v>
+        <v>127723444</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445321</v>
+        <v>445432</v>
       </c>
       <c r="R52" t="n">
-        <v>6768501</v>
+        <v>6768299</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,10 +5652,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723524</v>
+        <v>127723430</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5687,10 +5687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445455</v>
+        <v>445357</v>
       </c>
       <c r="R53" t="n">
-        <v>6768391</v>
+        <v>6768451</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5717,12 +5717,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5749,10 +5749,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723444</v>
+        <v>127723524</v>
       </c>
       <c r="B54" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5784,10 +5784,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445432</v>
+        <v>445455</v>
       </c>
       <c r="R54" t="n">
-        <v>6768299</v>
+        <v>6768391</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5814,12 +5814,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723430</v>
+        <v>127723425</v>
       </c>
       <c r="B55" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445357</v>
+        <v>445321</v>
       </c>
       <c r="R55" t="n">
-        <v>6768451</v>
+        <v>6768501</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5946,7 +5946,7 @@
         <v>127722829</v>
       </c>
       <c r="B56" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>127722889</v>
       </c>
       <c r="B57" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>127723499</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>127723526</v>
       </c>
       <c r="B59" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6336,10 +6336,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723492</v>
+        <v>127723488</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6371,10 +6371,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445366</v>
+        <v>445340</v>
       </c>
       <c r="R60" t="n">
-        <v>6768409</v>
+        <v>6768445</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6433,10 +6433,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723488</v>
+        <v>127723492</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6468,10 +6468,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445340</v>
+        <v>445366</v>
       </c>
       <c r="R61" t="n">
-        <v>6768445</v>
+        <v>6768409</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>127723413</v>
       </c>
       <c r="B62" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
         <v>127722914</v>
       </c>
       <c r="B63" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         <v>127722872</v>
       </c>
       <c r="B64" t="n">
-        <v>57833</v>
+        <v>57844</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6836,10 +6836,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723514</v>
+        <v>127723506</v>
       </c>
       <c r="B65" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6871,10 +6871,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445468</v>
+        <v>445509</v>
       </c>
       <c r="R65" t="n">
-        <v>6768439</v>
+        <v>6768424</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6933,10 +6933,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723455</v>
+        <v>127723496</v>
       </c>
       <c r="B66" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6968,10 +6968,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445417</v>
+        <v>445376</v>
       </c>
       <c r="R66" t="n">
-        <v>6768483</v>
+        <v>6768426</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,10 +7030,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723519</v>
+        <v>127723511</v>
       </c>
       <c r="B67" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7065,10 +7065,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445434</v>
+        <v>445497</v>
       </c>
       <c r="R67" t="n">
-        <v>6768437</v>
+        <v>6768438</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,10 +7127,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723496</v>
+        <v>127723514</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445376</v>
+        <v>445468</v>
       </c>
       <c r="R68" t="n">
-        <v>6768426</v>
+        <v>6768439</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,10 +7224,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723439</v>
+        <v>127723489</v>
       </c>
       <c r="B69" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445382</v>
+        <v>445349</v>
       </c>
       <c r="R69" t="n">
-        <v>6768296</v>
+        <v>6768438</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7289,12 +7289,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7321,10 +7321,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723506</v>
+        <v>127723455</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7356,10 +7356,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445509</v>
+        <v>445417</v>
       </c>
       <c r="R70" t="n">
-        <v>6768424</v>
+        <v>6768483</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,10 +7418,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723489</v>
+        <v>127723522</v>
       </c>
       <c r="B71" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445349</v>
+        <v>445457</v>
       </c>
       <c r="R71" t="n">
-        <v>6768438</v>
+        <v>6768411</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7515,10 +7515,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723522</v>
+        <v>127723519</v>
       </c>
       <c r="B72" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445457</v>
+        <v>445434</v>
       </c>
       <c r="R72" t="n">
-        <v>6768411</v>
+        <v>6768437</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,10 +7612,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723511</v>
+        <v>127723528</v>
       </c>
       <c r="B73" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7647,10 +7647,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445497</v>
+        <v>445493</v>
       </c>
       <c r="R73" t="n">
-        <v>6768438</v>
+        <v>6768388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,10 +7709,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127723528</v>
+        <v>127722917</v>
       </c>
       <c r="B74" t="n">
-        <v>79032</v>
+        <v>57684</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7720,34 +7720,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445493</v>
+        <v>445329</v>
       </c>
       <c r="R74" t="n">
-        <v>6768388</v>
+        <v>6768466</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7774,12 +7779,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7806,10 +7816,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722917</v>
+        <v>127722908</v>
       </c>
       <c r="B75" t="n">
-        <v>57673</v>
+        <v>57684</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7849,7 +7859,7 @@
         <v>445329</v>
       </c>
       <c r="R75" t="n">
-        <v>6768466</v>
+        <v>6768474</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7886,7 +7896,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska ringhack (gran)</t>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7913,10 +7923,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127722908</v>
+        <v>127723439</v>
       </c>
       <c r="B76" t="n">
-        <v>57673</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7924,39 +7934,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445329</v>
+        <v>445382</v>
       </c>
       <c r="R76" t="n">
-        <v>6768474</v>
+        <v>6768296</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7989,11 +7994,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8125,7 +8125,7 @@
         <v>127723415</v>
       </c>
       <c r="B78" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723533</v>
+        <v>127723411</v>
       </c>
       <c r="B79" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445523</v>
+        <v>445410</v>
       </c>
       <c r="R79" t="n">
-        <v>6768356</v>
+        <v>6768338</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8284,12 +8284,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723432</v>
+        <v>127723537</v>
       </c>
       <c r="B80" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445360</v>
+        <v>445488</v>
       </c>
       <c r="R80" t="n">
-        <v>6768399</v>
+        <v>6768315</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8381,12 +8381,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723560</v>
+        <v>127723533</v>
       </c>
       <c r="B81" t="n">
-        <v>92650</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445433</v>
+        <v>445523</v>
       </c>
       <c r="R81" t="n">
-        <v>6768412</v>
+        <v>6768356</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,50 +8510,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127722931</v>
+        <v>127723432</v>
       </c>
       <c r="B82" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445518</v>
+        <v>445360</v>
       </c>
       <c r="R82" t="n">
-        <v>6768355</v>
+        <v>6768399</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8612,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127722930</v>
+        <v>127723560</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>92661</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8623,39 +8618,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445390</v>
+        <v>445433</v>
       </c>
       <c r="R83" t="n">
-        <v>6768381</v>
+        <v>6768412</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8714,7 +8704,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127723030</v>
+        <v>127722931</v>
       </c>
       <c r="B84" t="n">
         <v>8450</v>
@@ -8754,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445376</v>
+        <v>445518</v>
       </c>
       <c r="R84" t="n">
-        <v>6768336</v>
+        <v>6768355</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8816,45 +8806,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127723411</v>
+        <v>127722930</v>
       </c>
       <c r="B85" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445410</v>
+        <v>445390</v>
       </c>
       <c r="R85" t="n">
-        <v>6768338</v>
+        <v>6768381</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8881,12 +8876,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8913,45 +8908,50 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723494</v>
+        <v>127723030</v>
       </c>
       <c r="B86" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>445355</v>
+        <v>445376</v>
       </c>
       <c r="R86" t="n">
-        <v>6768420</v>
+        <v>6768336</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9010,10 +9010,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723537</v>
+        <v>127723494</v>
       </c>
       <c r="B87" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9045,10 +9045,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445488</v>
+        <v>445355</v>
       </c>
       <c r="R87" t="n">
-        <v>6768315</v>
+        <v>6768420</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9110,7 +9110,7 @@
         <v>127722825</v>
       </c>
       <c r="B88" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>127723423</v>
       </c>
       <c r="B89" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>127723420</v>
       </c>
       <c r="B90" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9398,50 +9398,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723029</v>
+        <v>127723426</v>
       </c>
       <c r="B91" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445351</v>
+        <v>445324</v>
       </c>
       <c r="R91" t="n">
-        <v>6768348</v>
+        <v>6768470</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9500,10 +9495,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723436</v>
+        <v>127723452</v>
       </c>
       <c r="B92" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9535,10 +9530,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445366</v>
+        <v>445473</v>
       </c>
       <c r="R92" t="n">
-        <v>6768321</v>
+        <v>6768325</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9565,12 +9560,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9597,10 +9592,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723497</v>
+        <v>127723414</v>
       </c>
       <c r="B93" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9632,10 +9627,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445376</v>
+        <v>445429</v>
       </c>
       <c r="R93" t="n">
-        <v>6768407</v>
+        <v>6768360</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9662,12 +9657,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9694,10 +9689,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723504</v>
+        <v>127723436</v>
       </c>
       <c r="B94" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9729,10 +9724,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445449</v>
+        <v>445366</v>
       </c>
       <c r="R94" t="n">
-        <v>6768387</v>
+        <v>6768321</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9759,12 +9754,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9791,10 +9786,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723426</v>
+        <v>127723497</v>
       </c>
       <c r="B95" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9826,10 +9821,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445324</v>
+        <v>445376</v>
       </c>
       <c r="R95" t="n">
-        <v>6768470</v>
+        <v>6768407</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,12 +9851,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -9888,10 +9883,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723452</v>
+        <v>127723504</v>
       </c>
       <c r="B96" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9923,10 +9918,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445473</v>
+        <v>445449</v>
       </c>
       <c r="R96" t="n">
-        <v>6768325</v>
+        <v>6768387</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9985,45 +9980,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723414</v>
+        <v>127723029</v>
       </c>
       <c r="B97" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445429</v>
+        <v>445351</v>
       </c>
       <c r="R97" t="n">
-        <v>6768360</v>
+        <v>6768348</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10082,10 +10082,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723605</v>
+        <v>127723490</v>
       </c>
       <c r="B98" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10093,21 +10093,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10117,10 +10117,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445403</v>
+        <v>445353</v>
       </c>
       <c r="R98" t="n">
-        <v>6768385</v>
+        <v>6768438</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,10 +10179,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723440</v>
+        <v>127723454</v>
       </c>
       <c r="B99" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10214,10 +10214,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445394</v>
+        <v>445421</v>
       </c>
       <c r="R99" t="n">
-        <v>6768290</v>
+        <v>6768465</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10244,12 +10244,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10276,10 +10276,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127723490</v>
+        <v>127722918</v>
       </c>
       <c r="B100" t="n">
-        <v>79032</v>
+        <v>57684</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10287,34 +10287,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445353</v>
+        <v>445382</v>
       </c>
       <c r="R100" t="n">
-        <v>6768438</v>
+        <v>6768422</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10347,6 +10352,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10373,45 +10383,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723454</v>
+        <v>127723027</v>
       </c>
       <c r="B101" t="n">
-        <v>79032</v>
+        <v>8450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445421</v>
+        <v>445343</v>
       </c>
       <c r="R101" t="n">
-        <v>6768465</v>
+        <v>6768460</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10438,12 +10453,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10470,10 +10485,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723447</v>
+        <v>127723605</v>
       </c>
       <c r="B102" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10481,21 +10496,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10505,10 +10520,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445458</v>
+        <v>445403</v>
       </c>
       <c r="R102" t="n">
-        <v>6768338</v>
+        <v>6768385</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,12 +10550,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10567,10 +10582,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127723535</v>
+        <v>127722864</v>
       </c>
       <c r="B103" t="n">
-        <v>79032</v>
+        <v>91371</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10578,21 +10593,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10602,10 +10617,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445518</v>
+        <v>445327</v>
       </c>
       <c r="R103" t="n">
-        <v>6768343</v>
+        <v>6768444</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10664,10 +10679,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723483</v>
+        <v>127723440</v>
       </c>
       <c r="B104" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10699,10 +10714,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445310</v>
+        <v>445394</v>
       </c>
       <c r="R104" t="n">
-        <v>6768467</v>
+        <v>6768290</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10729,12 +10744,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10761,10 +10776,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127722864</v>
+        <v>127723447</v>
       </c>
       <c r="B105" t="n">
-        <v>91360</v>
+        <v>79043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10772,21 +10787,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10796,10 +10811,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445327</v>
+        <v>445458</v>
       </c>
       <c r="R105" t="n">
-        <v>6768444</v>
+        <v>6768338</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10826,12 +10841,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10858,10 +10873,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127722918</v>
+        <v>127723535</v>
       </c>
       <c r="B106" t="n">
-        <v>57673</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10869,39 +10884,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445382</v>
+        <v>445518</v>
       </c>
       <c r="R106" t="n">
-        <v>6768422</v>
+        <v>6768343</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10934,11 +10944,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -10965,50 +10970,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723027</v>
+        <v>127723483</v>
       </c>
       <c r="B107" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445343</v>
+        <v>445310</v>
       </c>
       <c r="R107" t="n">
-        <v>6768460</v>
+        <v>6768467</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11067,10 +11067,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723495</v>
+        <v>127723481</v>
       </c>
       <c r="B108" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11102,10 +11102,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445361</v>
+        <v>445320</v>
       </c>
       <c r="R108" t="n">
-        <v>6768425</v>
+        <v>6768481</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,10 +11164,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723481</v>
+        <v>127723495</v>
       </c>
       <c r="B109" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11199,10 +11199,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445320</v>
+        <v>445361</v>
       </c>
       <c r="R109" t="n">
-        <v>6768481</v>
+        <v>6768425</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11264,7 +11264,7 @@
         <v>127722832</v>
       </c>
       <c r="B110" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11361,7 +11361,7 @@
         <v>127723429</v>
       </c>
       <c r="B111" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>127723593</v>
       </c>
       <c r="B112" t="n">
-        <v>78699</v>
+        <v>78710</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11552,10 +11552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723607</v>
+        <v>127723498</v>
       </c>
       <c r="B113" t="n">
-        <v>78699</v>
+        <v>79043</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11563,21 +11563,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11587,10 +11587,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445529</v>
+        <v>445386</v>
       </c>
       <c r="R113" t="n">
-        <v>6768354</v>
+        <v>6768393</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,10 +11649,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B114" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11684,10 +11684,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R114" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,10 +11746,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723441</v>
+        <v>127723607</v>
       </c>
       <c r="B115" t="n">
-        <v>79032</v>
+        <v>78710</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11757,21 +11757,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11781,10 +11781,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445408</v>
+        <v>445529</v>
       </c>
       <c r="R115" t="n">
-        <v>6768287</v>
+        <v>6768354</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11811,12 +11811,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11843,10 +11843,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723532</v>
+        <v>127723530</v>
       </c>
       <c r="B116" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445523</v>
+        <v>445515</v>
       </c>
       <c r="R116" t="n">
-        <v>6768362</v>
+        <v>6768378</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,10 +11940,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723453</v>
+        <v>127723441</v>
       </c>
       <c r="B117" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11975,10 +11975,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445418</v>
+        <v>445408</v>
       </c>
       <c r="R117" t="n">
-        <v>6768439</v>
+        <v>6768287</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12005,12 +12005,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12037,10 +12037,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723498</v>
+        <v>127723453</v>
       </c>
       <c r="B118" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12072,10 +12072,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445386</v>
+        <v>445418</v>
       </c>
       <c r="R118" t="n">
-        <v>6768393</v>
+        <v>6768439</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,10 +12134,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723443</v>
+        <v>127723410</v>
       </c>
       <c r="B119" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12169,10 +12169,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445422</v>
+        <v>445434</v>
       </c>
       <c r="R119" t="n">
-        <v>6768295</v>
+        <v>6768336</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12231,10 +12231,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723438</v>
+        <v>127723443</v>
       </c>
       <c r="B120" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12266,10 +12266,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445375</v>
+        <v>445422</v>
       </c>
       <c r="R120" t="n">
-        <v>6768277</v>
+        <v>6768295</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12328,10 +12328,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723410</v>
+        <v>127723438</v>
       </c>
       <c r="B121" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12363,10 +12363,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445434</v>
+        <v>445375</v>
       </c>
       <c r="R121" t="n">
-        <v>6768336</v>
+        <v>6768277</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12428,7 +12428,7 @@
         <v>127723503</v>
       </c>
       <c r="B122" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>127722831</v>
       </c>
       <c r="B123" t="n">
-        <v>79650</v>
+        <v>79661</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>127723505</v>
       </c>
       <c r="B124" t="n">
-        <v>79032</v>
+        <v>79043</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127723518</v>
+        <v>127723565</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>445431</v>
+        <v>445406</v>
       </c>
       <c r="R2" t="n">
-        <v>6768443</v>
+        <v>6768484</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127723480</v>
+        <v>127723592</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>445314</v>
+        <v>445370</v>
       </c>
       <c r="R3" t="n">
-        <v>6768485</v>
+        <v>6768478</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127723421</v>
+        <v>127723593</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>445361</v>
+        <v>445417</v>
       </c>
       <c r="R4" t="n">
-        <v>6768495</v>
+        <v>6768470</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -934,12 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127723493</v>
+        <v>127723601</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>445363</v>
+        <v>445297</v>
       </c>
       <c r="R5" t="n">
-        <v>6768410</v>
+        <v>6768448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1068,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127723531</v>
+        <v>127723602</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1079,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>445524</v>
+        <v>445339</v>
       </c>
       <c r="R6" t="n">
-        <v>6768371</v>
+        <v>6768436</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127723479</v>
+        <v>127723603</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>445309</v>
+        <v>445353</v>
       </c>
       <c r="R7" t="n">
-        <v>6768491</v>
+        <v>6768433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127723434</v>
+        <v>127723604</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>445345</v>
+        <v>445370</v>
       </c>
       <c r="R8" t="n">
-        <v>6768366</v>
+        <v>6768425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1322,12 +1327,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1354,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127723416</v>
+        <v>127723605</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>445426</v>
+        <v>445403</v>
       </c>
       <c r="R9" t="n">
-        <v>6768417</v>
+        <v>6768385</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1419,12 +1424,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1451,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127723424</v>
+        <v>127723606</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>445311</v>
+        <v>445475</v>
       </c>
       <c r="R10" t="n">
-        <v>6768500</v>
+        <v>6768378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1516,12 +1521,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1548,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127722873</v>
+        <v>127723607</v>
       </c>
       <c r="B11" t="n">
-        <v>57844</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,39 +1564,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>445364</v>
+        <v>445529</v>
       </c>
       <c r="R11" t="n">
-        <v>6768295</v>
+        <v>6768354</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1618,12 +1618,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127723445</v>
+        <v>127722863</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>445446</v>
+        <v>445307</v>
       </c>
       <c r="R12" t="n">
-        <v>6768306</v>
+        <v>6768453</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1715,12 +1715,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127723512</v>
+        <v>127722864</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>445476</v>
+        <v>445327</v>
       </c>
       <c r="R13" t="n">
-        <v>6768436</v>
+        <v>6768444</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127723602</v>
+        <v>127723560</v>
       </c>
       <c r="B14" t="n">
-        <v>78710</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1855,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>445339</v>
+        <v>445433</v>
       </c>
       <c r="R14" t="n">
-        <v>6768436</v>
+        <v>6768412</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127723606</v>
+        <v>127723561</v>
       </c>
       <c r="B15" t="n">
-        <v>78710</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1952,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>445475</v>
+        <v>445519</v>
       </c>
       <c r="R15" t="n">
-        <v>6768378</v>
+        <v>6768373</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2038,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127723517</v>
+        <v>127722885</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>445463</v>
+        <v>445579</v>
       </c>
       <c r="R16" t="n">
-        <v>6768439</v>
+        <v>6768382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2135,14 +2135,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127723435</v>
+        <v>127723403</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>445375</v>
+        <v>445376</v>
       </c>
       <c r="R17" t="n">
-        <v>6768348</v>
+        <v>6768250</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2232,14 +2232,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127723442</v>
+        <v>127723404</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2267,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>445407</v>
+        <v>445396</v>
       </c>
       <c r="R18" t="n">
-        <v>6768295</v>
+        <v>6768248</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2329,14 +2329,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127723520</v>
+        <v>127723405</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2364,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>445439</v>
+        <v>445401</v>
       </c>
       <c r="R19" t="n">
-        <v>6768423</v>
+        <v>6768248</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2394,12 +2394,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127723561</v>
+        <v>127723407</v>
       </c>
       <c r="B20" t="n">
-        <v>92661</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>445519</v>
+        <v>445459</v>
       </c>
       <c r="R20" t="n">
-        <v>6768373</v>
+        <v>6768272</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2491,12 +2491,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2523,14 +2523,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127723500</v>
+        <v>127723408</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>445423</v>
+        <v>445472</v>
       </c>
       <c r="R21" t="n">
-        <v>6768386</v>
+        <v>6768283</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2588,12 +2588,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2620,14 +2620,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127723412</v>
+        <v>127723409</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>445423</v>
+        <v>445481</v>
       </c>
       <c r="R22" t="n">
-        <v>6768342</v>
+        <v>6768293</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2717,14 +2717,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127723527</v>
+        <v>127723410</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>445476</v>
+        <v>445434</v>
       </c>
       <c r="R23" t="n">
-        <v>6768382</v>
+        <v>6768336</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2814,14 +2814,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127723417</v>
+        <v>127723411</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>445413</v>
+        <v>445410</v>
       </c>
       <c r="R24" t="n">
-        <v>6768451</v>
+        <v>6768338</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2911,14 +2911,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127723433</v>
+        <v>127723412</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2946,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>445354</v>
+        <v>445423</v>
       </c>
       <c r="R25" t="n">
-        <v>6768399</v>
+        <v>6768342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,14 +3008,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127723525</v>
+        <v>127723413</v>
       </c>
       <c r="B26" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3043,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>445465</v>
+        <v>445444</v>
       </c>
       <c r="R26" t="n">
-        <v>6768379</v>
+        <v>6768341</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3073,12 +3073,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3105,14 +3105,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127723523</v>
+        <v>127723414</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>445451</v>
+        <v>445429</v>
       </c>
       <c r="R27" t="n">
-        <v>6768402</v>
+        <v>6768360</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3202,14 +3202,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127723487</v>
+        <v>127723415</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>445328</v>
+        <v>445422</v>
       </c>
       <c r="R28" t="n">
-        <v>6768445</v>
+        <v>6768387</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3267,12 +3267,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3299,14 +3299,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127723428</v>
+        <v>127723416</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>445329</v>
+        <v>445426</v>
       </c>
       <c r="R29" t="n">
-        <v>6768465</v>
+        <v>6768417</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3396,14 +3396,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127723529</v>
+        <v>127723417</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3431,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>445507</v>
+        <v>445413</v>
       </c>
       <c r="R30" t="n">
-        <v>6768383</v>
+        <v>6768451</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3493,14 +3493,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127723538</v>
+        <v>127723418</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>445485</v>
+        <v>445411</v>
       </c>
       <c r="R31" t="n">
-        <v>6768313</v>
+        <v>6768470</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3558,12 +3558,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3590,50 +3590,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127722895</v>
+        <v>127723420</v>
       </c>
       <c r="B32" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>445370</v>
+        <v>445395</v>
       </c>
       <c r="R32" t="n">
-        <v>6768276</v>
+        <v>6768485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3692,50 +3687,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127723028</v>
+        <v>127723421</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>445345</v>
+        <v>445361</v>
       </c>
       <c r="R33" t="n">
-        <v>6768382</v>
+        <v>6768495</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3794,32 +3784,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127723603</v>
+        <v>127723422</v>
       </c>
       <c r="B34" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3829,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>445353</v>
+        <v>445332</v>
       </c>
       <c r="R34" t="n">
-        <v>6768433</v>
+        <v>6768518</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3859,12 +3849,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3891,14 +3881,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127723536</v>
+        <v>127723423</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3926,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>445500</v>
+        <v>445325</v>
       </c>
       <c r="R35" t="n">
-        <v>6768348</v>
+        <v>6768515</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3956,12 +3946,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3988,14 +3978,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127723446</v>
+        <v>127723424</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4023,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>445453</v>
+        <v>445311</v>
       </c>
       <c r="R36" t="n">
-        <v>6768321</v>
+        <v>6768500</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4085,14 +4075,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127723515</v>
+        <v>127723425</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4120,10 +4110,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>445465</v>
+        <v>445321</v>
       </c>
       <c r="R37" t="n">
-        <v>6768438</v>
+        <v>6768501</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4150,12 +4140,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4182,14 +4172,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127723431</v>
+        <v>127723426</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4217,10 +4207,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>445369</v>
+        <v>445324</v>
       </c>
       <c r="R38" t="n">
-        <v>6768408</v>
+        <v>6768470</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4279,14 +4269,14 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127723482</v>
+        <v>127723427</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4314,10 +4304,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>445318</v>
+        <v>445322</v>
       </c>
       <c r="R39" t="n">
-        <v>6768474</v>
+        <v>6768457</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4344,12 +4334,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4376,14 +4366,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127723422</v>
+        <v>127723428</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4411,10 +4401,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>445332</v>
+        <v>445329</v>
       </c>
       <c r="R40" t="n">
-        <v>6768518</v>
+        <v>6768465</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,14 +4463,14 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127723427</v>
+        <v>127723429</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4508,7 +4498,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>445322</v>
+        <v>445339</v>
       </c>
       <c r="R41" t="n">
         <v>6768457</v>
@@ -4570,32 +4560,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127723565</v>
+        <v>127723430</v>
       </c>
       <c r="B42" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4595,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>445406</v>
+        <v>445357</v>
       </c>
       <c r="R42" t="n">
-        <v>6768484</v>
+        <v>6768451</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4641,11 +4631,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På kolad stubbe med fyra brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4672,14 +4657,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127723418</v>
+        <v>127723431</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4707,10 +4692,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>445411</v>
+        <v>445369</v>
       </c>
       <c r="R43" t="n">
-        <v>6768470</v>
+        <v>6768408</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,32 +4754,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127723604</v>
+        <v>127723432</v>
       </c>
       <c r="B44" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4804,10 +4789,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>445370</v>
+        <v>445360</v>
       </c>
       <c r="R44" t="n">
-        <v>6768425</v>
+        <v>6768399</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4834,12 +4819,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4866,32 +4851,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127723592</v>
+        <v>127723433</v>
       </c>
       <c r="B45" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4901,10 +4886,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>445370</v>
+        <v>445354</v>
       </c>
       <c r="R45" t="n">
-        <v>6768478</v>
+        <v>6768399</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,50 +4948,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127723025</v>
+        <v>127723434</v>
       </c>
       <c r="B46" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>445397</v>
+        <v>445345</v>
       </c>
       <c r="R46" t="n">
-        <v>6768481</v>
+        <v>6768366</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5065,50 +5045,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127723026</v>
+        <v>127723435</v>
       </c>
       <c r="B47" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>445387</v>
+        <v>445375</v>
       </c>
       <c r="R47" t="n">
-        <v>6768492</v>
+        <v>6768348</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5167,14 +5142,14 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127723521</v>
+        <v>127723436</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5202,10 +5177,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>445445</v>
+        <v>445366</v>
       </c>
       <c r="R48" t="n">
-        <v>6768409</v>
+        <v>6768321</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5232,12 +5207,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5264,14 +5239,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127723534</v>
+        <v>127723437</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5299,10 +5274,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>445528</v>
+        <v>445353</v>
       </c>
       <c r="R49" t="n">
-        <v>6768349</v>
+        <v>6768304</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5329,12 +5304,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5361,14 +5336,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127723501</v>
+        <v>127723438</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5396,10 +5371,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>445430</v>
+        <v>445375</v>
       </c>
       <c r="R50" t="n">
-        <v>6768379</v>
+        <v>6768277</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5426,12 +5401,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5458,14 +5433,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127723478</v>
+        <v>127723439</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5493,10 +5468,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>445305</v>
+        <v>445382</v>
       </c>
       <c r="R51" t="n">
-        <v>6768502</v>
+        <v>6768296</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5523,12 +5498,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5555,14 +5530,14 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>127723444</v>
+        <v>127723440</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5590,10 +5565,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>445432</v>
+        <v>445394</v>
       </c>
       <c r="R52" t="n">
-        <v>6768299</v>
+        <v>6768290</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5652,14 +5627,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127723430</v>
+        <v>127723441</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5687,10 +5662,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>445357</v>
+        <v>445408</v>
       </c>
       <c r="R53" t="n">
-        <v>6768451</v>
+        <v>6768287</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5749,14 +5724,14 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127723524</v>
+        <v>127723442</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5784,10 +5759,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>445455</v>
+        <v>445407</v>
       </c>
       <c r="R54" t="n">
-        <v>6768391</v>
+        <v>6768295</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5814,12 +5789,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5846,14 +5821,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127723425</v>
+        <v>127723443</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -5881,10 +5856,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>445321</v>
+        <v>445422</v>
       </c>
       <c r="R55" t="n">
-        <v>6768501</v>
+        <v>6768295</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5943,32 +5918,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127722829</v>
+        <v>127723444</v>
       </c>
       <c r="B56" t="n">
-        <v>79661</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5978,10 +5953,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>445339</v>
+        <v>445432</v>
       </c>
       <c r="R56" t="n">
-        <v>6768436</v>
+        <v>6768299</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6008,12 +5983,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6040,50 +6015,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>127722889</v>
+        <v>127723445</v>
       </c>
       <c r="B57" t="n">
-        <v>57681</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>445372</v>
+        <v>445446</v>
       </c>
       <c r="R57" t="n">
-        <v>6768323</v>
+        <v>6768306</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6142,14 +6112,14 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>127723499</v>
+        <v>127723446</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6177,10 +6147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>445418</v>
+        <v>445453</v>
       </c>
       <c r="R58" t="n">
-        <v>6768394</v>
+        <v>6768321</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6207,12 +6177,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6239,14 +6209,14 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>127723526</v>
+        <v>127723447</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6274,10 +6244,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>445468</v>
+        <v>445458</v>
       </c>
       <c r="R59" t="n">
-        <v>6768377</v>
+        <v>6768338</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6304,12 +6274,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6336,14 +6306,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>127723488</v>
+        <v>127723448</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6371,10 +6341,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>445340</v>
+        <v>445496</v>
       </c>
       <c r="R60" t="n">
-        <v>6768445</v>
+        <v>6768296</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6401,12 +6371,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6433,14 +6403,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>127723492</v>
+        <v>127723451</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6468,10 +6438,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>445366</v>
+        <v>445558</v>
       </c>
       <c r="R61" t="n">
-        <v>6768409</v>
+        <v>6768387</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6498,12 +6468,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6530,14 +6500,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>127723413</v>
+        <v>127723452</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6565,10 +6535,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>445444</v>
+        <v>445473</v>
       </c>
       <c r="R62" t="n">
-        <v>6768341</v>
+        <v>6768325</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6595,12 +6565,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6627,50 +6597,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>127722914</v>
+        <v>127723453</v>
       </c>
       <c r="B63" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>445325</v>
+        <v>445418</v>
       </c>
       <c r="R63" t="n">
-        <v>6768463</v>
+        <v>6768439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6697,17 +6662,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6734,50 +6694,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>127722872</v>
+        <v>127723454</v>
       </c>
       <c r="B64" t="n">
-        <v>57844</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>445414</v>
+        <v>445421</v>
       </c>
       <c r="R64" t="n">
-        <v>6768450</v>
+        <v>6768465</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,12 +6759,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6836,14 +6791,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>127723506</v>
+        <v>127723455</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6871,10 +6826,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>445509</v>
+        <v>445417</v>
       </c>
       <c r="R65" t="n">
-        <v>6768424</v>
+        <v>6768483</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6933,14 +6888,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>127723496</v>
+        <v>127723456</v>
       </c>
       <c r="B66" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -6968,10 +6923,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>445376</v>
+        <v>445400</v>
       </c>
       <c r="R66" t="n">
-        <v>6768426</v>
+        <v>6768513</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7030,14 +6985,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>127723511</v>
+        <v>127723477</v>
       </c>
       <c r="B67" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7065,10 +7020,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>445497</v>
+        <v>445297</v>
       </c>
       <c r="R67" t="n">
-        <v>6768438</v>
+        <v>6768511</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7127,14 +7082,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>127723514</v>
+        <v>127723478</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7162,10 +7117,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>445468</v>
+        <v>445305</v>
       </c>
       <c r="R68" t="n">
-        <v>6768439</v>
+        <v>6768502</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7224,14 +7179,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>127723489</v>
+        <v>127723479</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7259,10 +7214,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>445349</v>
+        <v>445309</v>
       </c>
       <c r="R69" t="n">
-        <v>6768438</v>
+        <v>6768491</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7321,14 +7276,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127723455</v>
+        <v>127723480</v>
       </c>
       <c r="B70" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7356,10 +7311,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>445417</v>
+        <v>445314</v>
       </c>
       <c r="R70" t="n">
-        <v>6768483</v>
+        <v>6768485</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7418,14 +7373,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>127723522</v>
+        <v>127723481</v>
       </c>
       <c r="B71" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7453,10 +7408,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>445457</v>
+        <v>445320</v>
       </c>
       <c r="R71" t="n">
-        <v>6768411</v>
+        <v>6768481</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7515,14 +7470,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>127723519</v>
+        <v>127723482</v>
       </c>
       <c r="B72" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -7550,10 +7505,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>445434</v>
+        <v>445318</v>
       </c>
       <c r="R72" t="n">
-        <v>6768437</v>
+        <v>6768474</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7612,14 +7567,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>127723528</v>
+        <v>127723483</v>
       </c>
       <c r="B73" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -7647,10 +7602,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>445493</v>
+        <v>445310</v>
       </c>
       <c r="R73" t="n">
-        <v>6768388</v>
+        <v>6768467</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7709,50 +7664,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>127722917</v>
+        <v>127723484</v>
       </c>
       <c r="B74" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>445329</v>
+        <v>445296</v>
       </c>
       <c r="R74" t="n">
-        <v>6768466</v>
+        <v>6768463</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7779,17 +7729,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack (gran)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7816,50 +7761,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>127722908</v>
+        <v>127723485</v>
       </c>
       <c r="B75" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>445329</v>
+        <v>445305</v>
       </c>
       <c r="R75" t="n">
-        <v>6768474</v>
+        <v>6768442</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7886,17 +7826,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7923,14 +7858,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>127723439</v>
+        <v>127723486</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -7958,10 +7893,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>445382</v>
+        <v>445315</v>
       </c>
       <c r="R76" t="n">
-        <v>6768296</v>
+        <v>6768435</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7988,12 +7923,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8020,50 +7955,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>127723034</v>
+        <v>127723487</v>
       </c>
       <c r="B77" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>445377</v>
+        <v>445328</v>
       </c>
       <c r="R77" t="n">
-        <v>6768394</v>
+        <v>6768445</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,14 +8052,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>127723415</v>
+        <v>127723488</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8157,10 +8087,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>445422</v>
+        <v>445340</v>
       </c>
       <c r="R78" t="n">
-        <v>6768387</v>
+        <v>6768445</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8187,12 +8117,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8219,14 +8149,14 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>127723411</v>
+        <v>127723489</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -8254,10 +8184,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>445410</v>
+        <v>445349</v>
       </c>
       <c r="R79" t="n">
-        <v>6768338</v>
+        <v>6768438</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8284,12 +8214,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8316,14 +8246,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>127723537</v>
+        <v>127723490</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8351,10 +8281,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>445488</v>
+        <v>445353</v>
       </c>
       <c r="R80" t="n">
-        <v>6768315</v>
+        <v>6768438</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8413,14 +8343,14 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127723533</v>
+        <v>127723492</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
@@ -8448,10 +8378,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>445523</v>
+        <v>445366</v>
       </c>
       <c r="R81" t="n">
-        <v>6768356</v>
+        <v>6768409</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,14 +8440,14 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127723432</v>
+        <v>127723493</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -8545,10 +8475,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>445360</v>
+        <v>445363</v>
       </c>
       <c r="R82" t="n">
-        <v>6768399</v>
+        <v>6768410</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8575,12 +8505,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8607,32 +8537,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127723560</v>
+        <v>127723494</v>
       </c>
       <c r="B83" t="n">
-        <v>92661</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8572,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>445433</v>
+        <v>445355</v>
       </c>
       <c r="R83" t="n">
-        <v>6768412</v>
+        <v>6768420</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,50 +8634,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127722931</v>
+        <v>127723495</v>
       </c>
       <c r="B84" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>445518</v>
+        <v>445361</v>
       </c>
       <c r="R84" t="n">
-        <v>6768355</v>
+        <v>6768425</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8774,12 +8699,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8806,50 +8731,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127722930</v>
+        <v>127723496</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>445390</v>
+        <v>445376</v>
       </c>
       <c r="R85" t="n">
-        <v>6768381</v>
+        <v>6768426</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8908,40 +8828,35 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127723030</v>
+        <v>127723497</v>
       </c>
       <c r="B86" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
@@ -8951,7 +8866,7 @@
         <v>445376</v>
       </c>
       <c r="R86" t="n">
-        <v>6768336</v>
+        <v>6768407</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8978,12 +8893,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9010,14 +8925,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127723494</v>
+        <v>127723498</v>
       </c>
       <c r="B87" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -9045,10 +8960,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>445355</v>
+        <v>445386</v>
       </c>
       <c r="R87" t="n">
-        <v>6768420</v>
+        <v>6768393</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9107,32 +9022,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127722825</v>
+        <v>127723499</v>
       </c>
       <c r="B88" t="n">
-        <v>79661</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9142,10 +9057,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>445386</v>
+        <v>445418</v>
       </c>
       <c r="R88" t="n">
-        <v>6768493</v>
+        <v>6768394</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9172,12 +9087,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9204,14 +9119,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127723423</v>
+        <v>127723500</v>
       </c>
       <c r="B89" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -9239,10 +9154,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>445325</v>
+        <v>445423</v>
       </c>
       <c r="R89" t="n">
-        <v>6768515</v>
+        <v>6768386</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9269,12 +9184,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9301,14 +9216,14 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127723420</v>
+        <v>127723501</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -9336,10 +9251,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>445395</v>
+        <v>445430</v>
       </c>
       <c r="R90" t="n">
-        <v>6768485</v>
+        <v>6768379</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,12 +9281,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9398,14 +9313,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127723426</v>
+        <v>127723503</v>
       </c>
       <c r="B91" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -9433,10 +9348,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>445324</v>
+        <v>445439</v>
       </c>
       <c r="R91" t="n">
-        <v>6768470</v>
+        <v>6768381</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,12 +9378,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9495,14 +9410,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>127723452</v>
+        <v>127723504</v>
       </c>
       <c r="B92" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -9530,10 +9445,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>445473</v>
+        <v>445449</v>
       </c>
       <c r="R92" t="n">
-        <v>6768325</v>
+        <v>6768387</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9592,14 +9507,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>127723414</v>
+        <v>127723505</v>
       </c>
       <c r="B93" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -9627,10 +9542,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>445429</v>
+        <v>445493</v>
       </c>
       <c r="R93" t="n">
-        <v>6768360</v>
+        <v>6768418</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,12 +9572,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9689,14 +9604,14 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>127723436</v>
+        <v>127723506</v>
       </c>
       <c r="B94" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -9724,10 +9639,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>445366</v>
+        <v>445509</v>
       </c>
       <c r="R94" t="n">
-        <v>6768321</v>
+        <v>6768424</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,12 +9669,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9786,14 +9701,14 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127723497</v>
+        <v>127723507</v>
       </c>
       <c r="B95" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
@@ -9821,10 +9736,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>445376</v>
+        <v>445515</v>
       </c>
       <c r="R95" t="n">
-        <v>6768407</v>
+        <v>6768429</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9883,14 +9798,14 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127723504</v>
+        <v>127723510</v>
       </c>
       <c r="B96" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -9918,10 +9833,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>445449</v>
+        <v>445505</v>
       </c>
       <c r="R96" t="n">
-        <v>6768387</v>
+        <v>6768439</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9980,50 +9895,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>127723029</v>
+        <v>127723511</v>
       </c>
       <c r="B97" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>445351</v>
+        <v>445497</v>
       </c>
       <c r="R97" t="n">
-        <v>6768348</v>
+        <v>6768438</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,12 +9960,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10082,14 +9992,14 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>127723490</v>
+        <v>127723512</v>
       </c>
       <c r="B98" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -10117,10 +10027,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>445353</v>
+        <v>445476</v>
       </c>
       <c r="R98" t="n">
-        <v>6768438</v>
+        <v>6768436</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10179,14 +10089,14 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>127723454</v>
+        <v>127723514</v>
       </c>
       <c r="B99" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
@@ -10214,10 +10124,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>445421</v>
+        <v>445468</v>
       </c>
       <c r="R99" t="n">
-        <v>6768465</v>
+        <v>6768439</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10276,50 +10186,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>127722918</v>
+        <v>127723515</v>
       </c>
       <c r="B100" t="n">
-        <v>57684</v>
+        <v>79327</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>445382</v>
+        <v>445465</v>
       </c>
       <c r="R100" t="n">
-        <v>6768422</v>
+        <v>6768438</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10352,11 +10257,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Färska ringhack (tall)</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10383,50 +10283,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>127723027</v>
+        <v>127723517</v>
       </c>
       <c r="B101" t="n">
-        <v>8450</v>
+        <v>79327</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Oxeråsen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>445343</v>
+        <v>445463</v>
       </c>
       <c r="R101" t="n">
-        <v>6768460</v>
+        <v>6768439</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10453,12 +10348,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10485,32 +10380,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>127723605</v>
+        <v>127723518</v>
       </c>
       <c r="B102" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10520,10 +10415,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>445403</v>
+        <v>445431</v>
       </c>
       <c r="R102" t="n">
-        <v>6768385</v>
+        <v>6768443</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10582,32 +10477,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>127722864</v>
+        <v>127723519</v>
       </c>
       <c r="B103" t="n">
-        <v>91371</v>
+        <v>79327</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10617,10 +10512,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>445327</v>
+        <v>445434</v>
       </c>
       <c r="R103" t="n">
-        <v>6768444</v>
+        <v>6768437</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10679,14 +10574,14 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>127723440</v>
+        <v>127723520</v>
       </c>
       <c r="B104" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -10714,10 +10609,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>445394</v>
+        <v>445439</v>
       </c>
       <c r="R104" t="n">
-        <v>6768290</v>
+        <v>6768423</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10744,12 +10639,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -10776,14 +10671,14 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>127723447</v>
+        <v>127723521</v>
       </c>
       <c r="B105" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -10811,10 +10706,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>445458</v>
+        <v>445445</v>
       </c>
       <c r="R105" t="n">
-        <v>6768338</v>
+        <v>6768409</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10841,12 +10736,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -10873,14 +10768,14 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>127723535</v>
+        <v>127723522</v>
       </c>
       <c r="B106" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -10908,10 +10803,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>445518</v>
+        <v>445457</v>
       </c>
       <c r="R106" t="n">
-        <v>6768343</v>
+        <v>6768411</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10970,14 +10865,14 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>127723483</v>
+        <v>127723523</v>
       </c>
       <c r="B107" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -11005,10 +10900,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>445310</v>
+        <v>445451</v>
       </c>
       <c r="R107" t="n">
-        <v>6768467</v>
+        <v>6768402</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11067,14 +10962,14 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>127723481</v>
+        <v>127723524</v>
       </c>
       <c r="B108" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -11102,10 +10997,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>445320</v>
+        <v>445455</v>
       </c>
       <c r="R108" t="n">
-        <v>6768481</v>
+        <v>6768391</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11164,14 +11059,14 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>127723495</v>
+        <v>127723525</v>
       </c>
       <c r="B109" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
@@ -11199,10 +11094,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>445361</v>
+        <v>445465</v>
       </c>
       <c r="R109" t="n">
-        <v>6768425</v>
+        <v>6768379</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11261,32 +11156,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127722832</v>
+        <v>127723526</v>
       </c>
       <c r="B110" t="n">
-        <v>79661</v>
+        <v>79327</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11296,10 +11191,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>445457</v>
+        <v>445468</v>
       </c>
       <c r="R110" t="n">
-        <v>6768397</v>
+        <v>6768377</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11358,14 +11253,14 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127723429</v>
+        <v>127723527</v>
       </c>
       <c r="B111" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -11393,10 +11288,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>445339</v>
+        <v>445476</v>
       </c>
       <c r="R111" t="n">
-        <v>6768457</v>
+        <v>6768382</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11423,12 +11318,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11455,32 +11350,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>127723593</v>
+        <v>127723528</v>
       </c>
       <c r="B112" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11490,10 +11385,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>445417</v>
+        <v>445493</v>
       </c>
       <c r="R112" t="n">
-        <v>6768470</v>
+        <v>6768388</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11552,14 +11447,14 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>127723498</v>
+        <v>127723529</v>
       </c>
       <c r="B113" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -11587,10 +11482,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>445386</v>
+        <v>445507</v>
       </c>
       <c r="R113" t="n">
-        <v>6768393</v>
+        <v>6768383</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11649,14 +11544,14 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>127723532</v>
+        <v>127723530</v>
       </c>
       <c r="B114" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -11684,10 +11579,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>445523</v>
+        <v>445515</v>
       </c>
       <c r="R114" t="n">
-        <v>6768362</v>
+        <v>6768378</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11746,32 +11641,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>127723607</v>
+        <v>127723531</v>
       </c>
       <c r="B115" t="n">
-        <v>78710</v>
+        <v>79327</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11781,10 +11676,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>445529</v>
+        <v>445524</v>
       </c>
       <c r="R115" t="n">
-        <v>6768354</v>
+        <v>6768371</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11843,14 +11738,14 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>127723530</v>
+        <v>127723532</v>
       </c>
       <c r="B116" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -11878,10 +11773,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>445515</v>
+        <v>445523</v>
       </c>
       <c r="R116" t="n">
-        <v>6768378</v>
+        <v>6768362</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11940,14 +11835,14 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>127723441</v>
+        <v>127723533</v>
       </c>
       <c r="B117" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -11975,10 +11870,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>445408</v>
+        <v>445523</v>
       </c>
       <c r="R117" t="n">
-        <v>6768287</v>
+        <v>6768356</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12005,12 +11900,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12037,14 +11932,14 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>127723453</v>
+        <v>127723534</v>
       </c>
       <c r="B118" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -12072,10 +11967,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>445418</v>
+        <v>445528</v>
       </c>
       <c r="R118" t="n">
-        <v>6768439</v>
+        <v>6768349</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12134,14 +12029,14 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>127723410</v>
+        <v>127723535</v>
       </c>
       <c r="B119" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -12169,10 +12064,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>445434</v>
+        <v>445518</v>
       </c>
       <c r="R119" t="n">
-        <v>6768336</v>
+        <v>6768343</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12199,12 +12094,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12231,14 +12126,14 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>127723443</v>
+        <v>127723536</v>
       </c>
       <c r="B120" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -12266,10 +12161,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>445422</v>
+        <v>445500</v>
       </c>
       <c r="R120" t="n">
-        <v>6768295</v>
+        <v>6768348</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12296,12 +12191,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12328,14 +12223,14 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>127723438</v>
+        <v>127723537</v>
       </c>
       <c r="B121" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -12363,10 +12258,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>445375</v>
+        <v>445488</v>
       </c>
       <c r="R121" t="n">
-        <v>6768277</v>
+        <v>6768315</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12393,12 +12288,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12425,14 +12320,14 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>127723503</v>
+        <v>127723538</v>
       </c>
       <c r="B122" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -12460,10 +12355,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>445439</v>
+        <v>445485</v>
       </c>
       <c r="R122" t="n">
-        <v>6768381</v>
+        <v>6768313</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12522,10 +12417,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>127722831</v>
+        <v>127722825</v>
       </c>
       <c r="B123" t="n">
-        <v>79661</v>
+        <v>79946</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12557,10 +12452,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>445370</v>
+        <v>445386</v>
       </c>
       <c r="R123" t="n">
-        <v>6768425</v>
+        <v>6768493</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12587,12 +12482,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12619,10 +12514,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>127723505</v>
+        <v>127722828</v>
       </c>
       <c r="B124" t="n">
-        <v>79043</v>
+        <v>79946</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12630,21 +12525,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12654,10 +12549,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>445493</v>
+        <v>445293</v>
       </c>
       <c r="R124" t="n">
-        <v>6768418</v>
+        <v>6768461</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12713,6 +12608,2663 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>127722829</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>445339</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6768436</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>127722831</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>445370</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6768425</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>127722832</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>445457</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6768397</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127722889</v>
+      </c>
+      <c r="B128" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>445372</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6768323</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>127722890</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>445306</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6768453</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>127722895</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>445370</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6768276</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>127722908</v>
+      </c>
+      <c r="B131" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>445329</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6768474</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>127722914</v>
+      </c>
+      <c r="B132" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>445325</v>
+      </c>
+      <c r="R132" t="n">
+        <v>6768463</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>127722917</v>
+      </c>
+      <c r="B133" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>445329</v>
+      </c>
+      <c r="R133" t="n">
+        <v>6768466</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Färska ringhack (gran)</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>127722918</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>445382</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6768422</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Färska ringhack (tall)</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>127722872</v>
+      </c>
+      <c r="B135" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>445414</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6768450</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>127722873</v>
+      </c>
+      <c r="B136" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>445364</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6768295</v>
+      </c>
+      <c r="S136" t="n">
+        <v>10</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>127722930</v>
+      </c>
+      <c r="B137" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>445390</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6768381</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>127722931</v>
+      </c>
+      <c r="B138" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>445518</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6768355</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>127723020</v>
+      </c>
+      <c r="B139" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>445379</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6768240</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>127723021</v>
+      </c>
+      <c r="B140" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>445390</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6768244</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>127723022</v>
+      </c>
+      <c r="B141" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>445412</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6768249</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>127723025</v>
+      </c>
+      <c r="B142" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>445397</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6768481</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>127723026</v>
+      </c>
+      <c r="B143" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>445387</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6768492</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>127723027</v>
+      </c>
+      <c r="B144" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>445343</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6768460</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>127723028</v>
+      </c>
+      <c r="B145" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>445345</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6768382</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>127723029</v>
+      </c>
+      <c r="B146" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>445351</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6768348</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>127723030</v>
+      </c>
+      <c r="B147" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>445376</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6768336</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>127723034</v>
+      </c>
+      <c r="B148" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>445377</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6768394</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>127729072</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Oxeråsen S. om, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>445342</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6768291</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>127723051</v>
+      </c>
+      <c r="B150" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Oxeråsen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>445307</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6768453</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35486-2025 artfynd.xlsx
+++ b/artfynd/A 35486-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY150"/>
+  <dimension ref="A1:AZ150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723565</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723592</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723593</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723601</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723602</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723603</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723604</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723605</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723606</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723607</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722863</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722864</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723560</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723561</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722885</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723403</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723404</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723405</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723407</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723408</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723409</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723410</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723411</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723412</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723413</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723414</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723415</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723416</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723417</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723418</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723420</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723421</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723422</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723423</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4072,6 +4247,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723424</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4169,6 +4349,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723425</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4266,6 +4451,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723426</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4363,6 +4553,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723427</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4460,6 +4655,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723428</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4557,6 +4757,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723429</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4654,6 +4859,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723430</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4751,6 +4961,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723431</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4848,6 +5063,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723432</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4945,6 +5165,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723433</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5042,6 +5267,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723434</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5139,6 +5369,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723435</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5236,6 +5471,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723436</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5333,6 +5573,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723437</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5430,6 +5675,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723438</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5527,6 +5777,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723439</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5624,6 +5879,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723440</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5721,6 +5981,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723441</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5818,6 +6083,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723442</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5915,6 +6185,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723443</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6012,6 +6287,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723444</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6109,6 +6389,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723445</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6206,6 +6491,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723446</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6303,6 +6593,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723447</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6400,6 +6695,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723448</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6497,6 +6797,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723451</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6594,6 +6899,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723452</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6691,6 +7001,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723453</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6788,6 +7103,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723454</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6885,6 +7205,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723455</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6982,6 +7307,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723456</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7079,6 +7409,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723477</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7176,6 +7511,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723478</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7273,6 +7613,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723479</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7370,6 +7715,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723480</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7467,6 +7817,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723481</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7564,6 +7919,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723482</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7661,6 +8021,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723483</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7758,6 +8123,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723484</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7855,6 +8225,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723485</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7952,6 +8327,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723486</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8049,6 +8429,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723487</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8146,6 +8531,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723488</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8243,6 +8633,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723489</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8340,6 +8735,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723490</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8437,6 +8837,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723492</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8534,6 +8939,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723493</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8631,6 +9041,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723494</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8728,6 +9143,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723495</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8825,6 +9245,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723496</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8922,6 +9347,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723497</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9019,6 +9449,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723498</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9116,6 +9551,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723499</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9213,6 +9653,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723500</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9310,6 +9755,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723501</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9407,6 +9857,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723503</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9504,6 +9959,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723504</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9601,6 +10061,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723505</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9698,6 +10163,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723506</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9795,6 +10265,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723507</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9892,6 +10367,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723510</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -9989,6 +10469,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723511</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10086,6 +10571,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723512</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10183,6 +10673,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723514</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10280,6 +10775,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723515</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10377,6 +10877,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723517</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10474,6 +10979,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723518</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10571,6 +11081,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723519</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10668,6 +11183,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723520</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10765,6 +11285,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723521</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10862,6 +11387,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723522</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10959,6 +11489,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723523</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11056,6 +11591,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723524</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11153,6 +11693,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723525</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11250,6 +11795,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723526</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11347,6 +11897,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723527</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11444,6 +11999,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723528</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11541,6 +12101,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723529</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11638,6 +12203,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723530</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11735,6 +12305,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723531</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11832,6 +12407,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723532</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11929,6 +12509,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723533</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12026,6 +12611,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723534</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12123,6 +12713,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723535</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12220,6 +12815,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723536</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12317,6 +12917,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723537</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12414,6 +13019,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723538</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12511,6 +13121,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722825</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12608,6 +13223,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722828</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12705,6 +13325,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722829</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12802,6 +13427,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722831</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12899,6 +13529,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722832</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13001,6 +13636,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722889</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13103,6 +13743,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722890</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13205,6 +13850,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722895</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13312,6 +13962,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722908</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13419,6 +14074,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722914</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13526,6 +14186,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722917</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13633,6 +14298,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722918</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13735,6 +14405,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722872</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -13837,6 +14512,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722873</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -13939,6 +14619,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722930</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14041,6 +14726,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127722931</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14143,6 +14833,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723020</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14245,6 +14940,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723021</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14347,6 +15047,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723022</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14449,6 +15154,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723025</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14551,6 +15261,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723026</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -14653,6 +15368,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723027</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -14755,6 +15475,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723028</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -14857,6 +15582,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723029</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -14959,6 +15689,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723030</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15061,6 +15796,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723034</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15168,6 +15908,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127729072</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15265,8 +16010,164 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127723051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>